--- a/sgo_lists.xlsx
+++ b/sgo_lists.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H305"/>
+  <dimension ref="A1:H304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -788,10 +788,22 @@
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>15900 North 78 Street, Ste. 210 Scottsdale, AZ 85260</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>480-699-8911</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>apesf.org</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>https://azdor.gov/sites/default/files/2023-06/REPORTS_sto-i-list.pdf</t>
@@ -810,10 +822,22 @@
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>921 N. Swan Road Tucson, AZ 85711</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>520-512-5438</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ibescholarships.org</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>https://azdor.gov/sites/default/files/2023-06/REPORTS_sto-i-list.pdf</t>
@@ -832,10 +856,22 @@
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>10645 N Tatum Blvd C200-294 Phoenix, AZ 85028</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>602-842-1795</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>valleytuitionorganization.org</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>https://azdor.gov/sites/default/files/2023-06/REPORTS_sto-i-list.pdf</t>
@@ -1272,9 +1308,21 @@
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>5251 DTC Parkway, Suite 1150 Greenwood Village CO 80111</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>303-407-0611</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>lrhodes@acescholarships.org</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
@@ -1294,9 +1342,21 @@
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>12615 Parallel Parkway Kansas City KS 66109</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>913-721-1573</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>dherrman@archkck.org</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
@@ -1316,9 +1376,21 @@
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>903 S. Glenn Avenue Wichita KS 67213</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>316-239-6472</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>alycia@mcadamsacademy.com</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
@@ -1338,9 +1410,21 @@
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1130 South Broadway Wichita KS 67211</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>316-682-3544</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>wellfavoredman@yahoo.com</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
@@ -1360,9 +1444,21 @@
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1110 N. Independence Beloit KS 67420</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>785-738-8774</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>joewalter320@gmail.com</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
@@ -1382,9 +1478,21 @@
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1307 Williams St. Great Bend KS 67530</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>620-792-3000</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>jason@goldenbeltcf.org</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
@@ -1404,9 +1512,21 @@
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1000 SW 10th Avenue Topeka KS 66604</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>785-357-4441</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>daniel@kslcms.org</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
@@ -1426,9 +1546,21 @@
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>8317 E. Douglas Wichita KS 67207</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>316-685-0152</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>ronda.goode@theindependentschool.com</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
@@ -1448,9 +1580,21 @@
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>7719 W 11th St. N Wichita KS 67212</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>316-214-2568</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>primefittrainer@gmail.com</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
@@ -1470,9 +1614,21 @@
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1110 Gravel Hill Rd Vinton VA 24179</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>540-890-8900</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>curtis@renewanation.org</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
@@ -1492,9 +1648,21 @@
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>910 Central Ave Dodge City KS 67801</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>620-227-1513</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>tdelgado@dcdiocese.org</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
@@ -1510,13 +1678,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>St. Paul Lutheran School Foundation</t>
+          <t>Scholarship Granting Fund for Catholic Diocese of Salina</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>103 N. 9th Street Salina KS 67401</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>785-827-8746</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>geoff.andrews@salinadiocese.org</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
@@ -1532,13 +1712,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Support for Catholic Schools, Inc.</t>
+          <t>St. Paul Lutheran School Foundation</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>320 N. 7th St. Leavenworth KS 66048</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>913-683-9604</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>john@jfdenney.com</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
@@ -1554,13 +1746,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Word of Life Ministries and Schools Inc.</t>
+          <t>Support for Catholic Schools, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>424 N. Broadway Wichita KS 67202</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>316-269-3915</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>schrockm@catholicdioceseofwichita.org</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
@@ -1571,22 +1775,34 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>KS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>A List of the Educational Assistance Organizations in the Program</t>
+          <t>Word of Life Ministries and Schools Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>915 E. 53rd St. Wichita KS 67219</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>316-644-3070</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Prob@WOLM.org</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://treasurer.mo.gov/Content/MOScholars_Information/MOScholarsEAOList2024-2025.xlsx</t>
+          <t>https://www.ksde.gov/docs/default-source/sf/sgo-directory-05122026.pdf</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1814,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Agudath Israel of Illinois dba Agudath Israel of Missouri</t>
+          <t>A List of the Educational Assistance Organizations in the Program</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1620,7 +1836,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bright Futures Fund</t>
+          <t>Agudath Israel of Illinois dba Agudath Israel of Missouri</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1642,7 +1858,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Children's Tuition Fund of MO</t>
+          <t>Bright Futures Fund</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1664,7 +1880,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Herzog Tomorrow Foundation</t>
+          <t>Children's Tuition Fund of MO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1686,7 +1902,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Missouri District of the Lutheran Church - Missouri Synod</t>
+          <t>Herzog Tomorrow Foundation</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1708,7 +1924,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Today and Tomorrow Educational Foundation</t>
+          <t>Missouri District of the Lutheran Church - Missouri Synod</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1725,12 +1941,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ACE Scholarships SSO, Montana, LLC</t>
+          <t>Today and Tomorrow Educational Foundation</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1740,7 +1956,7 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://svc.mt.gov/dor/educationdonation2/Pages/Reports/PublicStats?dt=SSO</t>
+          <t>https://treasurer.mo.gov/Content/MOScholars_Information/MOScholarsEAOList2024-2025.xlsx</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1968,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Big Sky Community School</t>
+          <t>ACE Scholarships SSO, Montana, LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1774,7 +1990,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Central Education Foundation of Silver Bow</t>
+          <t>Big Sky Community School</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1796,7 +2012,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Elevation Foundation Inc</t>
+          <t>Central Education Foundation of Silver Bow</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1818,7 +2034,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Great Falls Central Catholic High School</t>
+          <t>Elevation Foundation Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1840,7 +2056,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Holy Spirit Catholic School doing business as St. Patrick's Academy</t>
+          <t>Great Falls Central Catholic High School</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1862,7 +2078,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Kalispell Montessori Center Inc</t>
+          <t>Holy Spirit Catholic School doing business as St. Patrick's Academy</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1884,7 +2100,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Manhattan Christian School</t>
+          <t>Kalispell Montessori Center Inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1906,7 +2122,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Missoula Catholic Schools Foundation</t>
+          <t>Manhattan Christian School</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1928,7 +2144,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Missoula Christian Montessori School</t>
+          <t>Missoula Catholic Schools Foundation</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1950,7 +2166,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Montana Leadership Foundation</t>
+          <t>Missoula Christian Montessori School</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1972,7 +2188,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Our Lady of Lourdes Catholic School</t>
+          <t>Montana Leadership Foundation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1994,7 +2210,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Saint Matthew Parish Series 535, LLC</t>
+          <t>Our Lady of Lourdes Catholic School</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -2016,7 +2232,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Headwaters Academy, Inc.</t>
+          <t>Saint Matthew Parish Series 535, LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -2038,7 +2254,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Skola</t>
+          <t>The Headwaters Academy, Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -2060,7 +2276,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The Summit Lighthouse, Inc.</t>
+          <t>The Skola</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -2082,7 +2298,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The Way Christian School</t>
+          <t>The Summit Lighthouse, Inc.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -2104,7 +2320,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Valley Christian School</t>
+          <t>The Way Christian School</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -2126,7 +2342,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Woodland Montessori School Foundation</t>
+          <t>Valley Christian School</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -2143,12 +2359,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>AAA Scholarship Foundation-NV, LLC</t>
+          <t>Woodland Montessori School Foundation</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -2158,7 +2374,7 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://webapp-strapi-paas-prod-nde-001.azurewebsites.net/uploads/Registered_Scholarship_Organizations_af21ccf71e.pdf</t>
+          <t>https://svc.mt.gov/dor/educationdonation2/Pages/Reports/PublicStats?dt=SSO</t>
         </is>
       </c>
     </row>
@@ -2170,13 +2386,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AAA Scholarships</t>
+          <t>AAA Scholarship Foundation-NV, LLC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1452 W. Horizon Ridge Road, #541, Henderson NV 89012</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>(888)707-2465</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>kim@aaascholarships.org</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
@@ -2196,9 +2424,21 @@
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>24 W. Camelback Road Suite A 535,Phoenix, AZ 85013</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>(866)622-4ASK</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>info@ASKscholarships.org</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
@@ -2214,13 +2454,25 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ASK Scholarships</t>
+          <t>Silver State Scholarships</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>6655 W. Sahara Ave. #D106 Las Vegas, NV 89146</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>(702)736-7787</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>scholarships@silverstatescholarships.org</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
@@ -2236,13 +2488,25 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Silver State Scholarships</t>
+          <t>Education Fund of Northern Nevada</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>3025 Mill Street, Reno, NV 89509</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>(775)742-4285</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>efnninfo@gmail.com</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
@@ -2258,13 +2522,25 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Education Fund of Northern Nevada</t>
+          <t>Student Choice Fund of Nevada</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1755 Village Center Circle studentchoicefundofnevada.org</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>(702)410-8143</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Studentchoicefundofnevada@gmail.com</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
@@ -2275,44 +2551,60 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Injured Police Officers Fund</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
+          <t>ABC Ohio Foundation</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>33-2382950</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>351 Aurora Street, Hudson, Ohio 44236</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://webapp-strapi-paas-prod-nde-001.azurewebsites.net/uploads/Registered_Scholarship_Organizations_af21ccf71e.pdf</t>
+          <t>https://charitable.ohioago.gov/Scholarship-Granting-Organization-Certification/List</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Student Choice Fund of Nevada</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
+          <t>American Scholarship Network</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>42-1945763</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>4456 N Abbe Rd #305, Sheffield Village, Ohio 44054</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://webapp-strapi-paas-prod-nde-001.azurewebsites.net/uploads/Registered_Scholarship_Organizations_af21ccf71e.pdf</t>
+          <t>https://charitable.ohioago.gov/Scholarship-Granting-Organization-Certification/List</t>
         </is>
       </c>
     </row>
@@ -2324,17 +2616,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ABC Ohio Foundation</t>
+          <t>Aurora City Schools Scholarship Granting Organization</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>33-2382950</t>
+          <t>41-2906278</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>351 Aurora Street, Hudson, Ohio 44236</t>
+          <t>PO Box 109, Aurora, Ohio 44202</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -2354,17 +2646,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>American Scholarship Network</t>
+          <t>Buckeye Christian School Organization</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>42-1945763</t>
+          <t>34-1417866</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>4456 N Abbe Rd #305, Sheffield Village, Ohio 44054</t>
+          <t>2400 Chandlersville Rd, Zanesville, Ohio 43056</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -2384,17 +2676,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Aurora City Schools Scholarship Granting Organization</t>
+          <t>Chaminade Julienne Catholic Education Fund</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>41-2906278</t>
+          <t>99-1384296</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>PO Box 109, Aurora, Ohio 44202</t>
+          <t>505 S Ludlow St, Dayton, Ohio 45402</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -2414,17 +2706,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Buckeye Christian School Organization</t>
+          <t>CISE-SGO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>34-1417866</t>
+          <t>88-3142134</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2400 Chandlersville Rd, Zanesville, Ohio 43056</t>
+          <t>100 E. 8th Street, Cincinnati, Ohio 45202</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -2444,17 +2736,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Chaminade Julienne Catholic Education Fund</t>
+          <t>Give For Kids Scholarship Fund</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>99-1384296</t>
+          <t>39-4236057</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>505 S Ludlow St, Dayton, Ohio 45402</t>
+          <t>4334 BAINTREE RD, University Heights, Ohio 44118</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -2474,17 +2766,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CISE-SGO</t>
+          <t>Heights Tax Credit SGO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>88-3142134</t>
+          <t>41-4353004</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>100 E. 8th Street, Cincinnati, Ohio 45202</t>
+          <t>260 Fenwick Road, University Heights, Ohio 44118</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -2504,17 +2796,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Give For Kids Scholarship Fund</t>
+          <t>Julie Billiart Network Scholarship Granting Organization</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>39-4236057</t>
+          <t>33-1279122</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>4334 BAINTREE RD, University Heights, Ohio 44118</t>
+          <t>6140 Parkland Blvd, Ste. 300, Mayfield Heights, Ohio 44124</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -2534,17 +2826,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Heights Tax Credit SGO</t>
+          <t>Lutheran Scholarship Granting Organization of Ohio</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>41-4353004</t>
+          <t>87-3374872</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>260 Fenwick Road, University Heights, Ohio 44118</t>
+          <t>3870 Linden Rd, Rocky River, Ohio 44116</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -2564,17 +2856,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Julie Billiart Network Scholarship Granting Organization</t>
+          <t>Mount Notre Dame SGO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>33-1279122</t>
+          <t>92-3287314</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>6140 Parkland Blvd, Ste. 300, Mayfield Heights, Ohio 44124</t>
+          <t>711 E. Columbia Avenue, CINCINNATI, Ohio 45215</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -2594,17 +2886,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Lutheran Scholarship Granting Organization of Ohio</t>
+          <t>Mustard Seed Education Foundation</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>87-3374872</t>
+          <t>83-1341078</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>3870 Linden Rd, Rocky River, Ohio 44116</t>
+          <t>43 S. HURON ST., TOLEDO, Ohio 43604</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -2624,17 +2916,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Mount Notre Dame SGO</t>
+          <t>Nordonia Hills Schools Scholarship Granting Organization</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>92-3287314</t>
+          <t>92-2756655</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>711 E. Columbia Avenue, CINCINNATI, Ohio 45215</t>
+          <t>219 W AURORA RD STE A, NORTHFIELD, Ohio 44067</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -2654,17 +2946,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MUSTARD SEED EDUCATION FOUNDATION</t>
+          <t>Notre Dame Academy Foundation</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>83-1341078</t>
+          <t>82-3446307</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>43 S. HURON ST., TOLEDO, Ohio 43604</t>
+          <t>3535 W. Sylvania Avenue, Toledo, Ohio 43623</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -2684,17 +2976,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nordonia Hills Schools Scholarship Granting Organization</t>
+          <t>Notre Dame Schools Scholarship Granting Organization</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>92-2756655</t>
+          <t>88-1481999</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>219 W AURORA RD STE A, NORTHFIELD, Ohio 44067</t>
+          <t>13000 Auburn Road, Chardon, Ohio 44024</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -2714,17 +3006,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Notre Dame Academy Foundation</t>
+          <t>Ohio Association of Independent Schools Scholarship Granting Organizations</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>82-3446307</t>
+          <t>87-4616853</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>3535 W. Sylvania Avenue, Toledo, Ohio 43623</t>
+          <t>P.O. Box 492, Granville, Ohio 43023</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -2744,17 +3036,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Notre Dame Schools Scholarship Granting Organization</t>
+          <t>Saint Joseph Academy Scholarship Granting Organization</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>88-1481999</t>
+          <t>92-1890302</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>13000 Auburn Road, Chardon, Ohio 44024</t>
+          <t>3470 Rocky River Drive, Cleveland, Ohio 44111</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -2774,17 +3066,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ohio Association of Independent Schools Scholarship Granting Organizations</t>
+          <t>Saint Ursula Academy Foundation, Inc.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>87-4616853</t>
+          <t>34-1886759</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>P.O. Box 492, Granville, Ohio 43023</t>
+          <t>4025 Indian Road, Toledo, Ohio 43606</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -2804,17 +3096,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Saint Joseph Academy Scholarship Granting Organization</t>
+          <t>Seton Cincinnati SGO</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>92-1890302</t>
+          <t>92-2429826</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>3470 Rocky River Drive, Cleveland, Ohio 44111</t>
+          <t>3901 Glenway Avenue, Cincinnati, Ohio 45205</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -2834,17 +3126,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Saint Ursula Academy Foundation, Inc.</t>
+          <t>SMDPHS Scholarship Granting Organization</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>34-1886759</t>
+          <t>93-1632132</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4025 Indian Road, Toledo, Ohio 43606</t>
+          <t>6202 St. Clair, CLEVELAND, Ohio 44103</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -2864,17 +3156,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Seton Cincinnati SGO</t>
+          <t>St. Francis de Sales High School Foundation</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>92-2429826</t>
+          <t>34-1696266</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>3901 Glenway Avenue, Cincinnati, Ohio 45205</t>
+          <t>2323 W Bancroft St, Toledo, Ohio 43607</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -2894,17 +3186,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SMDPHS Scholarship Granting Organization</t>
+          <t>The Scholarship Granting Organization Of The Catholic Community Foundation</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>93-1632132</t>
+          <t>87-3652751</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>6202 St. Clair, CLEVELAND, Ohio 44103</t>
+          <t>1404 East 9th Street, Cleveland, Ohio 44114</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -2924,17 +3216,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>St. Francis de Sales High School Foundation</t>
+          <t>The St Johns Jesuit Scholarship Granting Organization</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>34-1696266</t>
+          <t>92-2707224</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2323 W Bancroft St, Toledo, Ohio 43607</t>
+          <t>5901 Airport Hwy, Toledo, Ohio 43615</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -2954,17 +3246,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>THE SCHOLARSHIP GRANTING ORGANIZATION OF THE CATHOLIC COMMUNITY FOUNDATION</t>
+          <t>Ursuline Foundation</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>87-3652751</t>
+          <t>31-1233054</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>1404 East 9th Street, Cleveland, Ohio 44114</t>
+          <t>5535 Pfeiffer Road, Cincinnati, Ohio 45242</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -2984,17 +3276,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>THE ST JOHNS JESUIT SCHOLARSHIP GRANTING ORGANIZATION</t>
+          <t>Waldorf Method Education Scholarship Association</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>92-2707224</t>
+          <t>93-3579746</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>5901 Airport Hwy, Toledo, Ohio 43615</t>
+          <t>76 Charleston Ave., Columbus, Ohio 43214</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -3009,60 +3301,76 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ursuline Foundation</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>31-1233054</t>
-        </is>
-      </c>
+          <t>Academy in Manayunk d/b/a AIM Academy</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>5535 Pfeiffer Road, Cincinnati, Ohio 45242</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
+          <t>1200 River Road, Conshohocken, PA  19428</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>(215) 483-2461</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>development@aimpa.org</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>www.aimpa.org</t>
+        </is>
+      </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://charitable.ohioago.gov/Scholarship-Granting-Organization-Certification/List</t>
+          <t>https://dced.pa.gov/wp-content/themes/business2015/csv/eitc_so_list.csv</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Waldorf Method Education Scholarship Association</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>93-3579746</t>
-        </is>
-      </c>
+          <t>Academy of Notre Dame de Namur</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>76 Charleston Ave., Columbus, Ohio 43214</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+          <t>560 Sproul Road, Villanova, PA  19085</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>(610) 971-1630</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Tkyle@ndapa.org</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>www.ndapa.org</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://charitable.ohioago.gov/Scholarship-Granting-Organization-Certification/List</t>
+          <t>https://dced.pa.gov/wp-content/themes/business2015/csv/eitc_so_list.csv</t>
         </is>
       </c>
     </row>
@@ -3074,28 +3382,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Academy in Manayunk d/b/a AIM Academy</t>
+          <t>ACSI Children's Education Fund d/b/a Children's Tuition Fund of Pennsylvania - SO</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1200 River Road, Conshohocken, PA  19428</t>
+          <t>P.O. Box 62249, Colorado Springs, CO  80962</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>(215) 483-2461</t>
+          <t>(717) 285-3022</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>development@aimpa.org</t>
+          <t>Saralee_lenhart@acsi.org</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>www.aimpa.org</t>
+          <t>www.childrenstuitionfund.org</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -3112,28 +3420,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Academy of Notre Dame de Namur</t>
+          <t>Agnes Irwin School</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>560 Sproul Road, Villanova, PA  19085</t>
+          <t>275 S. Ithan Ave., Bryn Mawr, PA  19010</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>(610) 971-1630</t>
+          <t>(610) 801-1260</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tkyle@ndapa.org</t>
+          <t>erauch@agnesirwin.org</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>www.ndapa.org</t>
+          <t>www.agnesirwin.org</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -3150,28 +3458,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ACSI Children's Education Fund d/b/a Children's Tuition Fund of Pennsylvania - SO</t>
+          <t>Aquinas Academy</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>P.O. Box 62249, Colorado Springs, CO  80962</t>
+          <t>2308 West Hardies Road, Gibsonia, PA  15044</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>(717) 285-3022</t>
+          <t>(724) 444-0722</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Saralee_lenhart@acsi.org</t>
+          <t>leonard@aquinasacademy-pittsburgh.org</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>www.childrenstuitionfund.org</t>
+          <t>www.aquinasacademy-pittsburgh.org</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -3188,28 +3496,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Agnes Irwin School</t>
+          <t>Armstrong County Community Foundation - SO</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>275 S. Ithan Ave., Bryn Mawr, PA  19010</t>
+          <t>220 S. Jefferson Street, Suite B, Kittanning, PA  16201</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>(610) 801-1260</t>
+          <t>(724) 548-5897</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>erauch@agnesirwin.org</t>
+          <t>jodi@servingtheheart.org</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>www.agnesirwin.org</t>
+          <t>www.servingtheheart.org</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -3226,28 +3534,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Aquinas Academy</t>
+          <t>Athletic Club of Fairhill Inc.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2308 West Hardies Road, Gibsonia, PA  15044</t>
+          <t>1205 E. Columbia Ave., Philadelphia, PA  19125</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>(724) 444-0722</t>
+          <t>(267) 908-9166</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>leonard@aquinasacademy-pittsburgh.org</t>
+          <t>acfairhill@gmail.com</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>www.aquinasacademy-pittsburgh.org</t>
+          <t>www.acfairhilll.com</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -3264,28 +3572,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Armstrong County Community Foundation - SO</t>
+          <t>Benchmark School</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>220 S. Jefferson Street, Suite B, Kittanning, PA  16201</t>
+          <t>2107 N. Providence Road, Media, PA  19063</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>(724) 548-5897</t>
+          <t>(610) 565-3741</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>jodi@servingtheheart.org</t>
+          <t>joemcpeak@benchmarkschool.org</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>www.servingtheheart.org</t>
+          <t>www.benchmarkschool.org</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -3302,28 +3610,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Athletic Club of Fairhill Inc.</t>
+          <t>Berks County Community Foundation - SO</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>1205 E. Columbia Ave., Philadelphia, PA  19125</t>
+          <t>237 Court Street, Reading, PA  19601</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>(267) 908-9166</t>
+          <t>(610) 685-2223</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>acfairhill@gmail.com</t>
+          <t>frankia@bccf.org</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>www.acfairhilll.com</t>
+          <t>www.bccf.org</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -3340,28 +3648,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Benchmark School</t>
+          <t>Bridge Educational Foundation - SO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2107 N. Providence Road, Media, PA  19063</t>
+          <t>909 Green Street, Harrisburg, PA  17102</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>(610) 565-3741</t>
+          <t>(717) 214-6792</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>joemcpeak@benchmarkschool.org</t>
+          <t>natalie.nutt@bridgeedu.org</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>www.benchmarkschool.org</t>
+          <t>www.bridgeedu.org</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -3378,28 +3686,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Berks County Community Foundation - SO</t>
+          <t>Bryn Athyn Church of the New Jerusalem</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>237 Court Street, Reading, PA  19601</t>
+          <t>600 Tomlinson Rd., PO Box 277, Bryn Athyn, PA  19009</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>(610) 685-2223</t>
+          <t>(215) 544-1407</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>frankia@bccf.org</t>
+          <t>Fauve.Nash@brynathynchurch.org</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>www.bccf.org</t>
+          <t>www.brynathynchurch.org</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -3416,28 +3724,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Bridge Educational Foundation - SO</t>
+          <t>Buckingham Friends School</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>909 Green Street, Harrisburg, PA  17102</t>
+          <t>5684 York Road, Lahaska, PA  18931</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>(717) 214-6792</t>
+          <t>(215) 794-7496</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>natalie.nutt@bridgeedu.org</t>
+          <t>sfrenkel@bfs.org</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>www.bridgeedu.org</t>
+          <t>www.bfs.org</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -3454,28 +3762,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Bryn Athyn Church of the New Jerusalem</t>
+          <t>Business Leadership Organized for Catholic Schools (BLOCS) - SO</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>600 Tomlinson Rd., PO Box 277, Bryn Athyn, PA  19009</t>
+          <t>Croton Road Corporate Center, 555 Croton Road, Suite 310, King of Prussia, PA  19406</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>(215) 544-1407</t>
+          <t>(484) 704-2307</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Fauve.Nash@brynathynchurch.org</t>
+          <t>kharvey@blocs.org</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>www.brynathynchurch.org</t>
+          <t>www.blocs.org</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -3492,28 +3800,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Buckingham Friends School</t>
+          <t>Buxmont Academy - SO</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>5684 York Road, Lahaska, PA  18931</t>
+          <t>531 Main Street, Bethlehem, PA  18018</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>(215) 794-7496</t>
+          <t>(215) 534-5215</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>sfrenkel@bfs.org</t>
+          <t>mdeantonio@csfbuxmont.org</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>www.bfs.org</t>
+          <t>www.csfbuxmont.org</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -3530,28 +3838,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Business Leadership Organized for Catholic Schools (BLOCS) - SO</t>
+          <t>Byerschool Foundation - SO</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Croton Road Corporate Center, 555 Croton Road, Suite 310, King of Prussia, PA  19406</t>
+          <t>1911 Arch Street, Philadelphia, PA  19103</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>(484) 704-2307</t>
+          <t>(215) 772-3053</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>kharvey@blocs.org</t>
+          <t>rgelb@byerschool.org</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>www.blocs.org</t>
+          <t>www.byerschool.org</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -3568,28 +3876,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Buxmont Academy - SO</t>
+          <t>C.B. Community Schools</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>531 Main Street, Bethlehem, PA  18018</t>
+          <t>4101 Freeland Avenue, Philadelphia, PA  19128</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>(215) 534-5215</t>
+          <t>(267) 766-3130</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>mdeantonio@csfbuxmont.org</t>
+          <t>mmccrea@cbcommunityschools.org</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>www.csfbuxmont.org</t>
+          <t>www.communityschools.org</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -3606,28 +3914,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Byerschool Foundation - SO</t>
+          <t>Calvary Christian Academy - SO</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>1911 Arch Street, Philadelphia, PA  19103</t>
+          <t>13500 Philmont Avenue, Philadelphia, PA  19116</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>(215) 772-3053</t>
+          <t>(215) 969-1579</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>rgelb@byerschool.org</t>
+          <t>Mpennisi@ccphilly.org</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>www.byerschool.org</t>
+          <t>www.cca.ccphilly.org</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -3644,28 +3952,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>C.B. Community Schools</t>
+          <t>Camphill Special School, Inc.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>4101 Freeland Avenue, Philadelphia, PA  19128</t>
+          <t>1784 Fairview Road, Glenmoore, PA  19343</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>(267) 766-3130</t>
+          <t>(610) 469-9236</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>mmccrea@cbcommunityschools.org</t>
+          <t>cripple@camphillschool.org</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>www.communityschools.org</t>
+          <t>www.camphillschool.org/</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -3682,28 +3990,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Calvary Christian Academy - SO</t>
+          <t>Carnegie Mellon University - SO</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>13500 Philmont Avenue, Philadelphia, PA  19116</t>
+          <t>Carnegie Mellon Children's School, 5000 Forbes Avenue, MMC-17, Pittsburgh, PA  15213</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>(215) 969-1579</t>
+          <t>(412) 268-2198</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mpennisi@ccphilly.org</t>
+          <t>lh37@andrew.cmu.edu</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>www.cca.ccphilly.org</t>
+          <t>www.cmu.edu/dietrich/psychology/cs/index.html</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -3720,28 +4028,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Camphill Special School, Inc.</t>
+          <t>Carroll Patriot Educational Fund</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>1784 Fairview Road, Glenmoore, PA  19343</t>
+          <t>Archbishop Carroll High School, 211 Matsonford Road, Radnor, PA  19087</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>(610) 469-9236</t>
+          <t>(267) 838-3462</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>cripple@camphillschool.org</t>
+          <t>cokeefe@jcarroll.org</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>www.camphillschool.org/</t>
+          <t>www.jcarroll.org</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -3758,28 +4066,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University - SO</t>
+          <t>Central Pennsylvania Scholarship Fund - SO</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Carnegie Mellon Children's School, 5000 Forbes Avenue, MMC-17, Pittsburgh, PA  15213</t>
+          <t>501 3rd Street, Tyrone, PA  16686</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>(412) 268-2198</t>
+          <t>(814) 942-4406</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>lh37@andrew.cmu.edu</t>
+          <t>tami@cpsfcharity.org</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>www.cmu.edu/dietrich/psychology/cs/index.html</t>
+          <t>www.pennsylvaniaeitc.org</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -3796,30 +4104,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Carroll Patriot Educational Fund</t>
+          <t>Chabad Jewish Scholarship Foundation - SO</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Archbishop Carroll High School, 211 Matsonford Road, Radnor, PA  19087</t>
+          <t>1311 Fort Washington Ave., Fort Washington, PA  19034</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>(267) 838-3462</t>
+          <t>(215) 591-9310</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>cokeefe@jcarroll.org</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>www.jcarroll.org</t>
-        </is>
-      </c>
+          <t>devorah@jewishmc.com</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
           <t>https://dced.pa.gov/wp-content/themes/business2015/csv/eitc_so_list.csv</t>
@@ -3834,28 +4138,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Central Pennsylvania Scholarship Fund - SO</t>
+          <t>Children First America Delaware County - SO</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>501 3rd Street, Tyrone, PA  16686</t>
+          <t>1005 W. 7th Street, Chester, PA  19013</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>(814) 942-4406</t>
+          <t>(610) 872-7472</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>tami@cpsfcharity.org</t>
+          <t>cfadelawareco@aol.com</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>www.pennsylvaniaeitc.org</t>
+          <t>www.cfadelco.org</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -3872,26 +4176,30 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Chabad Jewish Scholarship Foundation - SO</t>
+          <t>Children's Scholarship Fund of Pennsylvania - SO</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>1311 Fort Washington Ave., Fort Washington, PA  19034</t>
+          <t>633 Mayfield Road, Clarion, PA  16214</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>(215) 591-9310</t>
+          <t>(814) 226-4160</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>devorah@jewishmc.com</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr"/>
+          <t>mbauer@kriebelgas.com</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>www.csfofpa.org</t>
+        </is>
+      </c>
       <c r="H132" t="inlineStr">
         <is>
           <t>https://dced.pa.gov/wp-content/themes/business2015/csv/eitc_so_list.csv</t>
@@ -3906,28 +4214,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Children First America Delaware County - SO</t>
+          <t>Children's Scholarship Fund Philadelphia - SO</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>1005 W. 7th Street, Chester, PA  19013</t>
+          <t>1500 Walnut Street, Suite 1300, Philadelphia, PA  19102</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>(610) 872-7472</t>
+          <t>(215) 670-8411</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>cfadelawareco@aol.com</t>
+          <t>mstaples@csfphiladelphia.org</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>www.cfadelco.org</t>
+          <t>www.csfphiladelphia.org</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -3944,28 +4252,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Children's Scholarship Fund of Pennsylvania - SO</t>
+          <t>Christian School Association of York - SO</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>633 Mayfield Road, Clarion, PA  16214</t>
+          <t>907 Greenbriar Rd., York, PA  17404</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>(814) 226-4160</t>
+          <t>(717) 767-6842</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>mbauer@kriebelgas.com</t>
+          <t>aallen@csyonline.com</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>www.csfofpa.org</t>
+          <t>www.csyonline.com</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -3982,28 +4290,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Children's Scholarship Fund Philadelphia - SO</t>
+          <t>Commonwealth Charitable Management, Inc. - SO</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>1500 Walnut Street, Suite 1300, Philadelphia, PA  19102</t>
+          <t>270 Lake Avenue, Montrose, PA  18801</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>(215) 670-8411</t>
+          <t>(570) 278-3800</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>mstaples@csfphiladelphia.org</t>
+          <t>cclayton@commonwealthcharitable.org</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>www.csfphiladelphia.org</t>
+          <t>www.commonwealthcharitable.org</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -4020,28 +4328,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Christian School Association of York - SO</t>
+          <t>Community Country Day School</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>907 Greenbriar Rd., York, PA  17404</t>
+          <t>5800 Old Zuck Road, Erie, PA  16506</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>(717) 767-6842</t>
+          <t>(814) 833-7933</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>aallen@csyonline.com</t>
+          <t>angelacollins@ccdserie.com</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>www.csyonline.com</t>
+          <t>www.ccdserie.com</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -4058,28 +4366,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Commonwealth Charitable Management, Inc. - SO</t>
+          <t>Community Foundation of Fayette County - SO</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>270 Lake Avenue, Montrose, PA  18801</t>
+          <t>250 West Main Street, Uniontown, PA  15401</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>(570) 278-3800</t>
+          <t>(724) 437-8600</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>cclayton@commonwealthcharitable.org</t>
+          <t>cvalentine@cffayettepa.org</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>www.commonwealthcharitable.org</t>
+          <t>www.cffayettepa.org</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -4096,28 +4404,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Community Country Day School</t>
+          <t>Community Foundation of Greene County - SO</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>5800 Old Zuck Road, Erie, PA  16506</t>
+          <t>108 East High Street, P.O. Box 768, Waynesburg, PA  15370</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>(814) 833-7933</t>
+          <t>(724) 627-2010</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>angelacollins@ccdserie.com</t>
+          <t>dave.cfgcpa@gmail.com</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>www.ccdserie.com</t>
+          <t>www.cfgcpa.org</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -4134,28 +4442,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Community Foundation of Fayette County - SO</t>
+          <t>Community Foundation of Western PA and Eastern OH - SO</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>250 West Main Street, Uniontown, PA  15401</t>
+          <t>7 West State Street, Suite 301, Sharon, PA  16146</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>(724) 437-8600</t>
+          <t>(724) 981-5882</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>cvalentine@cffayettepa.org</t>
+          <t>julia@comm-foundation.org</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>www.cffayettepa.org</t>
+          <t>www.comm-foundation.org</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -4172,28 +4480,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Community Foundation of Greene County - SO</t>
+          <t>Community Partnership School - SO</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>108 East High Street, P.O. Box 768, Waynesburg, PA  15370</t>
+          <t>3033 W. Glenwood Avenue, Philadelphia, PA  19121</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>(724) 627-2010</t>
+          <t>(215) 235-0461</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>dave.cfgcpa@gmail.com</t>
+          <t>m.closter@cpsphilly.org</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>www.cfgcpa.org</t>
+          <t>www.communitypartnershipschool.org</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -4210,28 +4518,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Community Foundation of Western PA and Eastern OH - SO</t>
+          <t>Comprehensive Learning Center, Inc. - SO</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>7 West State Street, Suite 301, Sharon, PA  16146</t>
+          <t>444 Jacksonville Rd., Warminster, PA  18974</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>(724) 981-5882</t>
+          <t>(215) 956-3861</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>julia@comm-foundation.org</t>
+          <t>kmartin@clcschoolprograms.org</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>www.comm-foundation.org</t>
+          <t>www.clcschoolprograms.org</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -4248,28 +4556,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Community Partnership School - SO</t>
+          <t>Cornerstone Christian Academy</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>3033 W. Glenwood Avenue, Philadelphia, PA  19121</t>
+          <t>1939 S. 58th Street, P.O. Box 5520, Philadelphia, PA  19143</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>(215) 235-0461</t>
+          <t>(215) 724-6858</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>m.closter@cpsphilly.org</t>
+          <t>dblackwell@cornerstonephiladelphia.com</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>www.communitypartnershipschool.org</t>
+          <t>www.wearecornerstone.com</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -4286,28 +4594,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Comprehensive Learning Center, Inc. - SO</t>
+          <t>Crispus Attucks Association, Inc. - SO</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>444 Jacksonville Rd., Warminster, PA  18974</t>
+          <t>605 S. Duke Street, York, PA  17401</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>(215) 956-3861</t>
+          <t>(717) 848-3612</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>kmartin@clcschoolprograms.org</t>
+          <t>dwilliams@crispusattucks.org</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>www.clcschoolprograms.org</t>
+          <t>www.crispusattucks.org</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -4324,28 +4632,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Cornerstone Christian Academy</t>
+          <t>Cristo Rey Philadelphia High School</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>1939 S. 58th Street, P.O. Box 5520, Philadelphia, PA  19143</t>
+          <t>1717 W. Allegheny Avenue, Philadelphia, PA  19132</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>(215) 724-6858</t>
+          <t>(215) 219-3943</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>dblackwell@cornerstonephiladelphia.com</t>
+          <t>ljensen@crphs.org</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>www.wearecornerstone.com</t>
+          <t>www.cristoreyphiladelphia.org</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -4362,28 +4670,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Crispus Attucks Association, Inc. - SO</t>
+          <t>Crossroads Foundation</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>605 S. Duke Street, York, PA  17401</t>
+          <t>6901 Lynn Way, Pittsburgh, PA  15208</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>(717) 848-3612</t>
+          <t>(412) 228-4611</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>dwilliams@crispusattucks.org</t>
+          <t>kkalson@crfdn.org</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>www.crispusattucks.org</t>
+          <t>www.crossroadsfoundation.org</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -4400,28 +4708,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Cristo Rey Philadelphia High School</t>
+          <t>Dayspring Christian Academy - SO</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>1717 W. Allegheny Avenue, Philadelphia, PA  19132</t>
+          <t>120 College Avenue, Suite 106, Mountville, PA  17554</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>(215) 219-3943</t>
+          <t>(717) 285-2000</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>ljensen@crphs.org</t>
+          <t>jriddell@dayspringchristian.com</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>www.cristoreyphiladelphia.org</t>
+          <t>www.dayspringchristian.com</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -4438,28 +4746,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Crossroads Foundation</t>
+          <t>Delaware Valley Friends School</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>6901 Lynn Way, Pittsburgh, PA  15208</t>
+          <t>19 E. Central Ave., Paoli, PA  19301</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>(412) 228-4611</t>
+          <t>(610) 640-4150</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>kkalson@crfdn.org</t>
+          <t>stephanie.speakman@dvfriends.org</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>www.crossroadsfoundation.org</t>
+          <t>www.dvfriends.org</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -4476,28 +4784,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Dayspring Christian Academy - SO</t>
+          <t>dePaul School in Northeastern Pennsylvania</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>120 College Avenue, Suite 106, Mountville, PA  17554</t>
+          <t>415 Biden Street, Scranton, PA  18505</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>(717) 285-2000</t>
+          <t>(570) 534-4736</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>jriddell@dayspringchristian.com</t>
+          <t>cgilroy@friendshiphousepa.org</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>www.dayspringchristian.com</t>
+          <t>www.depaulschoolnepa.org</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -4514,28 +4822,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Delaware Valley Friends School</t>
+          <t>Devon Preparatory School</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>19 E. Central Ave., Paoli, PA  19301</t>
+          <t>363 N. Valley Forge Road, Devon, PA  19333</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>(610) 640-4150</t>
+          <t>(610) 688-7337</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>stephanie.speakman@dvfriends.org</t>
+          <t>sroxberry@devonprep.com</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>www.dvfriends.org</t>
+          <t>www.devonprep.com</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -4552,28 +4860,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>dePaul School in Northeastern Pennsylvania</t>
+          <t>Discovery MI Preschool d/b/a Discovery Montessori</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>415 Biden Street, Scranton, PA  18505</t>
+          <t>1733 N. Main Ave, Scranton, PA  18508</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>(570) 534-4736</t>
+          <t>(570) 702-7909</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>cgilroy@friendshiphousepa.org</t>
+          <t>mydiscoverypreschool@gmail.com</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>www.depaulschoolnepa.org</t>
+          <t>www.discoverypa.org</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -4590,28 +4898,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Devon Preparatory School</t>
+          <t>Drexel Neumann Academy</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>363 N. Valley Forge Road, Devon, PA  19333</t>
+          <t>1901 Potter Street, Chester, PA  19013</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>(610) 688-7337</t>
+          <t>(610) 872-7358</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>sroxberry@devonprep.com</t>
+          <t>f.gillen@drexelneumannacademy.net</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>www.devonprep.com</t>
+          <t>www.drexelneumannacademy.net</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -4628,28 +4936,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Discovery MI Preschool d/b/a Discovery Montessori</t>
+          <t>Eastern Pennsylvania Scholarship Foundation - Diocese of Allentown - SO</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>1733 N. Main Ave, Scranton, PA  18508</t>
+          <t>P.O. Box F, 1515 Martin Luther King Jr. Drive, Allentown, PA  18102</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>(570) 702-7909</t>
+          <t>(484) 704-2311</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>mydiscoverypreschool@gmail.com</t>
+          <t>aimpellizzeri@blocs.org</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>www.discoverypa.org</t>
+          <t>www.allentowndiocese.org</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -4666,28 +4974,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Drexel Neumann Academy</t>
+          <t>Erie Day School, Inc. - SO</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>1901 Potter Street, Chester, PA  19013</t>
+          <t>1372 West Sixth Street, Erie, PA  16505</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>(610) 872-7358</t>
+          <t>(814) 452-4273</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>f.gillen@drexelneumannacademy.net</t>
+          <t>sgrosch@eriedayschool.com</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>www.drexelneumannacademy.net</t>
+          <t>www.eriedayschool.org</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -4704,28 +5012,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Eastern Pennsylvania Scholarship Foundation - Diocese of Allentown - SO</t>
+          <t>Everence Foundation, Inc. d/b/a Mennonite Foundation - SO</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>P.O. Box F, 1515 Martin Luther King Jr. Drive, Allentown, PA  18102</t>
+          <t>1110 N. Main St., P.O. Box 483, Goshen, IN  46527</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>(484) 704-2311</t>
+          <t>(717) 653-6662</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>aimpellizzeri@blocs.org</t>
+          <t>Elyse.Kauffman@everence.com</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>www.allentowndiocese.org</t>
+          <t>www.everence.com</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -4742,28 +5050,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Erie Day School, Inc. - SO</t>
+          <t>Extra Mile Education Foundation, Inc.</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>1372 West Sixth Street, Erie, PA  16505</t>
+          <t>603 Stanwix St., Suite 348, Pittsburgh, PA  15222</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>(814) 452-4273</t>
+          <t>(412) 716-8637</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>sgrosch@eriedayschool.com</t>
+          <t>avescio@extramilefdn.org</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>www.eriedayschool.org</t>
+          <t>www.extramilefdn.org</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -4780,28 +5088,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Everence Foundation, Inc. d/b/a Mennonite Foundation - SO</t>
+          <t>Faith Builders Educational Programs, Inc. - SO</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>1110 N. Main St., P.O. Box 483, Goshen, IN  46527</t>
+          <t>28527 Guys Mills Rd., Guys Mills, PA  16327</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>(717) 653-6662</t>
+          <t>(814) 789-4518</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Elyse.Kauffman@everence.com</t>
+          <t>secretary@fbscholarship.org</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>www.everence.com</t>
+          <t>www.fbscholarship.org</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -4818,28 +5126,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Extra Mile Education Foundation, Inc.</t>
+          <t>Faith Christian School Association of Monroe County, Inc.</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>603 Stanwix St., Suite 348, Pittsburgh, PA  15222</t>
+          <t>122 Dante Street, Roseto, PA  18013</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>(412) 716-8637</t>
+          <t>(610) 588-8815</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>avescio@extramilefdn.org</t>
+          <t>hazelton@fcslions.org</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>www.extramilefdn.org</t>
+          <t>www.fcslions.org</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -4856,28 +5164,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Faith Builders Educational Programs, Inc. - SO</t>
+          <t>Falk Laboratory School of the University of Pittsburgh</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>28527 Guys Mills Rd., Guys Mills, PA  16327</t>
+          <t>4060 Allequippa Street, Pittsburgh, PA  15261</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>(814) 789-4518</t>
+          <t>(412) 624-8020</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>secretary@fbscholarship.org</t>
+          <t>jill.sarada@pitt.edu</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>www.fbscholarship.org</t>
+          <t>www.falkschool.pitt.edu/</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -4894,28 +5202,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Faith Christian School Association of Monroe County, Inc.</t>
+          <t>Family Choice Scholarship Program of the PA Family Institute - SO</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>122 Dante Street, Roseto, PA  18013</t>
+          <t>23 North Front Street, Harrisburg, PA  17101</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>(610) 588-8815</t>
+          <t>(717) 743-1146</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>hazelton@fcslions.org</t>
+          <t>familychoice@pafamily.org</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>www.fcslions.org</t>
+          <t>www.myfamilychoice.org</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -4932,28 +5240,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Falk Laboratory School of the University of Pittsburgh</t>
+          <t>First Regular Baptist Church of Northumberland</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>4060 Allequippa Street, Pittsburgh, PA  15261</t>
+          <t>Northumberland Christian School, 351 Fifth Street, Northumberland, PA  17857</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>(412) 624-8020</t>
+          <t>(570) 473-9786</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>jill.sarada@pitt.edu</t>
+          <t>jdrees@norrychristian.net</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>www.falkschool.pitt.edu/</t>
+          <t>www.norrychristian.net</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -4970,28 +5278,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Family Choice Scholarship Program of the PA Family Institute - SO</t>
+          <t>First Tee Greater Philadelphia - SO</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>23 North Front Street, Harrisburg, PA  17101</t>
+          <t>800 Walnut Lane, Philadelphia, PA  19128</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>(717) 743-1146</t>
+          <t>(215) 680-5750</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>familychoice@pafamily.org</t>
+          <t>jmcaleese@firstteephila.org</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>www.myfamilychoice.org</t>
+          <t>www.firstteephiladelphia.org</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -5008,28 +5316,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>First Regular Baptist Church of Northumberland</t>
+          <t>Foundation for Catholic Education - SO</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Northumberland Christian School, 351 Fifth Street, Northumberland, PA  17857</t>
+          <t>1373 Enterprise Drive, West Chester, PA  19380</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>(570) 473-9786</t>
+          <t>(610) 793-8065</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>jdrees@norrychristian.net</t>
+          <t>jparsons@ctdi.com</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>www.norrychristian.net</t>
+          <t>www.foundationforcatholiceducation.org</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -5046,28 +5354,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>First Tee Greater Philadelphia - SO</t>
+          <t>Foundation for Jewish Day Schools of Greater Philadelphia - SO</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>800 Walnut Lane, Philadelphia, PA  19128</t>
+          <t>2001 Market St. - 23rd Floor, Philadelphia, PA  19103</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>(215) 680-5750</t>
+          <t>(215) 832-0525</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>jmcaleese@firstteephila.org</t>
+          <t>ematz@jewishphilly.org</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>www.firstteephiladelphia.org</t>
+          <t>www.jewishphilly.org</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -5084,28 +5392,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Foundation for Catholic Education - SO</t>
+          <t>Frankford Friends School</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>1373 Enterprise Drive, West Chester, PA  19380</t>
+          <t>1500 Orthodox Street, Philadelphia, PA  19124</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>(610) 793-8065</t>
+          <t>(267) 513-8013</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>jparsons@ctdi.com</t>
+          <t>jwheeler@frankfordfriends.org</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>www.foundationforcatholiceducation.org</t>
+          <t>www.frankfordfriends.org</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -5122,28 +5430,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Foundation for Jewish Day Schools of Greater Philadelphia - SO</t>
+          <t>French International School of Philadelphia - SO</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2001 Market St. - 23rd Floor, Philadelphia, PA  19103</t>
+          <t>150 North Highland Avenue, Bala Cynwyd, PA  19004</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>(215) 832-0525</t>
+          <t>(610) 667-1284</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>ematz@jewishphilly.org</t>
+          <t>Leballeur@frenchschoolphila.org</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>www.jewishphilly.org</t>
+          <t>www.frenchschoolphila.org</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -5160,28 +5468,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Frankford Friends School</t>
+          <t>Friends Select School</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>1500 Orthodox Street, Philadelphia, PA  19124</t>
+          <t>1651 Benjamin Franklin Parkway, Philadelphia, PA  19103</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>(267) 513-8013</t>
+          <t>(215) 561-5900</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>jwheeler@frankfordfriends.org</t>
+          <t>aneglawi@friends-select.org</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>www.frankfordfriends.org</t>
+          <t>www.friends-select.org</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -5198,28 +5506,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>French International School of Philadelphia - SO</t>
+          <t>Fund for Girard College</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>150 North Highland Avenue, Bala Cynwyd, PA  19004</t>
+          <t>2101 S. College Avenue, Philadelphia, PA  19121</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>(610) 667-1284</t>
+          <t>(215) 787-4436</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Leballeur@frenchschoolphila.org</t>
+          <t>resposito@girardcollege.edu</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>www.frenchschoolphila.org</t>
+          <t>www.girardcollege.edu/support/fund/</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -5236,28 +5544,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Friends Select School</t>
+          <t>Fund for the Advancement of Minorities through Education, Inc. (FAME)</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>1651 Benjamin Franklin Parkway, Philadelphia, PA  19103</t>
+          <t>P.O. Box 100073, Pittsburgh, PA  15233</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>(215) 561-5900</t>
+          <t>(412) 363-5553</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>aneglawi@friends-select.org</t>
+          <t>hmoreland@famefund.org</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>www.friends-select.org</t>
+          <t>www.famefund.org</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -5274,28 +5582,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Fund for Girard College</t>
+          <t>George Junior Republic - SO</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2101 S. College Avenue, Philadelphia, PA  19121</t>
+          <t>233 George Junior Road, Grove City, PA  16127</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>(215) 787-4436</t>
+          <t>(724) 458-9330</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>resposito@girardcollege.edu</t>
+          <t>tduong@gjr.org</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>www.girardcollege.edu/support/fund/</t>
+          <t>www.GJR.org</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -5312,28 +5620,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Fund for the Advancement of Minorities through Education, Inc. (FAME)</t>
+          <t>George School</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
-          <t>P.O. Box 100073, Pittsburgh, PA  15233</t>
+          <t>1690 Newtown Langhorne Road, Newtown, PA  18940</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>(412) 363-5553</t>
+          <t>(215) 579-6573</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>hmoreland@famefund.org</t>
+          <t>ahessert@georgeschool.org</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>www.famefund.org</t>
+          <t>www.georgeschool.org</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -5350,28 +5658,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>George Junior Republic - SO</t>
+          <t>Germantown Academy (Public School of Germantown) - SO</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
-          <t>233 George Junior Road, Grove City, PA  16127</t>
+          <t>340 Morris Road, Fort Washington, PA  19034</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>(724) 458-9330</t>
+          <t>(267) 405-7140</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>tduong@gjr.org</t>
+          <t>karen.wertz@germantownacademy.org</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>www.GJR.org</t>
+          <t>www.germantownacademy.net</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -5388,28 +5696,28 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>George School</t>
+          <t>Gesu School, Inc. - SO</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
-          <t>1690 Newtown Langhorne Road, Newtown, PA  18940</t>
+          <t>1700 West Thompson Street, Philadelphia, PA  19121</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>(215) 579-6573</t>
+          <t>(267) 546-7484</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>ahessert@georgeschool.org</t>
+          <t>rob.weinstein@gesuschool.org</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>www.georgeschool.org</t>
+          <t>www.gesuschool.org</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -5426,28 +5734,28 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Germantown Academy (Public School of Germantown) - SO</t>
+          <t>Gladwyne Montessori School - SO</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
-          <t>340 Morris Road, Fort Washington, PA  19034</t>
+          <t>920 Youngsford Road, Gladwyne, PA  19035</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>(267) 405-7140</t>
+          <t>(610) 649-1761</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>karen.wertz@germantownacademy.org</t>
+          <t>mdyson@gladwyne.org</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>www.germantownacademy.net</t>
+          <t>www.gladwyne.org</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -5464,28 +5772,28 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Gesu School, Inc. - SO</t>
+          <t>Goals and Assists Foundation</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
-          <t>1700 West Thompson Street, Philadelphia, PA  19121</t>
+          <t>3601 S. Broad Street, Philadelphia, PA  19148</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>(267) 546-7484</t>
+          <t>(215) 952-5271</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>rob.weinstein@gesuschool.org</t>
+          <t>sharan@sniderhockey.org</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>www.gesuschool.org</t>
+          <t>www.sniderhockey.org</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -5502,28 +5810,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Gladwyne Montessori School - SO</t>
+          <t>Greene Street Friends School - SO</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>920 Youngsford Road, Gladwyne, PA  19035</t>
+          <t>20 West Armat St, Philadelphia, PA  19144</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>(610) 649-1761</t>
+          <t>(215) 438-7000</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>mdyson@gladwyne.org</t>
+          <t>mwaldor@greenestreetfriends.org</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>www.gladwyne.org</t>
+          <t>www.greenestreetfriends.org</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -5540,28 +5848,28 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Goals and Assists Foundation</t>
+          <t>Greene Towne School - SO</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>3601 S. Broad Street, Philadelphia, PA  19148</t>
+          <t>55 N. 22nd Street, Philadelphia, PA  19103</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>(215) 952-5271</t>
+          <t>(215) 563-6368</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>sharan@sniderhockey.org</t>
+          <t>areath@gtms.org</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>www.sniderhockey.org</t>
+          <t>www.gtms.org</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -5578,28 +5886,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Greene Street Friends School - SO</t>
+          <t>Gwynedd Mercy Academy High School</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>20 West Armat St, Philadelphia, PA  19144</t>
+          <t>1345 Sumneytown Pike, Lower Gwynedd, PA  19002</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>(215) 438-7000</t>
+          <t>(267) 885-3717</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>mwaldor@greenestreetfriends.org</t>
+          <t>cfrascatore@gmahs.org</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>www.greenestreetfriends.org</t>
+          <t>www.gmahs.org</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -5616,28 +5924,28 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Greene Towne School - SO</t>
+          <t>Harrisburg Academy</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>55 N. 22nd Street, Philadelphia, PA  19103</t>
+          <t>10 Erford Road, Wormleysburg, PA  17043</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>(215) 563-6368</t>
+          <t>(717) 763-7811</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>areath@gtms.org</t>
+          <t>preston.s@harrisburgacademy.org</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>www.gtms.org</t>
+          <t>www.harrisburgacademy.org</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -5654,28 +5962,28 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Gwynedd Mercy Academy High School</t>
+          <t>Heritage Community Initiatives - SO</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
-          <t>1345 Sumneytown Pike, Lower Gwynedd, PA  19002</t>
+          <t>820 Braddock Avenue, Braddock, PA  15104</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>(267) 885-3717</t>
+          <t>(412) 351-0535</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>cfrascatore@gmahs.org</t>
+          <t>lkelley@heritageserves.org</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>www.gmahs.org</t>
+          <t>www.heritageserves.org</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -5692,28 +6000,28 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Harrisburg Academy</t>
+          <t>High Point Classical Academy</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>10 Erford Road, Wormleysburg, PA  17043</t>
+          <t>1919 Mountain Road, Larksville, PA  18651</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>(717) 763-7811</t>
+          <t>(570) 592-4203</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>preston.s@harrisburgacademy.org</t>
+          <t>bakolodgie@highpointclassicalacademy.com</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>www.harrisburgacademy.org</t>
+          <t>highpointclassicalacademy.com</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -5730,28 +6038,28 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Heritage Community Initiatives - SO</t>
+          <t>Hill School</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>820 Braddock Avenue, Braddock, PA  15104</t>
+          <t>860 Beech Street, Pottstown, PA  19484</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>(412) 351-0535</t>
+          <t>(610) 705-1199</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>lkelley@heritageserves.org</t>
+          <t>kkoller@thehill.org</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>www.heritageserves.org</t>
+          <t>www.thehill.org</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -5768,28 +6076,28 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>High Point Classical Academy</t>
+          <t>HMS School for Children with Cerebral Palsy</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1919 Mountain Road, Larksville, PA  18651</t>
+          <t>4400 Baltimore Avenue, Philadelphia, PA  19104</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>(570) 592-4203</t>
+          <t>(215) 222-2566</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>bakolodgie@highpointclassicalacademy.com</t>
+          <t>Cpimentel@HMSSchool.org</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>highpointclassicalacademy.com</t>
+          <t>www.hmsschool.org</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -5806,28 +6114,28 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Hill School</t>
+          <t>Holy Family Foundation - SO</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
-          <t>860 Beech Street, Pottstown, PA  19484</t>
+          <t>8235 Ohio River Blvd., Pittsburgh, PA  15202</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>(610) 705-1199</t>
+          <t>(412) 239-9011</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>kkoller@thehill.org</t>
+          <t>sexauer.michael@hfi-pgh.org</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>www.thehill.org</t>
+          <t>www.hfi-pgh.org</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -5844,28 +6152,28 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>HMS School for Children with Cerebral Palsy</t>
+          <t>Hope Partnership for Education</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
-          <t>4400 Baltimore Avenue, Philadelphia, PA  19104</t>
+          <t>2601 N. 11th St., Philadelphia, PA  19133</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>(215) 222-2566</t>
+          <t>(215) 232-5410</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Cpimentel@HMSSchool.org</t>
+          <t>vsheppard@hope-partnership.org</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>www.hmsschool.org</t>
+          <t>www.hope-partnership.org</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -5882,28 +6190,28 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Holy Family Foundation - SO</t>
+          <t>House of Hope York, PA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
-          <t>8235 Ohio River Blvd., Pittsburgh, PA  15202</t>
+          <t>23 N. Pleasant Avenue, Jacobus, PA  17407</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>(412) 239-9011</t>
+          <t>(717) 235-3198</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>sexauer.michael@hfi-pgh.org</t>
+          <t>lori.ziegler@houseofhopeyork.org</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>www.hfi-pgh.org</t>
+          <t>www.houseof hopeyork.org</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -5920,30 +6228,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Hope Partnership for Education</t>
+          <t>IFA Foundation</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2601 N. 11th St., Philadelphia, PA  19133</t>
+          <t>7157 Camp Hill Rd., Fort Washington, PA  19034</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>(215) 232-5410</t>
+          <t>(484) 919-0282</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>vsheppard@hope-partnership.org</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>www.hope-partnership.org</t>
-        </is>
-      </c>
+          <t>john@ifa.llc</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr">
         <is>
           <t>https://dced.pa.gov/wp-content/themes/business2015/csv/eitc_so_list.csv</t>
@@ -5958,28 +6262,28 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>House of Hope York, PA</t>
+          <t>Imani Christian Academy - SO</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
-          <t>23 N. Pleasant Avenue, Jacobus, PA  17407</t>
+          <t>2150 East Hills Drive, Pittsburgh, PA  15221</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>(717) 235-3198</t>
+          <t>(412) 731-7982</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>lori.ziegler@houseofhopeyork.org</t>
+          <t>pnzambi@imaniadmin.org</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>www.houseof hopeyork.org</t>
+          <t>www.imanipgh.org</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -5996,26 +6300,30 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>IFA Foundation</t>
+          <t>Independence Mission Schools</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
-          <t>7157 Camp Hill Rd., Fort Washington, PA  19034</t>
+          <t>1012 W. Thompson Street, Philadelphia, PA  19122</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>(484) 919-0282</t>
+          <t>(215) 771-7038</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>john@ifa.llc</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr"/>
+          <t>bfoley@imsphila.org</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://imsphila.org/</t>
+        </is>
+      </c>
       <c r="H188" t="inlineStr">
         <is>
           <t>https://dced.pa.gov/wp-content/themes/business2015/csv/eitc_so_list.csv</t>
@@ -6030,28 +6338,28 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Imani Christian Academy - SO</t>
+          <t>Indian Creek Valley Christian Family and Children's Center - SO</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2150 East Hills Drive, Pittsburgh, PA  15221</t>
+          <t>2166 Indian Head Rd., Champion, PA  15622</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>(412) 731-7982</t>
+          <t>(724) 455-2122</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>pnzambi@imaniadmin.org</t>
+          <t>merle_skinner@champion.org</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>www.imanipgh.org</t>
+          <t>www.champion.org</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -6068,28 +6376,28 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Independence Mission Schools</t>
+          <t>Jewish Community Alliance of Northeastern Pennsylvania - SO</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
-          <t>1012 W. Thompson Street, Philadelphia, PA  19122</t>
+          <t>613 S.J. Strauss Lane, Kingston, PA  18704</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>(215) 771-7038</t>
+          <t>(570) 574-1136</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>bfoley@imsphila.org</t>
+          <t>jgillespie@nepajca.org.</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://imsphila.org/</t>
+          <t>www.jewishwilkes-barre.org</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -6106,28 +6414,28 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Indian Creek Valley Christian Family and Children's Center - SO</t>
+          <t>Jewish Federation of the Lehigh Valley - SO</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2166 Indian Head Rd., Champion, PA  15622</t>
+          <t>702 N. 22nd Street, Allentown, PA  18104</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>(724) 455-2122</t>
+          <t>(610) 821-5500</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>merle_skinner@champion.org</t>
+          <t>aaron@jflv.org</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>www.champion.org</t>
+          <t>www.jewishlehighvalley.org</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -6144,28 +6452,28 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Jewish Community Alliance of Northeastern Pennsylvania - SO</t>
+          <t>Junior Achievement of Western PA - SO</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
-          <t>613 S.J. Strauss Lane, Kingston, PA  18704</t>
+          <t>90 Emerson Lane, Suite 1403, Bridgeville, PA  15017</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>(570) 574-1136</t>
+          <t>(814) 691-7619</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>jgillespie@nepajca.org.</t>
+          <t>jknepper@jawesternpa.org</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>www.jewishwilkes-barre.org</t>
+          <t>www.jawesternpa.org</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -6182,28 +6490,28 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Jewish Federation of the Lehigh Valley - SO</t>
+          <t>Keystone Christian Education Association - SO</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
-          <t>702 N. 22nd Street, Allentown, PA  18104</t>
+          <t>6101 Bell Road, Harrisburg, PA  17111</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>(610) 821-5500</t>
+          <t>(717) 564-1164</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>aaron@jflv.org</t>
+          <t>tclater@kcea.com</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>www.jewishlehighvalley.org</t>
+          <t>KCEA.com</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -6220,28 +6528,28 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Junior Achievement of Western PA - SO</t>
+          <t>Kimberton Waldorf School - SO</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
-          <t>90 Emerson Lane, Suite 1403, Bridgeville, PA  15017</t>
+          <t>410 West Seven Stars Road, Phoenixville, PA  19460</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>(814) 691-7619</t>
+          <t>(610) 933-3635</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>jknepper@jawesternpa.org</t>
+          <t>development@kimberton.org</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>www.jawesternpa.org</t>
+          <t>www.kimberton.org</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -6258,28 +6566,28 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Keystone Christian Education Association - SO</t>
+          <t>Kiskiminetas Springs School</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
-          <t>6101 Bell Road, Harrisburg, PA  17111</t>
+          <t>1888 Brett Lane, Saltsburg, PA  15681</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>(717) 564-1164</t>
+          <t>(724) 639-8047</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>tclater@kcea.com</t>
+          <t>vickie.fluharty@kiski.org</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>KCEA.com</t>
+          <t>www.kiski.org</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -6296,28 +6604,28 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Kimberton Waldorf School - SO</t>
+          <t>La Salle Academy</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
-          <t>410 West Seven Stars Road, Phoenixville, PA  19460</t>
+          <t>1434 North 2nd Street, Philadelphia, PA  19122</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>(610) 933-3635</t>
+          <t>(215) 739-5804</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>development@kimberton.org</t>
+          <t>mgthomson@lasalleacademy.net</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>www.kimberton.org</t>
+          <t>www.lasalleacademy.net</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -6334,28 +6642,28 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Kiskiminetas Springs School</t>
+          <t>Lancaster Country Day School - SO</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
-          <t>1888 Brett Lane, Saltsburg, PA  15681</t>
+          <t>725 Hamilton Road, Lancaster, PA  17603</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>(724) 639-8047</t>
+          <t>(717) 397-7240</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>vickie.fluharty@kiski.org</t>
+          <t>lamars@lancastercountryday.org</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>www.kiski.org</t>
+          <t>www.lancastercountryday.org</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -6372,28 +6680,28 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>La Salle Academy</t>
+          <t>Lancaster County Career &amp; Technology Foundation - SO</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
-          <t>1434 North 2nd Street, Philadelphia, PA  19122</t>
+          <t>432 Old Market Street, Mt. Joy, PA  17552</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>(215) 739-5804</t>
+          <t>(717) 653-3009</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>mgthomson@lasalleacademy.net</t>
+          <t>jbaker@lancasterctc.edu</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>www.lasalleacademy.net</t>
+          <t>www.lcctf.org</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -6410,28 +6718,28 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Lancaster Country Day School - SO</t>
+          <t>Lancaster County Christian School</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
-          <t>725 Hamilton Road, Lancaster, PA  17603</t>
+          <t>2390 New Holland Pike, Lancaster, PA  17601</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>(717) 397-7240</t>
+          <t>(717) 556-0711</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>lamars@lancastercountryday.org</t>
+          <t>nlong@lccs.cc</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>www.lancastercountryday.org</t>
+          <t>www.lccs.cc</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -6448,28 +6756,28 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Lancaster County Career &amp; Technology Foundation - SO</t>
+          <t>Liguori Academy, Inc.</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
-          <t>432 Old Market Street, Mt. Joy, PA  17552</t>
+          <t>2343 East Tucker Street, Philadelphia, PA  19125</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>(717) 653-3009</t>
+          <t>(267) 571-1952</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>jbaker@lancasterctc.edu</t>
+          <t>mmarrone@liguoriacademy.org</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>www.lcctf.org</t>
+          <t>www.liguoriacademy.org</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -6486,28 +6794,28 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Lancaster County Christian School</t>
+          <t>Linden Hall School for Girls</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2390 New Holland Pike, Lancaster, PA  17601</t>
+          <t>212 E. Main Street, Lititz, PA  17543</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>(717) 556-0711</t>
+          <t>(717) 626-8512</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>nlong@lccs.cc</t>
+          <t>business@lindenhall.org</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>www.lccs.cc</t>
+          <t>www.lindenhall.org</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -6524,28 +6832,28 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Liguori Academy, Inc.</t>
+          <t>LOGAN Hope - SO</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2343 East Tucker Street, Philadelphia, PA  19125</t>
+          <t>4934 N. 13th St., Philadelphia, PA  19141</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>(267) 571-1952</t>
+          <t>(215) 455-7442</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>mmarrone@liguoriacademy.org</t>
+          <t>jim@loganhope.org</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>www.liguoriacademy.org</t>
+          <t>www.loganhope.org</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -6562,28 +6870,28 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Linden Hall School for Girls</t>
+          <t>Logos Academy (Harrisburg) - SO</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
-          <t>212 E. Main Street, Lititz, PA  17543</t>
+          <t>251 Verbeke Street, Harrisburg, PA  17102</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>(717) 626-8512</t>
+          <t>(717) 727-5154</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>business@lindenhall.org</t>
+          <t>lauren.bonnema@logoshbg.org</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>www.lindenhall.org</t>
+          <t>www.logosHBG.org</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -6600,28 +6908,28 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>LOGAN Hope - SO</t>
+          <t>Logos Academy Scholarship Organization</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
-          <t>4934 N. 13th St., Philadelphia, PA  19141</t>
+          <t>250 West King Street, York, PA  17401</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>(215) 455-7442</t>
+          <t>(717) 848-9835</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>jim@loganhope.org</t>
+          <t>lisa.knier@logosyork.org</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>www.loganhope.org</t>
+          <t>www.logosyork.org</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -6638,28 +6946,28 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Logos Academy (Harrisburg) - SO</t>
+          <t>Londonderry School - SO</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
-          <t>251 Verbeke Street, Harrisburg, PA  17102</t>
+          <t>1800 Bamberger Road, Harrisburg, PA  17110</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>(717) 727-5154</t>
+          <t>(717) 540-0543</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>lauren.bonnema@logoshbg.org</t>
+          <t>jennifer.pomerantz@thelondonderryschool.org</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>www.logosHBG.org</t>
+          <t>www.thelondonderryschool.org</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -6676,28 +6984,28 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Logos Academy Scholarship Organization</t>
+          <t>Malvern Preparatory School</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
-          <t>250 West King Street, York, PA  17401</t>
+          <t>418 S. Warren Avenue, Malvern, PA  19355</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>(717) 848-9835</t>
+          <t>(484) 595-1122</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>lisa.knier@logosyork.org</t>
+          <t>nwertsch@malvernprep.org</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>www.logosyork.org</t>
+          <t>www.malvernprep.org</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -6714,28 +7022,28 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Londonderry School - SO</t>
+          <t>McGlynn Center</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
-          <t>1800 Bamberger Road, Harrisburg, PA  17110</t>
+          <t>72 Midland Court, P.O. Box 842, Wilkes-Barre, PA  18702</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>(717) 540-0543</t>
+          <t>(570) 824-8891</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>jennifer.pomerantz@thelondonderryschool.org</t>
+          <t>pnork@mcglynncenter.org</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>www.thelondonderryschool.org</t>
+          <t>www.mcglynncenter.org</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -6752,28 +7060,28 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Malvern Preparatory School</t>
+          <t>Meadowbrook Christian School Scholarship Organization K-12</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
-          <t>418 S. Warren Avenue, Malvern, PA  19355</t>
+          <t>Wesleyan Church Corporation, 363 Stamm Road, Milton, PA  17847</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>(484) 595-1122</t>
+          <t>(570) 742-2638</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>nwertsch@malvernprep.org</t>
+          <t>sheri.hoffman@mcslions.org</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>www.malvernprep.org</t>
+          <t>www.mcslions.org</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -6790,28 +7098,28 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>McGlynn Center</t>
+          <t>Media-Providence Friends School, Inc. - SO</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
-          <t>72 Midland Court, P.O. Box 842, Wilkes-Barre, PA  18702</t>
+          <t>125 W. Third Street, Media, PA  19063</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>(570) 824-8891</t>
+          <t>(610) 565-1960</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>pnork@mcglynncenter.org</t>
+          <t>cmcgoff@mpfs.org</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>www.mcglynncenter.org</t>
+          <t>www.mpfs.org</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -6828,28 +7136,28 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Meadowbrook Christian School Scholarship Organization K-12</t>
+          <t>Mercersburg Academy</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Wesleyan Church Corporation, 363 Stamm Road, Milton, PA  17847</t>
+          <t>100 Academy Drive, Mercersburg, PA  17236</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>(570) 742-2638</t>
+          <t>(717) 328-6359</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>sheri.hoffman@mcslions.org</t>
+          <t>batsonm@mercersburg.edu</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>www.mcslions.org</t>
+          <t>www.mercersburg.edu</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -6866,28 +7174,28 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Media-Providence Friends School, Inc. - SO</t>
+          <t>Mercy Vocational High School</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
-          <t>125 W. Third Street, Media, PA  19063</t>
+          <t>d/b/a Mercy Career &amp; Technical High School, 2900 W. Hunting Park Avenue, Philadelphia, PA  19129</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>(610) 565-1960</t>
+          <t>(215) 226-1225</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>cmcgoff@mpfs.org</t>
+          <t>ngreen@mercycte.org</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>www.mpfs.org</t>
+          <t>www.mercyvocational.org</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -6904,28 +7212,28 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Mercersburg Academy</t>
+          <t>Mercyhurst Preparatory School</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
-          <t>100 Academy Drive, Mercersburg, PA  17236</t>
+          <t>538 East Grandview Blvd., Erie, PA  16504</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>(717) 328-6359</t>
+          <t>(814) 824-2408</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>batsonm@mercersburg.edu</t>
+          <t>jgray@mpslakers.com</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>www.mercersburg.edu</t>
+          <t>www.mpslakers.com</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -6942,28 +7250,28 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Mercy Vocational High School</t>
+          <t>Merion Mercy Academy</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
-          <t>d/b/a Mercy Career &amp; Technical High School, 2900 W. Hunting Park Avenue, Philadelphia, PA  19129</t>
+          <t>511 Montgomery Ave., Merion Station, PA  19066</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>(215) 226-1225</t>
+          <t>(610) 664-6655</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>ngreen@mercycte.org</t>
+          <t>kcawley@merion-mercy.com</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>www.mercyvocational.org</t>
+          <t>www.merion-mercy.com</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -6980,28 +7288,28 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Mercyhurst Preparatory School</t>
+          <t>MMI Preparatory School</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>538 East Grandview Blvd., Erie, PA  16504</t>
+          <t>154 Centre Street, Freeland, PA  18224</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>(814) 824-2408</t>
+          <t>(570) 636-1108</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>jgray@mpslakers.com</t>
+          <t>kmcnulty@mmiprep.org</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>www.mpslakers.com</t>
+          <t>www.mmiprep.org</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -7018,28 +7326,28 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Merion Mercy Academy</t>
+          <t>Montessori Academy of Lancaster - SO</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
-          <t>511 Montgomery Ave., Merion Station, PA  19066</t>
+          <t>2750 Weaver Road, Lancaster, PA  17601</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>(610) 664-6655</t>
+          <t>(717) 560-0815</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>kcawley@merion-mercy.com</t>
+          <t>carol@montlanc.com</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>www.merion-mercy.com</t>
+          <t>www.montlanc.com</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -7056,28 +7364,28 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MMI Preparatory School</t>
+          <t>Montgomery County Scholarships, Inc.</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
-          <t>154 Centre Street, Freeland, PA  18224</t>
+          <t>101 Greenwood Avenue, Suite 380, Jenkintown, PA  19046</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>(570) 636-1108</t>
+          <t>(215) 253-8511</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>kmcnulty@mmiprep.org</t>
+          <t>jed.silversmith@pataxcredits.org</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>www.mmiprep.org</t>
+          <t>www.pataxcredits.org/</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -7094,28 +7402,28 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Montessori Academy of Lancaster - SO</t>
+          <t>Moravian Academy</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2750 Weaver Road, Lancaster, PA  17601</t>
+          <t>7 East Market Street, Bethlehem, PA  18018</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>(717) 560-0815</t>
+          <t>(610) 332-5291</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>carol@montlanc.com</t>
+          <t>bzaiser@mamail.net</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>www.montlanc.com</t>
+          <t>www.moravianacademy.org</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -7132,28 +7440,28 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Montgomery County Scholarships, Inc.</t>
+          <t>Nativity School of Harrisburg</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
-          <t>101 Greenwood Avenue, Suite 380, Jenkintown, PA  19046</t>
+          <t>2101 N. 5th Street, Harrisburg, PA  17110</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>(215) 253-8511</t>
+          <t>(717) 236-5602</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>jed.silversmith@pataxcredits.org</t>
+          <t>er@nativityschoolofharrisburg.org</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>www.pataxcredits.org/</t>
+          <t>www.nativityharrisburg.org</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -7170,28 +7478,28 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Moravian Academy</t>
+          <t>NativityMiguel School of Scranton</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
-          <t>7 East Market Street, Bethlehem, PA  18018</t>
+          <t>2300 Adams Ave., Scranton, PA  18509</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>(610) 332-5291</t>
+          <t>(570) 955-5176</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>bzaiser@mamail.net</t>
+          <t>rprislupski@nmscranton.org</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>www.moravianacademy.org</t>
+          <t>www.nativitymiguelscranton.org</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -7208,28 +7516,28 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Nativity School of Harrisburg</t>
+          <t>Neumann Scholarship Foundation - SO</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2101 N. 5th Street, Harrisburg, PA  17110</t>
+          <t>4800 Union Deposit Road, Harrisburg, PA  17111</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>(717) 236-5602</t>
+          <t>(717) 657-4804</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>er@nativityschoolofharrisburg.org</t>
+          <t>dbreen@hbgdiocese.org</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>www.nativityharrisburg.org</t>
+          <t>www.hbgdiocese.org</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -7246,28 +7554,28 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>NativityMiguel School of Scranton</t>
+          <t>Newtown Friends School</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2300 Adams Ave., Scranton, PA  18509</t>
+          <t>1940 Newtown Langhorne Road, Newtown, PA  18940</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>(570) 955-5176</t>
+          <t>(215) 968-2225</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>rprislupski@nmscranton.org</t>
+          <t>cfrank@newtownfriends.org</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>www.nativitymiguelscranton.org</t>
+          <t>www.newtownfriends.org</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -7284,28 +7592,28 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Neumann Scholarship Foundation - SO</t>
+          <t>Opera Philadelphia</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
-          <t>4800 Union Deposit Road, Harrisburg, PA  17111</t>
+          <t>1420 Locust St., Suite 210, Philadelphia, PA  19119</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>(717) 657-4804</t>
+          <t>(215) 893-5924</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>dbreen@hbgdiocese.org</t>
+          <t>mangum@operaphila.org</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>www.hbgdiocese.org</t>
+          <t>www.operaphila.org</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -7322,28 +7630,28 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Newtown Friends School</t>
+          <t>Our Lady of the Sacred Heart High School</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
-          <t>1940 Newtown Langhorne Road, Newtown, PA  18940</t>
+          <t>1504 Woodcrest Avenue, Coraopolis, PA  15108</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>(215) 968-2225</t>
+          <t>(412) 269-7726</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>cfrank@newtownfriends.org</t>
+          <t>ckarashin@olsh.org</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>www.newtownfriends.org</t>
+          <t>www.olsh.org</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -7360,30 +7668,26 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Opera Philadelphia</t>
+          <t>Our Promise Inc.</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
         <is>
-          <t>1420 Locust St., Suite 210, Philadelphia, PA  19119</t>
+          <t>1205 E. Columbia Ave., Philadelphia, PA  19125</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>(215) 893-5924</t>
+          <t>(267) 825-3188</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>mangum@operaphila.org</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>www.operaphila.org</t>
-        </is>
-      </c>
+          <t>sherman.washi@gmail.com</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr">
         <is>
           <t>https://dced.pa.gov/wp-content/themes/business2015/csv/eitc_so_list.csv</t>
@@ -7398,28 +7702,28 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Our Lady of the Sacred Heart High School</t>
+          <t>Pen Ryn School</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
-          <t>1504 Woodcrest Avenue, Coraopolis, PA  15108</t>
+          <t>235 South Olds Boulevard, Fairless Hills, PA  19030</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>(412) 269-7726</t>
+          <t>(215) 547-1800</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>ckarashin@olsh.org</t>
+          <t>billodcpa@aol.com</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>www.olsh.org</t>
+          <t>www.penryn.org</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -7436,26 +7740,30 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Our Promise Inc.</t>
+          <t>Penngift Foundation, Inc. - SO</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
-          <t>1205 E. Columbia Ave., Philadelphia, PA  19125</t>
+          <t>P.O. Box 121, Elverson, PA  19520</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>(267) 825-3188</t>
+          <t>(610) 286-1936</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>sherman.washi@gmail.com</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr"/>
+          <t>jcox@penngift.org</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>www.penngift.org</t>
+        </is>
+      </c>
       <c r="H226" t="inlineStr">
         <is>
           <t>https://dced.pa.gov/wp-content/themes/business2015/csv/eitc_so_list.csv</t>
@@ -7470,28 +7778,28 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Pen Ryn School</t>
+          <t>Penn-Mont Academy - SO</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
-          <t>235 South Olds Boulevard, Fairless Hills, PA  19030</t>
+          <t>131 Holliday Hills Drive, Hollidaysburg, PA  16648</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>(215) 547-1800</t>
+          <t>(814) 696-8801</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>billodcpa@aol.com</t>
+          <t>kathleen.dombrosky@pennmontacademy.com</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>www.penryn.org</t>
+          <t>www.pennmontacademy.com</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -7508,28 +7816,28 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Penngift Foundation, Inc. - SO</t>
+          <t>Perkiomen School</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
-          <t>P.O. Box 121, Elverson, PA  19520</t>
+          <t>200 Seminary Street, Pennsburg, PA  18073</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>(610) 286-1936</t>
+          <t>(267) 717-5548</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>jcox@penngift.org</t>
+          <t>sfarrand@perkiomen.org</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>www.penngift.org</t>
+          <t>www.perkiomen.org</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -7546,28 +7854,28 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Penn-Mont Academy - SO</t>
+          <t>Phase 4 Learning Center, Inc. - SO</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
-          <t>131 Holliday Hills Drive, Hollidaysburg, PA  16648</t>
+          <t>5850 Centre Avenue, Pittsburgh, PA  15206</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>(814) 696-8801</t>
+          <t>(215) 650-9004</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>kathleen.dombrosky@pennmontacademy.com</t>
+          <t>eraphael@phase4lc.org</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>www.pennmontacademy.com</t>
+          <t>www.phase4learningcenter.org</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -7584,28 +7892,28 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Perkiomen School</t>
+          <t>Philadelphia School of Democracy, Inc.</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
-          <t>200 Seminary Street, Pennsburg, PA  18073</t>
+          <t>4950 Springfield Ave., Philadelphia, PA  19143</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>(267) 717-5548</t>
+          <t>(215) 218-9586</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>sfarrand@perkiomen.org</t>
+          <t>mark@phillyfreeschool.org</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>www.perkiomen.org</t>
+          <t>www.phillyfreeschool.org</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -7622,28 +7930,28 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Phase 4 Learning Center, Inc. - SO</t>
+          <t>Pittsburgh Jewish Educational Improvement Foundation</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
-          <t>5850 Centre Avenue, Pittsburgh, PA  15206</t>
+          <t>2000 Technology Drive, Pittsburgh, PA  15219</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>(215) 650-9004</t>
+          <t>(412) 992-5250</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>eraphael@phase4lc.org</t>
+          <t>sjablow@jfedpgh.org</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>www.phase4learningcenter.org</t>
+          <t>www.jewishpgh.org</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -7660,28 +7968,28 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Philadelphia School of Democracy, Inc.</t>
+          <t>PJHS Scholarship Organization  (St. Joe's Prep &amp; Scranton Prep)</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
-          <t>4950 Springfield Ave., Philadelphia, PA  19143</t>
+          <t>1000 Wyoming Avenue, Scranton, PA  18509</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>(215) 218-9586</t>
+          <t>(570) 941-7737</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>mark@phillyfreeschool.org</t>
+          <t>mweed@scrantonprep.com</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>www.phillyfreeschool.org</t>
+          <t>www.scrantonprep.com</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -7698,28 +8006,28 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Pittsburgh Jewish Educational Improvement Foundation</t>
+          <t>Pocono Mountains United Way - SO</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2000 Technology Drive, Pittsburgh, PA  15219</t>
+          <t>301 McConnell Street, Stroudsburg, PA  18360</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>(412) 992-5250</t>
+          <t>(570) 517-3955</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>sjablow@jfedpgh.org</t>
+          <t>michael@poconounitedway.org</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>www.jewishpgh.org</t>
+          <t>www.poconounitedway.org</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -7736,28 +8044,28 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>PJHS Scholarship Organization  (St. Joe's Prep &amp; Scranton Prep)</t>
+          <t>Poise Foundation - SO</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
-          <t>1000 Wyoming Avenue, Scranton, PA  18509</t>
+          <t>Two Gateway Center, Suite 1700, 603 Stanwix Street, Pittsburgh, PA  15222</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>(570) 941-7737</t>
+          <t>(412) 281-4967</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>mweed@scrantonprep.com</t>
+          <t>Kjackson@poisefdn.org</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>www.scrantonprep.com</t>
+          <t>www.poisefoundation.org</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -7774,28 +8082,28 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Pocono Mountains United Way - SO</t>
+          <t>Quaker School at Horsham</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
-          <t>301 McConnell Street, Stroudsburg, PA  18360</t>
+          <t>250 Meetinghouse Rd., Horsham, PA  19044</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>(570) 517-3955</t>
+          <t>(215) 674-2875</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>michael@poconounitedway.org</t>
+          <t>gim@quakerschool.org</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>www.poconounitedway.org</t>
+          <t>www.quakerschool.org</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -7812,28 +8120,28 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Poise Foundation - SO</t>
+          <t>Sacred Heart Academy Bryn Mawr</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Two Gateway Center, Suite 1700, 603 Stanwix Street, Pittsburgh, PA  15222</t>
+          <t>480 S. Bryn Mawr Avenue, Bryn Mawr, PA  19010</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>(412) 281-4967</t>
+          <t>(610) 527-3915</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Kjackson@poisefdn.org</t>
+          <t>howard.walker@shabrynmawr.org</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>www.poisefoundation.org</t>
+          <t>www.shabrynmawr.org</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -7850,28 +8158,28 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Quaker School at Horsham</t>
+          <t>Saint James School</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
-          <t>250 Meetinghouse Rd., Horsham, PA  19044</t>
+          <t>3217 W. Clearfield Street, Philadelphia, PA  19132</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>(215) 674-2875</t>
+          <t>(484) 224-3886</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>gim@quakerschool.org</t>
+          <t>taxcredit@stjamesphila.org</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>www.quakerschool.org</t>
+          <t>www.stjamesphila.org</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -7888,28 +8196,28 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Sacred Heart Academy Bryn Mawr</t>
+          <t>Salvaggio Academy</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr">
         <is>
-          <t>480 S. Bryn Mawr Avenue, Bryn Mawr, PA  19010</t>
+          <t>1390 Ridgeview Drive, Allentown, PA  18104</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>(610) 527-3915</t>
+          <t>(610) 530-5241</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>howard.walker@shabrynmawr.org</t>
+          <t>salvaggioacademy.tax@cai.io</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>www.shabrynmawr.org</t>
+          <t>www.salvaggioacademy.org</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -7926,28 +8234,28 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Saint James School</t>
+          <t>Scholarship Partners Foundation - SO</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
         <is>
-          <t>3217 W. Clearfield Street, Philadelphia, PA  19132</t>
+          <t>723 East Pittsburgh St., Greensburg, PA  15601</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>(484) 224-3886</t>
+          <t>(724) 552-2589</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>taxcredit@stjamesphila.org</t>
+          <t>wbarnes@dioceseofgreensburg.org</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>www.stjamesphila.org</t>
+          <t>www.dioceseofgreensburg.org</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -7964,28 +8272,28 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Salvaggio Academy</t>
+          <t>Scholastic Opportunity Scholarship Fund (SOS) - SO</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
-          <t>1390 Ridgeview Drive, Allentown, PA  18104</t>
+          <t>Diocese of Pittsburgh, 2900 Noblestown Rd., Pittsburgh, PA  15205</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>(610) 530-5241</t>
+          <t>(412) 456-3085</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>salvaggioacademy.tax@cai.io</t>
+          <t>mfreker@diopitt.org</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>www.salvaggioacademy.org</t>
+          <t>www.diopitt.org</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -8002,28 +8310,28 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Scholarship Partners Foundation - SO</t>
+          <t>Sewickley Academy</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
-          <t>723 East Pittsburgh St., Greensburg, PA  15601</t>
+          <t>315 Academy Avenue, Sewickley, PA  15143</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>(724) 552-2589</t>
+          <t>(412) 741-2230</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>wbarnes@dioceseofgreensburg.org</t>
+          <t>bvuono@sewickley.org</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>www.dioceseofgreensburg.org</t>
+          <t>www.sewickley.org</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -8040,28 +8348,28 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Scholastic Opportunity Scholarship Fund (SOS) - SO</t>
+          <t>Shady Side Academy - SO</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Diocese of Pittsburgh, 2900 Noblestown Rd., Pittsburgh, PA  15205</t>
+          <t>423 Fox Chapel Road, Pittsburgh, PA  15238</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>(412) 456-3085</t>
+          <t>(412) 968-3032</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>mfreker@diopitt.org</t>
+          <t>jscott@shadysideacademy.org</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>www.diopitt.org</t>
+          <t>www.shadysideacademy.org</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -8078,28 +8386,28 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Sewickley Academy</t>
+          <t>Silverback Educational Foundation for the Arts, Dance &amp; Athletics - SO</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
-          <t>315 Academy Avenue, Sewickley, PA  15143</t>
+          <t>3811 West Chester Pike, Bldg. 2, Ste. 200, Newtown Square, PA  19073</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>(412) 741-2230</t>
+          <t>(717) 856-9195</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>bvuono@sewickley.org</t>
+          <t>rstover@grahampartners.net</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>www.sewickley.org</t>
+          <t>www.silverback-sefada.org</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -8116,28 +8424,28 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Shady Side Academy - SO</t>
+          <t>Solebury School</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
-          <t>423 Fox Chapel Road, Pittsburgh, PA  15238</t>
+          <t>6832 Phillips Mill Road, New Hope, PA  18938</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>(412) 968-3032</t>
+          <t>(215) 862-5261</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>jscott@shadysideacademy.org</t>
+          <t>mmarshall@solebury.org</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>www.shadysideacademy.org</t>
+          <t>www.solebury.org</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -8154,30 +8462,26 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Silverback Educational Foundation for the Arts, Dance &amp; Athletics - SO</t>
+          <t>Spanish Scholarship Fund</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
         <is>
-          <t>3811 West Chester Pike, Bldg. 2, Ste. 200, Newtown Square, PA  19073</t>
+          <t>1436 Lansdowne Ave, Darby, PA  19023</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>(717) 856-9195</t>
+          <t>(610) 558-4593</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>rstover@grahampartners.net</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>www.silverback-sefada.org</t>
-        </is>
-      </c>
+          <t>rowers3@verizon.net</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr">
         <is>
           <t>https://dced.pa.gov/wp-content/themes/business2015/csv/eitc_so_list.csv</t>
@@ -8192,28 +8496,28 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Solebury School</t>
+          <t>Springside Chestnut Hill Academy</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr">
         <is>
-          <t>6832 Phillips Mill Road, New Hope, PA  18938</t>
+          <t>500 West Willow Grove Avenue, Philadelphia, PA  19118</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>(215) 862-5261</t>
+          <t>(215) 754-1622</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>mmarshall@solebury.org</t>
+          <t>mboozer@sch.org</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>www.solebury.org</t>
+          <t>www.sch.org</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -8230,26 +8534,30 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Spanish Scholarship Fund</t>
+          <t>St. Edmund's Academy - SO</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
         <is>
-          <t>1436 Lansdowne Ave, Darby, PA  19023</t>
+          <t>5705 Darlington Road, Pittsburgh, PA  15217</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>(610) 558-4593</t>
+          <t>(412) 521-1907</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>rowers3@verizon.net</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr"/>
+          <t>dianamcallister@stedmunds.net</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>www.stedmunds.net</t>
+        </is>
+      </c>
       <c r="H247" t="inlineStr">
         <is>
           <t>https://dced.pa.gov/wp-content/themes/business2015/csv/eitc_so_list.csv</t>
@@ -8264,28 +8572,28 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Springside Chestnut Hill Academy</t>
+          <t>St. Stephen's Episcopal School</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
         <is>
-          <t>500 West Willow Grove Avenue, Philadelphia, PA  19118</t>
+          <t>215 N. Front Street, Harrisburg, PA  17101</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>(215) 754-1622</t>
+          <t>(717) 238-8590</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>mboozer@sch.org</t>
+          <t>dshaffer@sseschool.org</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>www.sch.org</t>
+          <t>www.sseschool.org</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -8302,28 +8610,28 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>St. Edmund's Academy - SO</t>
+          <t>State College Friends School - SO</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
         <is>
-          <t>5705 Darlington Road, Pittsburgh, PA  15217</t>
+          <t>1900 University Drive, State College, PA  16801</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>(412) 521-1907</t>
+          <t>(814) 237-8386</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>dianamcallister@stedmunds.net</t>
+          <t>jlove@scfriends.org</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>www.stedmunds.net</t>
+          <t>www.scfriends.org</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -8340,28 +8648,28 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>St. Stephen's Episcopal School</t>
+          <t>Susquehanna Waldorf School - SO</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
-          <t>215 N. Front Street, Harrisburg, PA  17101</t>
+          <t>15 West Walnut St., Marietta, PA  17547</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>(717) 238-8590</t>
+          <t>(717) 649-1344</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>dshaffer@sseschool.org</t>
+          <t>deborah.duke@susquehanna.org</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>www.sseschool.org</t>
+          <t>www.susquehannawaldorf.org</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -8378,28 +8686,28 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>State College Friends School - SO</t>
+          <t>Talk Institute and School a/k/a Talk, Inc. - SO</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
         <is>
-          <t>1900 University Drive, State College, PA  16801</t>
+          <t>6 Campus Blvd., Newtown Square, PA  19073</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>(814) 237-8386</t>
+          <t>(610) 356-5566</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>jlove@scfriends.org</t>
+          <t>kristen.tabun@talkinc.org</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>www.scfriends.org</t>
+          <t>www.talkinc.org</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -8416,28 +8724,28 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Susquehanna Waldorf School - SO</t>
+          <t>The Baldwin School</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
-          <t>15 West Walnut St., Marietta, PA  17547</t>
+          <t>701 Montgomery Ave., Bryn Mawr, PA  19010</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>(717) 649-1344</t>
+          <t>(610) 525-2700</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>deborah.duke@susquehanna.org</t>
+          <t>brian.lorigan@baldwinschool.org</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>www.susquehannawaldorf.org</t>
+          <t>www.baldwinschool.org</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -8454,28 +8762,28 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Talk Institute and School a/k/a Talk, Inc. - SO</t>
+          <t>The Campus Laboratory School of Carlow University - SO</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
-          <t>6 Campus Blvd., Newtown Square, PA  19073</t>
+          <t>3333 Fifth Avenue, Pittsburgh, PA  15213</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>(610) 356-5566</t>
+          <t>(412) 578-2072</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>kristen.tabun@talkinc.org</t>
+          <t>hashroyer@carlow.edu</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>www.talkinc.org</t>
+          <t>www.camousschool.edu</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -8492,28 +8800,28 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>The Baldwin School</t>
+          <t>The Church Farm School</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
-          <t>701 Montgomery Ave., Bryn Mawr, PA  19010</t>
+          <t>1001 East Lincoln Highway, Exton, PA  19341</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>(610) 525-2700</t>
+          <t>(610) 363-5383</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>brian.lorigan@baldwinschool.org</t>
+          <t>advancement@gocfs.net</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>www.baldwinschool.org</t>
+          <t>www.gocfs.net</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -8530,28 +8838,28 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>The Campus Laboratory School of Carlow University - SO</t>
+          <t>The Concept School</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
-          <t>3333 Fifth Avenue, Pittsburgh, PA  15213</t>
+          <t>1120 E. Street Rd., Westtown, PA  19395</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>(412) 578-2072</t>
+          <t>(610) 399-1135</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>hashroyer@carlow.edu</t>
+          <t>slevine@theconceptschool.org</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>www.camousschool.edu</t>
+          <t>www.theconceptschool.org</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -8568,28 +8876,28 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>The Church Farm School</t>
+          <t>The Ellis School - SO</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr">
         <is>
-          <t>1001 East Lincoln Highway, Exton, PA  19341</t>
+          <t>6425 Fifth Avenue, Pittsburgh, PA  15206</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>(610) 363-5383</t>
+          <t>(412) 661-5992</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>advancement@gocfs.net</t>
+          <t>devereuxc@theellisschool.org</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>www.gocfs.net</t>
+          <t>www.theellisschool.org</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -8606,28 +8914,28 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>The Concept School</t>
+          <t>The Episcopal Academy</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr">
         <is>
-          <t>1120 E. Street Rd., Westtown, PA  19395</t>
+          <t>1785 Bishop White Drive, Newtown Square, PA  19073</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>(610) 399-1135</t>
+          <t>(484) 424-1424</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>slevine@theconceptschool.org</t>
+          <t>tfanning@episcopalacademy.org</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>www.theconceptschool.org</t>
+          <t>www.episcopalacademy.org</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -8644,28 +8952,28 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>The Ellis School - SO</t>
+          <t>The Glen Montessori School - SO</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
         <is>
-          <t>6425 Fifth Avenue, Pittsburgh, PA  15206</t>
+          <t>950 Perry Highway, Pittsburgh, PA  15237</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>(412) 661-5992</t>
+          <t>(412) 318-4885</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>devereuxc@theellisschool.org</t>
+          <t>jherrmann@glenmontessori.org</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>www.theellisschool.org</t>
+          <t>www.glenmontessori.org</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -8682,28 +8990,28 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>The Episcopal Academy</t>
+          <t>The Grayson School - SO</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr">
         <is>
-          <t>1785 Bishop White Drive, Newtown Square, PA  19073</t>
+          <t>211 Matsonford Rd., Radnor, PA  19008</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>(484) 424-1424</t>
+          <t>(484) 428-3241</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>tfanning@episcopalacademy.org</t>
+          <t>jnance@thegraysonschool.org</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>www.episcopalacademy.org</t>
+          <t>www.thegraysonschool.org</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -8720,28 +9028,28 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>The Glen Montessori School - SO</t>
+          <t>The Haverford School - SO</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
         <is>
-          <t>950 Perry Highway, Pittsburgh, PA  15237</t>
+          <t>450 Lancaster Avenue, Haverford, PA  19041</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>(412) 318-4885</t>
+          <t>(484) 417-2794</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>jherrmann@glenmontessori.org</t>
+          <t>mnierenberg@haverford.org</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>www.glenmontessori.org</t>
+          <t>www.haverford.org</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -8758,28 +9066,28 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>The Grayson School - SO</t>
+          <t>The Hill Top Preparatory School, Inc.</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
-          <t>211 Matsonford Rd., Radnor, PA  19008</t>
+          <t>737 S. Ithan Avenue, Bryn Mawr, PA  19010</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>(484) 428-3241</t>
+          <t>(610) 527-3230</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>jnance@thegraysonschool.org</t>
+          <t>jtremoglie@hilltopprep.org</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>www.thegraysonschool.org</t>
+          <t>www.hilltopprep.org</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -8796,28 +9104,28 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>The Haverford School - SO</t>
+          <t>The Hillside School</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
-          <t>450 Lancaster Avenue, Haverford, PA  19041</t>
+          <t>2697 Brookside Road, Macungie, PA  18062</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>(484) 417-2794</t>
+          <t>(610) 967-3701</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>mnierenberg@haverford.org</t>
+          <t>dkuntzman@hillsideschool.org</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>www.haverford.org</t>
+          <t>www.hillsideschool.org</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -8834,28 +9142,28 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>The Hill Top Preparatory School, Inc.</t>
+          <t>The Janus School</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
         <is>
-          <t>737 S. Ithan Avenue, Bryn Mawr, PA  19010</t>
+          <t>205 Lefever Road, Mount Joy, PA  17552</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>(610) 527-3230</t>
+          <t>(717) 653-0025</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>jtremoglie@hilltopprep.org</t>
+          <t>sshaffer@thejanusschool.org</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>www.hilltopprep.org</t>
+          <t>www.thejanusschool.org</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -8872,28 +9180,28 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>The Hillside School</t>
+          <t>The Joshua Group - SO</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2697 Brookside Road, Macungie, PA  18062</t>
+          <t>1442 Market St., Harrisburg, PA  17103</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>(610) 967-3701</t>
+          <t>(717) 236-4464</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>dkuntzman@hillsideschool.org</t>
+          <t>j.politis@joshuagrouphbg.org</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>www.hillsideschool.org</t>
+          <t>www.joshuagroup.org</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -8910,28 +9218,28 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>The Janus School</t>
+          <t>The Learning Lamp, Inc. - SO</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr">
         <is>
-          <t>205 Lefever Road, Mount Joy, PA  17552</t>
+          <t>2025 Bedford St., Johnstown, PA  15904</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>(717) 653-0025</t>
+          <t>(814) 262-0732</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>sshaffer@thejanusschool.org</t>
+          <t>lspangler@thelearninglamp.org</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>www.thejanusschool.org</t>
+          <t>www.thelearninglamp.org</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -8948,28 +9256,28 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>The Joshua Group - SO</t>
+          <t>The Neighborhood Academy - SO</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
-          <t>1442 Market St., Harrisburg, PA  17103</t>
+          <t>709 North Aiken Avenue, Pittsburgh, PA  15206</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>(717) 236-4464</t>
+          <t>(412) 365-5045</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>j.politis@joshuagrouphbg.org</t>
+          <t>jamie.donne@theneighborhoodacademy.org</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>www.joshuagroup.org</t>
+          <t>www.theneighborhoodacademy.org</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -8986,28 +9294,28 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>The Learning Lamp, Inc. - SO</t>
+          <t>The Phelps School</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025 Bedford St., Johnstown, PA  15904</t>
+          <t>583 Sugartown Road, Malvern, PA  19355</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>(814) 262-0732</t>
+          <t>(610) 644-1754</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>lspangler@thelearninglamp.org</t>
+          <t>sfahey@thephelpsschool.org</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>www.thelearninglamp.org</t>
+          <t>www.thephelpsschool.org</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -9024,28 +9332,28 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>The Neighborhood Academy - SO</t>
+          <t>The Samuel School - SO</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr">
         <is>
-          <t>709 North Aiken Avenue, Pittsburgh, PA  15206</t>
+          <t>510 Joyce Road, Camp Hill, PA  17011</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>(412) 365-5045</t>
+          <t>(717) 557-1119</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>jamie.donne@theneighborhoodacademy.org</t>
+          <t>rpeck@samuelschool.com</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>www.theneighborhoodacademy.org</t>
+          <t>www.samuelschool.com</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -9062,28 +9370,28 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>The Phelps School</t>
+          <t>The School in Rose Valley - SO</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr">
         <is>
-          <t>583 Sugartown Road, Malvern, PA  19355</t>
+          <t>20 School Lane, Rose Valley, PA  19063</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>(610) 644-1754</t>
+          <t>(610) 566-1088</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>sfahey@thephelpsschool.org</t>
+          <t>nava@theschoolinrosevalley.org</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>www.thephelpsschool.org</t>
+          <t>www.theschoolinrosevalley.org</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -9100,28 +9408,28 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>The Samuel School - SO</t>
+          <t>The Shipley School</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
-          <t>510 Joyce Road, Camp Hill, PA  17011</t>
+          <t>814 Yarrow Street, Bryn Mawr, PA  19010</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>(717) 557-1119</t>
+          <t>(610) 525-4300</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>rpeck@samuelschool.com</t>
+          <t>pdaly@shipleyschool.org</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>www.samuelschool.com</t>
+          <t>www.shipleyschool.org</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -9138,28 +9446,28 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>The School in Rose Valley - SO</t>
+          <t>The Swain School, Inc. - SO</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
-          <t>20 School Lane, Rose Valley, PA  19063</t>
+          <t>1100 S. 24th Street, Allentown, PA  18103</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>(610) 566-1088</t>
+          <t>(610) 332-5291</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>nava@theschoolinrosevalley.org</t>
+          <t>bzaiser@mamail.net</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>www.theschoolinrosevalley.org</t>
+          <t>www.moravianacademy.org</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -9176,28 +9484,28 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>The Shipley School</t>
+          <t>The Vista School - SO</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
-          <t>814 Yarrow Street, Bryn Mawr, PA  19010</t>
+          <t>1021 Springboard Drive, Hershey, PA  17033</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>(610) 525-4300</t>
+          <t>(717) 583-5102</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>pdaly@shipleyschool.org</t>
+          <t>communications@vistaautismservices.org</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>www.shipleyschool.org</t>
+          <t>www.thevistaschool.org</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -9214,28 +9522,28 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>The Swain School, Inc. - SO</t>
+          <t>Trinity Lutheran Church &amp; School - SO</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
-          <t>1100 S. 24th Street, Allentown, PA  18103</t>
+          <t>53 West Avenue, Wellsboro, PA  16901</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>(610) 332-5291</t>
+          <t>(570) 724-7723</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>bzaiser@mamail.net</t>
+          <t>bkohler@trinitylutheranwellsboro.org</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>www.moravianacademy.org</t>
+          <t>www.trinitylutheranwellsboro.org</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -9252,28 +9560,28 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>The Vista School - SO</t>
+          <t>United Disabilities Services</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
-          <t>1021 Springboard Drive, Hershey, PA  17033</t>
+          <t>2270 Erin Court, Lancaster, PA  17601</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>(717) 583-5102</t>
+          <t>(717) 715-8770</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>communications@vistaautismservices.org</t>
+          <t>elizabethb@udservices.org</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>www.thevistaschool.org</t>
+          <t>www.udservices.org/school</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -9290,28 +9598,28 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Trinity Lutheran Church &amp; School - SO</t>
+          <t>United Way of Lackawanna and Wayne Counties - SO</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
-          <t>53 West Avenue, Wellsboro, PA  16901</t>
+          <t>615 Jefferson Avenue, Scranton, PA  18510</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>(570) 724-7723</t>
+          <t>(570) 343-1267</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>bkohler@trinitylutheranwellsboro.org</t>
+          <t>abassani@uwlc.net</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>www.trinitylutheranwellsboro.org</t>
+          <t>www.uwlc.net</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -9328,28 +9636,28 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>United Disabilities Services</t>
+          <t>Upland Country Day School</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2270 Erin Court, Lancaster, PA  17601</t>
+          <t>420 West Street Road, Kennett Square, PA  19348</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>(717) 715-8770</t>
+          <t>(610) 444-8114</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>elizabethb@udservices.org</t>
+          <t>eswarter@uplandcds.org</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>www.udservices.org/school</t>
+          <t>www.uplandcds.org</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -9366,28 +9674,28 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>United Way of Lackawanna and Wayne Counties - SO</t>
+          <t>Valley School of Ligonier</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
-          <t>615 Jefferson Avenue, Scranton, PA  18510</t>
+          <t>P.O. Box 616, Ligonier, PA  15658</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>(570) 343-1267</t>
+          <t>(724) 238-5028</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>abassani@uwlc.net</t>
+          <t>development@valleyschoolofligonier.org</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>www.uwlc.net</t>
+          <t>www.valleyschoolofligonier.org</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -9404,28 +9712,28 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Upland Country Day School</t>
+          <t>Villa Joseph Marie High School</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
-          <t>420 West Street Road, Kennett Square, PA  19348</t>
+          <t>1180 Holland Road, Holland, PA  18966</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>(610) 444-8114</t>
+          <t>(215) 357-8810</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>eswarter@uplandcds.org</t>
+          <t>lharkrader@vjmhs.org</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>www.uplandcds.org</t>
+          <t>www.vjmhs.org</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -9442,28 +9750,28 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Valley School of Ligonier</t>
+          <t>Villa Maria Academy (Malvern)</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
-          <t>P.O. Box 616, Ligonier, PA  15658</t>
+          <t>370 Central Avenue, Malvern, PA  19355</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>(724) 238-5028</t>
+          <t>(610) 644-2551</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>development@valleyschoolofligonier.org</t>
+          <t>mlamb@vmahs.org</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>www.valleyschoolofligonier.org</t>
+          <t>www.vmahs.org</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -9480,28 +9788,28 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Villa Joseph Marie High School</t>
+          <t>Villa Maria Academy Lower School</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
-          <t>1180 Holland Road, Holland, PA  18966</t>
+          <t>280 IHM Drive, Malvern, PA  19355</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>(215) 357-8810</t>
+          <t>(610) 644-4864</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>lharkrader@vjmhs.org</t>
+          <t>pscanlon@villamaria.org</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>www.vjmhs.org</t>
+          <t>www.villamaria.org</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -9518,28 +9826,28 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Villa Maria Academy (Malvern)</t>
+          <t>Villa Maria Cathedral Preparatory Catholic School System</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
-          <t>370 Central Avenue, Malvern, PA  19355</t>
+          <t>250 West 10th Street, Erie, PA  16501</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>(610) 644-2551</t>
+          <t>(814) 453-7737</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>mlamb@vmahs.org</t>
+          <t>Joanne.Rogers@cathedralprep.com</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>www.vmahs.org</t>
+          <t>www.cathedralprep.com</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -9556,28 +9864,28 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Villa Maria Academy Lower School</t>
+          <t>Waldorf School of Pittsburgh</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
-          <t>280 IHM Drive, Malvern, PA  19355</t>
+          <t>201 S. Winebiddle Street, Pittsburgh, PA  15224</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>(610) 644-4864</t>
+          <t>(412) 441-5792</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>pscanlon@villamaria.org</t>
+          <t>dtaylor@waldorfpittsburgh.org</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>www.villamaria.org</t>
+          <t>www.waldorfpittsburgh.org</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -9594,28 +9902,28 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Villa Maria Cathedral Preparatory Catholic School System</t>
+          <t>Washington County Community Foundation - SO</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
-          <t>250 West 10th Street, Erie, PA  16501</t>
+          <t>1253 Route 519, P.O. Box 308, Eighty Four, PA  15330</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>(814) 453-7737</t>
+          <t>(724) 222-6330</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Joanne.Rogers@cathedralprep.com</t>
+          <t>scholar@wccf.net</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>www.cathedralprep.com</t>
+          <t>www.wccf.net</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -9632,28 +9940,28 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Waldorf School of Pittsburgh</t>
+          <t>Water Street Ministries - SO</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
-          <t>201 S. Winebiddle Street, Pittsburgh, PA  15224</t>
+          <t>P.O. Box 7267, Lancaster, PA  17604</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>(412) 441-5792</t>
+          <t>(717) 358-2084</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>dtaylor@waldorfpittsburgh.org</t>
+          <t>mwilcox@wsm.org</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>www.waldorfpittsburgh.org</t>
+          <t>www.wsm.org</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -9670,28 +9978,28 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Washington County Community Foundation - SO</t>
+          <t>Watson Institute - SO</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
-          <t>1253 Route 519, P.O. Box 308, Eighty Four, PA  15330</t>
+          <t>301 Camp Meeting Road, Sewickley, PA  15143</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>(724) 222-6330</t>
+          <t>(412) 749-2885</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>scholar@wccf.net</t>
+          <t>karam@thewatsoninstitute.org</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>www.wccf.net</t>
+          <t>www.thewatsoninstitute.org</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -9708,28 +10016,28 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Water Street Ministries - SO</t>
+          <t>West Chester Friends School - SO</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
-          <t>P.O. Box 7267, Lancaster, PA  17604</t>
+          <t>415 N. High Street, West Chester, PA  19380</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>(717) 358-2084</t>
+          <t>(610) 696-2615</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>mwilcox@wsm.org</t>
+          <t>smccardell@wcfriends.org</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>www.wsm.org</t>
+          <t>www.wcfriends.org</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -9746,28 +10054,28 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Watson Institute - SO</t>
+          <t>Western Pennsylvania Montessori School - SO</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
-          <t>301 Camp Meeting Road, Sewickley, PA  15143</t>
+          <t>2379 Wyland Ave., Allison Park, PA  15101</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>(412) 749-2885</t>
+          <t>(412) 487-2700</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>karam@thewatsoninstitute.org</t>
+          <t>director@wpms.edu</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>www.thewatsoninstitute.org</t>
+          <t>www.wpms.edu</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -9784,28 +10092,28 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>West Chester Friends School - SO</t>
+          <t>Westtown School</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
-          <t>415 N. High Street, West Chester, PA  19380</t>
+          <t>975 Westtown Road, West Chester, PA  19382</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>(610) 696-2615</t>
+          <t>(610) 399-7922</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>smccardell@wcfriends.org</t>
+          <t>courtnay.tyus@westtown.edu</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>www.wcfriends.org</t>
+          <t>www.westtown.edu</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -9822,28 +10130,28 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Western Pennsylvania Montessori School - SO</t>
+          <t>William Penn Charter School - SO</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2379 Wyland Ave., Allison Park, PA  15101</t>
+          <t>3000 West School House Lane, Philadelphia, PA  19144</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>(412) 487-2700</t>
+          <t>(215) 844-3460</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>director@wpms.edu</t>
+          <t>crahill@penncharter.com</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>www.wpms.edu</t>
+          <t>www.penncharter.com</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -9860,28 +10168,28 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Westtown School</t>
+          <t>Winchester Thurston School - SO</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
-          <t>975 Westtown Road, West Chester, PA  19382</t>
+          <t>555 Morewood Avenue, Pittsburgh, PA  15213</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>(610) 399-7922</t>
+          <t>(412) 578-3738</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>courtnay.tyus@westtown.edu</t>
+          <t>gaym@winchesterthurston.org</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>www.westtown.edu</t>
+          <t>www.winchesterthurston.org</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -9898,28 +10206,28 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>William Penn Charter School - SO</t>
+          <t>Wyoming Valley Children's Association - SO</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
-          <t>3000 West School House Lane, Philadelphia, PA  19144</t>
+          <t>1133 Wyoming Avenue, Forty Fort, PA  18704</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>(215) 844-3460</t>
+          <t>(570) 714-1246</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>crahill@penncharter.com</t>
+          <t>nzanon@wvcakids.org</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>www.penncharter.com</t>
+          <t>www.wvcakids.org</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -9936,28 +10244,28 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Winchester Thurston School - SO</t>
+          <t>Wyoming Valley Montessori Association, Inc. - SO</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
-          <t>555 Morewood Avenue, Pittsburgh, PA  15213</t>
+          <t>d/b/a Wyoming Valley Montessori School, 851 West Market Street, Kingston, PA  18704</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>(412) 578-3738</t>
+          <t>(570) 288-3708</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>gaym@winchesterthurston.org</t>
+          <t>cdecker@wvms.org</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>www.winchesterthurston.org</t>
+          <t>www.wvms.org</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -9974,28 +10282,28 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Wyoming Valley Children's Association - SO</t>
+          <t>Yeshiva Academy of Harrisburg Foundation</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
-          <t>1133 Wyoming Avenue, Forty Fort, PA  18704</t>
+          <t>d/b/a Silver Academy Foundation, 4218 Prosperous Drive, Harrisburg, PA  17112</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>(570) 714-1246</t>
+          <t>(717) 574-9121</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>nzanon@wvcakids.org</t>
+          <t>martinlowy@comcast.net</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>www.wvcakids.org</t>
+          <t>www.silveracademypa.org</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -10012,28 +10320,28 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Wyoming Valley Montessori Association, Inc. - SO</t>
+          <t>York College of Pennsylvania - SO</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
-          <t>d/b/a Wyoming Valley Montessori School, 851 West Market Street, Kingston, PA  18704</t>
+          <t>441 Country Club Road, York, PA  17403</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>(570) 288-3708</t>
+          <t>(717) 815-6711</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>cdecker@wvms.org</t>
+          <t>dkey1@ycds.org</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>www.wvms.org</t>
+          <t>www.ycds.org</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -10050,28 +10358,28 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Yeshiva Academy of Harrisburg Foundation</t>
+          <t>YSC Academy</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
-          <t>d/b/a Silver Academy Foundation, 4218 Prosperous Drive, Harrisburg, PA  17112</t>
+          <t>2501 Seaport Drive, Union Power Plant, River Front Suite No. 100, Chester, PA  19013</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>(717) 574-9121</t>
+          <t>(610) 722-0500</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>martinlowy@comcast.net</t>
+          <t>gokupniarek@strikerpartners.com</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>www.silveracademypa.org</t>
+          <t>www.yscacademy.com</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -10083,76 +10391,44 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>RI</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>York College of Pennsylvania - SO</t>
+          <t>Scholarship Organization</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>441 Country Club Road, York, PA  17403</t>
-        </is>
-      </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>(717) 815-6711</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>dkey1@ycds.org</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>www.ycds.org</t>
-        </is>
-      </c>
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="inlineStr"/>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr"/>
       <c r="H296" t="inlineStr">
         <is>
-          <t>https://dced.pa.gov/wp-content/themes/business2015/csv/eitc_so_list.csv</t>
+          <t>https://tax.ri.gov/sites/g/files/xkgbur541/files/2025-07/Tax%20Credits%20for%20Contributions%20to%20Scholarship%20Organizations%20June%2030%20SGO%20List%20for%202025.pdf</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>RI</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>YSC Academy</t>
+          <t>Achievement for Children with Challenges Empowered by School Scholarships (ACCESS)</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>2501 Seaport Drive, Union Power Plant, River Front Suite No. 100, Chester, PA  19013</t>
-        </is>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>(610) 722-0500</t>
-        </is>
-      </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>gokupniarek@strikerpartners.com</t>
-        </is>
-      </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>www.yscacademy.com</t>
-        </is>
-      </c>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="inlineStr"/>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr"/>
       <c r="H297" t="inlineStr">
         <is>
-          <t>https://dced.pa.gov/wp-content/themes/business2015/csv/eitc_so_list.csv</t>
+          <t>https://tax.ri.gov/sites/g/files/xkgbur541/files/2025-07/Tax%20Credits%20for%20Contributions%20to%20Scholarship%20Organizations%20June%2030%20SGO%20List%20for%202025.pdf</t>
         </is>
       </c>
     </row>
@@ -10164,7 +10440,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Achievement for Children with Challenges Empowered by School Scholarships (ACCESS)</t>
+          <t>Children's Tuition Fund of Rhode Island</t>
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
@@ -10186,7 +10462,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Children's Tuition Fund of Rhode Island</t>
+          <t>F.A.C.E. of Rhode Island</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
@@ -10208,7 +10484,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>F.A.C.E. of Rhode Island</t>
+          <t>Scholarships to Economically Poor Students (STEPS)</t>
         </is>
       </c>
       <c r="C300" t="inlineStr"/>
@@ -10230,7 +10506,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Scholarships to Economically Poor Students (STEPS)</t>
+          <t>Star Scholars Opportunity Program</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
@@ -10252,7 +10528,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Star Scholars Opportunity Program</t>
+          <t>Teach Initiative</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
@@ -10274,7 +10550,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Teach Initiative</t>
+          <t>The Foundation for Rhode Island Day Schools</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
@@ -10291,12 +10567,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>RI</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>The Foundation for Rhode Island Day Schools</t>
+          <t>South Dakota Partners in Education</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
@@ -10306,28 +10582,6 @@
       <c r="G304" t="inlineStr"/>
       <c r="H304" t="inlineStr">
         <is>
-          <t>https://tax.ri.gov/sites/g/files/xkgbur541/files/2025-07/Tax%20Credits%20for%20Contributions%20to%20Scholarship%20Organizations%20June%2030%20SGO%20List%20for%202025.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>South Dakota Partners in Education</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr"/>
-      <c r="D305" t="inlineStr"/>
-      <c r="E305" t="inlineStr"/>
-      <c r="F305" t="inlineStr"/>
-      <c r="G305" t="inlineStr"/>
-      <c r="H305" t="inlineStr">
-        <is>
           <t>https://dlr.sd.gov/insurance/tax_credit_program/documents/sgo_participation_list.pdf</t>
         </is>
       </c>

--- a/sgo_lists.xlsx
+++ b/sgo_lists.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H356"/>
+  <dimension ref="A1:H355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -498,7 +498,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Scholarships for Kids, Inc.</t>
+          <t>Scholarships for Kids Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -542,7 +542,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Renaissance Scholarships, Inc.</t>
+          <t>Renaissance Scholarships Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -564,7 +564,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C2 Opportunity Scholarships, LLC</t>
+          <t>C2 Opportunity Scholarships LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rocket City Scholarship Granting Organization, Inc.</t>
+          <t>Rocket City Scholarship Granting Organization Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -630,7 +630,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Academics Plus Opportunity Scholarship Fund, LLC</t>
+          <t>Academics Plus Opportunity Scholarship Fund LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -674,7 +674,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AAA Scholarship Foundation, Inc.</t>
+          <t>AAA Scholarship Foundation Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -718,7 +718,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Beacons of Hope, Inc.</t>
+          <t>Beacons of Hope Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Arizona Private Education Scholarship Fund,</t>
+          <t>Arizona Private Education Scholarship Fund</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -886,7 +886,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A.A.A. Scholarship Foundation- FL, LLC</t>
+          <t>A.A.A. Scholarship Foundation- FL LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A A A Scholarship Foundation, Inc.</t>
+          <t>A A A Scholarship Foundation Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Georgia Student Scholarship Organization, Inc.</t>
+          <t>Georgia Student Scholarship Organization Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Georgia Tax Credit Scholarship Program, Inc.</t>
+          <t>Georgia Tax Credit Scholarship Program Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Golden Dome Scholarship Fund, Inc.</t>
+          <t>Golden Dome Scholarship Fund Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GRACE Scholars, Inc.</t>
+          <t>GRACE Scholars Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GREAT SSO, Inc.</t>
+          <t>GREAT SSO Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A Pay It Forward Scholarship, Inc.</t>
+          <t>A Pay It Forward Scholarship Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Georgia Tuition Assistance Program, Inc.</t>
+          <t>The Georgia Tuition Assistance Program Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Lutheran Scholarship Granting Organization of Indiana, Inc.</t>
+          <t>The Lutheran Scholarship Granting Organization of Indiana Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ACE Scholarships SGO, Kansas LLC</t>
+          <t>ACE Scholarships SGO Kansas LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Christian Faith Centre, Inc.</t>
+          <t>Christian Faith Centre Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kansas Lutheran Schools Scholarship Foundation, Inc.</t>
+          <t>Kansas Lutheran Schools Scholarship Foundation Inc.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Scholarships for Catholic Schools, Inc.</t>
+          <t>Scholarships for Catholic Schools Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Support for Catholic Schools, Inc.</t>
+          <t>Support for Catholic Schools Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ACE Scholarships SSO, Montana, LLC</t>
+          <t>ACE Scholarships SSO Montana LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Saint Matthew Parish Series 535, LLC</t>
+          <t>Saint Matthew Parish Series 535 LLC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Headwaters Academy, Inc.</t>
+          <t>The Headwaters Academy Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>The Summit Lighthouse, Inc.</t>
+          <t>The Summit Lighthouse Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -2577,34 +2577,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>AAA Scholarship Foundation-NV, LLC</t>
+          <t>The Children’s Scholarship Fund</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>1452 W. Horizon Ridge Road, #541, Henderson NV 89012</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>(888)707-2465</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>kim@aaascholarships.org</t>
-        </is>
-      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://webapp-strapi-paas-prod-nde-001.azurewebsites.net/uploads/Registered_Scholarship_Organizations_af21ccf71e.pdf</t>
+          <t>https://www.revenue.nh.gov/sites/g/files/ehbemt736/files/documents/scholarship-organizations-approved-2025-2026.pdf</t>
         </is>
       </c>
     </row>
@@ -2616,23 +2604,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>America’s Scholarship Konnection</t>
+          <t>AAA Scholarship Foundation-NV LLC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>24 W. Camelback Road Suite A 535,Phoenix, AZ 85013</t>
+          <t>1452 W. Horizon Ridge Road, #541, Henderson NV 89012</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>(866)622-4ASK</t>
+          <t>(888)707-2465</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>info@ASKscholarships.org</t>
+          <t>kim@aaascholarships.org</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -2650,23 +2638,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Silver State Scholarships</t>
+          <t>America’s Scholarship Konnection</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>6655 W. Sahara Ave. #D106 Las Vegas, NV 89146</t>
+          <t>24 W. Camelback Road Suite A 535,Phoenix, AZ 85013</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>(702)736-7787</t>
+          <t>(866)622-4ASK</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>scholarships@silverstatescholarships.org</t>
+          <t>info@ASKscholarships.org</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -2684,23 +2672,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Education Fund of Northern Nevada</t>
+          <t>Silver State Scholarships</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>3025 Mill Street, Reno, NV 89509</t>
+          <t>6655 W. Sahara Ave. #D106 Las Vegas, NV 89146</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>(775)742-4285</t>
+          <t>(702)736-7787</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>efnninfo@gmail.com</t>
+          <t>scholarships@silverstatescholarships.org</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -2718,23 +2706,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Student Choice Fund of Nevada</t>
+          <t>Education Fund of Northern Nevada</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>1755 Village Center Circle studentchoicefundofnevada.org</t>
+          <t>3025 Mill Street, Reno, NV 89509</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>(702)410-8143</t>
+          <t>(775)742-4285</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Studentchoicefundofnevada@gmail.com</t>
+          <t>efnninfo@gmail.com</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -2747,44 +2735,64 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>The Children’s Scholarship Fund</t>
+          <t>Student Choice Fund of Nevada</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1755 Village Center Circle studentchoicefundofnevada.org</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>(702)410-8143</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Studentchoicefundofnevada@gmail.com</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.revenue.nh.gov/sites/g/files/ehbemt736/files/documents/scholarship-organizations-approved-2025-2026.pdf</t>
+          <t>https://webapp-strapi-paas-prod-nde-001.azurewebsites.net/uploads/Registered_Scholarship_Organizations_af21ccf71e.pdf</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Children’s Scholarship Fund</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
+          <t>ABC Ohio Foundation</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>33-2382950</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>351 Aurora Street, Hudson, Ohio 44236</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.revenue.nh.gov/sites/g/files/ehbemt736/files/documents/scholarship-organizations-approved-2025-2026.pdf</t>
+          <t>https://charitable.ohioago.gov/Scholarship-Granting-Organization-Certification/List</t>
         </is>
       </c>
     </row>
@@ -2796,17 +2804,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ABC Ohio Foundation</t>
+          <t>American Scholarship Network</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>33-2382950</t>
+          <t>42-1945763</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>351 Aurora Street, Hudson, Ohio 44236</t>
+          <t>4456 N Abbe Rd #305, Sheffield Village, Ohio 44054</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -2826,17 +2834,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>American Scholarship Network</t>
+          <t>Aurora City Schools Scholarship Granting Organization</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>42-1945763</t>
+          <t>41-2906278</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>4456 N Abbe Rd #305, Sheffield Village, Ohio 44054</t>
+          <t>PO Box 109, Aurora, Ohio 44202</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -2856,17 +2864,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Aurora City Schools Scholarship Granting Organization</t>
+          <t>Buckeye Christian School Organization</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>41-2906278</t>
+          <t>34-1417866</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>PO Box 109, Aurora, Ohio 44202</t>
+          <t>2400 Chandlersville Rd, Zanesville, Ohio 43056</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -2886,17 +2894,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Buckeye Christian School Organization</t>
+          <t>Chaminade Julienne Catholic Education Fund</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>34-1417866</t>
+          <t>99-1384296</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2400 Chandlersville Rd, Zanesville, Ohio 43056</t>
+          <t>505 S Ludlow St, Dayton, Ohio 45402</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -2916,17 +2924,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Chaminade Julienne Catholic Education Fund</t>
+          <t>CISE-SGO</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>99-1384296</t>
+          <t>88-3142134</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>505 S Ludlow St, Dayton, Ohio 45402</t>
+          <t>100 E. 8th Street, Cincinnati, Ohio 45202</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -2946,17 +2954,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CISE-SGO</t>
+          <t>Give For Kids Scholarship Fund</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>88-3142134</t>
+          <t>39-4236057</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>100 E. 8th Street, Cincinnati, Ohio 45202</t>
+          <t>4334 BAINTREE RD, University Heights, Ohio 44118</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -2976,17 +2984,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Give For Kids Scholarship Fund</t>
+          <t>Heights Tax Credit SGO</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>39-4236057</t>
+          <t>41-4353004</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>4334 BAINTREE RD, University Heights, Ohio 44118</t>
+          <t>260 Fenwick Road, University Heights, Ohio 44118</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -3006,17 +3014,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Heights Tax Credit SGO</t>
+          <t>Julie Billiart Network Scholarship Granting Organization</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>41-4353004</t>
+          <t>33-1279122</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>260 Fenwick Road, University Heights, Ohio 44118</t>
+          <t>6140 Parkland Blvd, Ste. 300, Mayfield Heights, Ohio 44124</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -3036,17 +3044,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Julie Billiart Network Scholarship Granting Organization</t>
+          <t>Lutheran Scholarship Granting Organization of Ohio</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>33-1279122</t>
+          <t>87-3374872</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>6140 Parkland Blvd, Ste. 300, Mayfield Heights, Ohio 44124</t>
+          <t>3870 Linden Rd, Rocky River, Ohio 44116</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -3066,17 +3074,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Lutheran Scholarship Granting Organization of Ohio</t>
+          <t>Mount Notre Dame SGO</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>87-3374872</t>
+          <t>92-3287314</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>3870 Linden Rd, Rocky River, Ohio 44116</t>
+          <t>711 E. Columbia Avenue, CINCINNATI, Ohio 45215</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -3096,17 +3104,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Mount Notre Dame SGO</t>
+          <t>Mustard Seed Education Foundation</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>92-3287314</t>
+          <t>83-1341078</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>711 E. Columbia Avenue, CINCINNATI, Ohio 45215</t>
+          <t>43 S. HURON ST., TOLEDO, Ohio 43604</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -3126,17 +3134,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Mustard Seed Education Foundation</t>
+          <t>Nordonia Hills Schools Scholarship Granting Organization</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>83-1341078</t>
+          <t>92-2756655</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>43 S. HURON ST., TOLEDO, Ohio 43604</t>
+          <t>219 W AURORA RD STE A, NORTHFIELD, Ohio 44067</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -3156,17 +3164,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nordonia Hills Schools Scholarship Granting Organization</t>
+          <t>Notre Dame Academy Foundation</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>92-2756655</t>
+          <t>82-3446307</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>219 W AURORA RD STE A, NORTHFIELD, Ohio 44067</t>
+          <t>3535 W. Sylvania Avenue, Toledo, Ohio 43623</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -3186,17 +3194,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Notre Dame Academy Foundation</t>
+          <t>Notre Dame Schools Scholarship Granting Organization</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>82-3446307</t>
+          <t>88-1481999</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>3535 W. Sylvania Avenue, Toledo, Ohio 43623</t>
+          <t>13000 Auburn Road, Chardon, Ohio 44024</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -3216,17 +3224,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Notre Dame Schools Scholarship Granting Organization</t>
+          <t>Ohio Association of Independent Schools Scholarship Granting Organizations</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>88-1481999</t>
+          <t>87-4616853</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>13000 Auburn Road, Chardon, Ohio 44024</t>
+          <t>P.O. Box 492, Granville, Ohio 43023</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -3246,17 +3254,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ohio Association of Independent Schools Scholarship Granting Organizations</t>
+          <t>Saint Joseph Academy Scholarship Granting Organization</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>87-4616853</t>
+          <t>92-1890302</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>P.O. Box 492, Granville, Ohio 43023</t>
+          <t>3470 Rocky River Drive, Cleveland, Ohio 44111</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -3276,17 +3284,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Saint Joseph Academy Scholarship Granting Organization</t>
+          <t>Saint Ursula Academy Foundation Inc.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>92-1890302</t>
+          <t>34-1886759</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>3470 Rocky River Drive, Cleveland, Ohio 44111</t>
+          <t>4025 Indian Road, Toledo, Ohio 43606</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -3306,17 +3314,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Saint Ursula Academy Foundation, Inc.</t>
+          <t>Seton Cincinnati SGO</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>34-1886759</t>
+          <t>92-2429826</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>4025 Indian Road, Toledo, Ohio 43606</t>
+          <t>3901 Glenway Avenue, Cincinnati, Ohio 45205</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
@@ -3336,17 +3344,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Seton Cincinnati SGO</t>
+          <t>SMDPHS Scholarship Granting Organization</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>92-2429826</t>
+          <t>93-1632132</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>3901 Glenway Avenue, Cincinnati, Ohio 45205</t>
+          <t>6202 St. Clair, CLEVELAND, Ohio 44103</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -3366,17 +3374,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SMDPHS Scholarship Granting Organization</t>
+          <t>St. Francis de Sales High School Foundation</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>93-1632132</t>
+          <t>34-1696266</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>6202 St. Clair, CLEVELAND, Ohio 44103</t>
+          <t>2323 W Bancroft St, Toledo, Ohio 43607</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -3396,17 +3404,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>St. Francis de Sales High School Foundation</t>
+          <t>The Scholarship Granting Organization Of The Catholic Community Foundation</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>34-1696266</t>
+          <t>87-3652751</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2323 W Bancroft St, Toledo, Ohio 43607</t>
+          <t>1404 East 9th Street, Cleveland, Ohio 44114</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -3426,17 +3434,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>The Scholarship Granting Organization Of The Catholic Community Foundation</t>
+          <t>The St Johns Jesuit Scholarship Granting Organization</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>87-3652751</t>
+          <t>92-2707224</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>1404 East 9th Street, Cleveland, Ohio 44114</t>
+          <t>5901 Airport Hwy, Toledo, Ohio 43615</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -3456,17 +3464,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>The St Johns Jesuit Scholarship Granting Organization</t>
+          <t>Ursuline Foundation</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>92-2707224</t>
+          <t>31-1233054</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>5901 Airport Hwy, Toledo, Ohio 43615</t>
+          <t>5535 Pfeiffer Road, Cincinnati, Ohio 45242</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -3486,17 +3494,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ursuline Foundation</t>
+          <t>Waldorf Method Education Scholarship Association</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>31-1233054</t>
+          <t>93-3579746</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>5535 Pfeiffer Road, Cincinnati, Ohio 45242</t>
+          <t>76 Charleston Ave., Columbus, Ohio 43214</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -3511,30 +3519,38 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Waldorf Method Education Scholarship Association</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>93-3579746</t>
-        </is>
-      </c>
+          <t>Academy in Manayunk d/b/a AIM Academy</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>76 Charleston Ave., Columbus, Ohio 43214</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+          <t>1200 River Road, Conshohocken, PA  19428</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>(215) 483-2461</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>development@aimpa.org</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>www.aimpa.org</t>
+        </is>
+      </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://charitable.ohioago.gov/Scholarship-Granting-Organization-Certification/List</t>
+          <t>https://dced.pa.gov/wp-content/themes/business2015/csv/eitc_so_list.csv</t>
         </is>
       </c>
     </row>
@@ -3546,28 +3562,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Academy in Manayunk d/b/a AIM Academy</t>
+          <t>Academy of Notre Dame de Namur</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>1200 River Road, Conshohocken, PA  19428</t>
+          <t>560 Sproul Road, Villanova, PA  19085</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>(215) 483-2461</t>
+          <t>(610) 971-1630</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>development@aimpa.org</t>
+          <t>Tkyle@ndapa.org</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>www.aimpa.org</t>
+          <t>www.ndapa.org</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -3584,28 +3600,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Academy of Notre Dame de Namur</t>
+          <t>ACSI Children's Education Fund d/b/a Children's Tuition Fund of Pennsylvania</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>560 Sproul Road, Villanova, PA  19085</t>
+          <t>P.O. Box 62249, Colorado Springs, CO  80962</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>(610) 971-1630</t>
+          <t>(717) 285-3022</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tkyle@ndapa.org</t>
+          <t>Saralee_lenhart@acsi.org</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>www.ndapa.org</t>
+          <t>www.childrenstuitionfund.org</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -3622,28 +3638,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ACSI Children's Education Fund d/b/a Children's Tuition Fund of Pennsylvania</t>
+          <t>Agnes Irwin School</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>P.O. Box 62249, Colorado Springs, CO  80962</t>
+          <t>275 S. Ithan Ave., Bryn Mawr, PA  19010</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>(717) 285-3022</t>
+          <t>(610) 801-1260</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Saralee_lenhart@acsi.org</t>
+          <t>erauch@agnesirwin.org</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>www.childrenstuitionfund.org</t>
+          <t>www.agnesirwin.org</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -3660,28 +3676,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Agnes Irwin School</t>
+          <t>Aquinas Academy</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>275 S. Ithan Ave., Bryn Mawr, PA  19010</t>
+          <t>2308 West Hardies Road, Gibsonia, PA  15044</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>(610) 801-1260</t>
+          <t>(724) 444-0722</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>erauch@agnesirwin.org</t>
+          <t>leonard@aquinasacademy-pittsburgh.org</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>www.agnesirwin.org</t>
+          <t>www.aquinasacademy-pittsburgh.org</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -3698,28 +3714,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Aquinas Academy</t>
+          <t>Armstrong County Community Foundation</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2308 West Hardies Road, Gibsonia, PA  15044</t>
+          <t>220 S. Jefferson Street, Suite B, Kittanning, PA  16201</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>(724) 444-0722</t>
+          <t>(724) 548-5897</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>leonard@aquinasacademy-pittsburgh.org</t>
+          <t>jodi@servingtheheart.org</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>www.aquinasacademy-pittsburgh.org</t>
+          <t>www.servingtheheart.org</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -3736,28 +3752,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Armstrong County Community Foundation</t>
+          <t>Athletic Club of Fairhill Inc.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>220 S. Jefferson Street, Suite B, Kittanning, PA  16201</t>
+          <t>1205 E. Columbia Ave., Philadelphia, PA  19125</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>(724) 548-5897</t>
+          <t>(267) 908-9166</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>jodi@servingtheheart.org</t>
+          <t>acfairhill@gmail.com</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>www.servingtheheart.org</t>
+          <t>www.acfairhilll.com</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -3774,28 +3790,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Athletic Club of Fairhill Inc.</t>
+          <t>Benchmark School</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>1205 E. Columbia Ave., Philadelphia, PA  19125</t>
+          <t>2107 N. Providence Road, Media, PA  19063</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>(267) 908-9166</t>
+          <t>(610) 565-3741</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>acfairhill@gmail.com</t>
+          <t>joemcpeak@benchmarkschool.org</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>www.acfairhilll.com</t>
+          <t>www.benchmarkschool.org</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -3812,28 +3828,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Benchmark School</t>
+          <t>Berks County Community Foundation</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2107 N. Providence Road, Media, PA  19063</t>
+          <t>237 Court Street, Reading, PA  19601</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>(610) 565-3741</t>
+          <t>(610) 685-2223</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>joemcpeak@benchmarkschool.org</t>
+          <t>frankia@bccf.org</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>www.benchmarkschool.org</t>
+          <t>www.bccf.org</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -3850,28 +3866,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Berks County Community Foundation</t>
+          <t>Bridge Educational Foundation</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>237 Court Street, Reading, PA  19601</t>
+          <t>909 Green Street, Harrisburg, PA  17102</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>(610) 685-2223</t>
+          <t>(717) 214-6792</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>frankia@bccf.org</t>
+          <t>natalie.nutt@bridgeedu.org</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>www.bccf.org</t>
+          <t>www.bridgeedu.org</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -3888,28 +3904,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Bridge Educational Foundation</t>
+          <t>Bryn Athyn Church of the New Jerusalem</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>909 Green Street, Harrisburg, PA  17102</t>
+          <t>600 Tomlinson Rd., PO Box 277, Bryn Athyn, PA  19009</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>(717) 214-6792</t>
+          <t>(215) 544-1407</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>natalie.nutt@bridgeedu.org</t>
+          <t>Fauve.Nash@brynathynchurch.org</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>www.bridgeedu.org</t>
+          <t>www.brynathynchurch.org</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -3926,28 +3942,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Bryn Athyn Church of the New Jerusalem</t>
+          <t>Buckingham Friends School</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>600 Tomlinson Rd., PO Box 277, Bryn Athyn, PA  19009</t>
+          <t>5684 York Road, Lahaska, PA  18931</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>(215) 544-1407</t>
+          <t>(215) 794-7496</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Fauve.Nash@brynathynchurch.org</t>
+          <t>sfrenkel@bfs.org</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>www.brynathynchurch.org</t>
+          <t>www.bfs.org</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -3964,28 +3980,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Buckingham Friends School</t>
+          <t>Business Leadership Organized for Catholic Schools (BLOCS)</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>5684 York Road, Lahaska, PA  18931</t>
+          <t>Croton Road Corporate Center, 555 Croton Road, Suite 310, King of Prussia, PA  19406</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>(215) 794-7496</t>
+          <t>(484) 704-2307</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>sfrenkel@bfs.org</t>
+          <t>kharvey@blocs.org</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>www.bfs.org</t>
+          <t>www.blocs.org</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -4002,28 +4018,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Business Leadership Organized for Catholic Schools (BLOCS)</t>
+          <t>Buxmont Academy</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Croton Road Corporate Center, 555 Croton Road, Suite 310, King of Prussia, PA  19406</t>
+          <t>531 Main Street, Bethlehem, PA  18018</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>(484) 704-2307</t>
+          <t>(215) 534-5215</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>kharvey@blocs.org</t>
+          <t>mdeantonio@csfbuxmont.org</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>www.blocs.org</t>
+          <t>www.csfbuxmont.org</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -4040,28 +4056,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Buxmont Academy</t>
+          <t>Byerschool Foundation</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>531 Main Street, Bethlehem, PA  18018</t>
+          <t>1911 Arch Street, Philadelphia, PA  19103</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>(215) 534-5215</t>
+          <t>(215) 772-3053</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>mdeantonio@csfbuxmont.org</t>
+          <t>rgelb@byerschool.org</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>www.csfbuxmont.org</t>
+          <t>www.byerschool.org</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -4078,28 +4094,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Byerschool Foundation</t>
+          <t>C.B. Community Schools</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>1911 Arch Street, Philadelphia, PA  19103</t>
+          <t>4101 Freeland Avenue, Philadelphia, PA  19128</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>(215) 772-3053</t>
+          <t>(267) 766-3130</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>rgelb@byerschool.org</t>
+          <t>mmccrea@cbcommunityschools.org</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>www.byerschool.org</t>
+          <t>www.communityschools.org</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -4116,28 +4132,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>C.B. Community Schools</t>
+          <t>Calvary Christian Academy</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>4101 Freeland Avenue, Philadelphia, PA  19128</t>
+          <t>13500 Philmont Avenue, Philadelphia, PA  19116</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>(267) 766-3130</t>
+          <t>(215) 969-1579</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>mmccrea@cbcommunityschools.org</t>
+          <t>Mpennisi@ccphilly.org</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>www.communityschools.org</t>
+          <t>www.cca.ccphilly.org</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -4154,28 +4170,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Calvary Christian Academy</t>
+          <t>Camphill Special School Inc.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>13500 Philmont Avenue, Philadelphia, PA  19116</t>
+          <t>1784 Fairview Road, Glenmoore, PA  19343</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>(215) 969-1579</t>
+          <t>(610) 469-9236</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mpennisi@ccphilly.org</t>
+          <t>cripple@camphillschool.org</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>www.cca.ccphilly.org</t>
+          <t>www.camphillschool.org/</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -4192,28 +4208,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Camphill Special School, Inc.</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>1784 Fairview Road, Glenmoore, PA  19343</t>
+          <t>Carnegie Mellon Children's School, 5000 Forbes Avenue, MMC-17, Pittsburgh, PA  15213</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>(610) 469-9236</t>
+          <t>(412) 268-2198</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>cripple@camphillschool.org</t>
+          <t>lh37@andrew.cmu.edu</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>www.camphillschool.org/</t>
+          <t>www.cmu.edu/dietrich/psychology/cs/index.html</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -4230,28 +4246,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Carroll Patriot Educational Fund</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Carnegie Mellon Children's School, 5000 Forbes Avenue, MMC-17, Pittsburgh, PA  15213</t>
+          <t>Archbishop Carroll High School, 211 Matsonford Road, Radnor, PA  19087</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>(412) 268-2198</t>
+          <t>(267) 838-3462</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>lh37@andrew.cmu.edu</t>
+          <t>cokeefe@jcarroll.org</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>www.cmu.edu/dietrich/psychology/cs/index.html</t>
+          <t>www.jcarroll.org</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -4268,28 +4284,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Carroll Patriot Educational Fund</t>
+          <t>Center School</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Archbishop Carroll High School, 211 Matsonford Road, Radnor, PA  19087</t>
+          <t>2450 Hamilton Avenue, Abington, PA  19001</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>(267) 838-3462</t>
+          <t>(215) 657-2200</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>cokeefe@jcarroll.org</t>
+          <t>jbean@centerschoolpa.org</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>www.jcarroll.org</t>
+          <t>www.centerschoolpa.org</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -4306,28 +4322,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Center School</t>
+          <t>Central Pennsylvania Scholarship Fund</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2450 Hamilton Avenue, Abington, PA  19001</t>
+          <t>501 3rd Street, Tyrone, PA  16686</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>(215) 657-2200</t>
+          <t>(814) 942-4406</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>jbean@centerschoolpa.org</t>
+          <t>tami@cpsfcharity.org</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>www.centerschoolpa.org</t>
+          <t>www.pennsylvaniaeitc.org</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -4344,30 +4360,26 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Central Pennsylvania Scholarship Fund</t>
+          <t>Chabad Jewish Scholarship Foundation</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>501 3rd Street, Tyrone, PA  16686</t>
+          <t>1311 Fort Washington Ave., Fort Washington, PA  19034</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>(814) 942-4406</t>
+          <t>(215) 591-9310</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>tami@cpsfcharity.org</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>www.pennsylvaniaeitc.org</t>
-        </is>
-      </c>
+          <t>devorah@jewishmc.com</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
           <t>https://dced.pa.gov/wp-content/themes/business2015/csv/eitc_so_list.csv</t>
@@ -4382,26 +4394,30 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Chabad Jewish Scholarship Foundation</t>
+          <t>Children First America Delaware County</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>1311 Fort Washington Ave., Fort Washington, PA  19034</t>
+          <t>1005 W. 7th Street, Chester, PA  19013</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>(215) 591-9310</t>
+          <t>(610) 872-7472</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>devorah@jewishmc.com</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr"/>
+          <t>cfadelawareco@aol.com</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>www.cfadelco.org</t>
+        </is>
+      </c>
       <c r="H139" t="inlineStr">
         <is>
           <t>https://dced.pa.gov/wp-content/themes/business2015/csv/eitc_so_list.csv</t>
@@ -4416,28 +4432,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Children First America Delaware County</t>
+          <t>Children's Scholarship Fund of Pennsylvania</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>1005 W. 7th Street, Chester, PA  19013</t>
+          <t>633 Mayfield Road, Clarion, PA  16214</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>(610) 872-7472</t>
+          <t>(814) 226-4160</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>cfadelawareco@aol.com</t>
+          <t>mbauer@kriebelgas.com</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>www.cfadelco.org</t>
+          <t>www.csfofpa.org</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -4454,28 +4470,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Children's Scholarship Fund of Pennsylvania</t>
+          <t>Children's Scholarship Fund Philadelphia</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>633 Mayfield Road, Clarion, PA  16214</t>
+          <t>1500 Walnut Street, Suite 1300, Philadelphia, PA  19102</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>(814) 226-4160</t>
+          <t>(215) 670-8411</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>mbauer@kriebelgas.com</t>
+          <t>mstaples@csfphiladelphia.org</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>www.csfofpa.org</t>
+          <t>www.csfphiladelphia.org</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -4492,28 +4508,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Children's Scholarship Fund Philadelphia</t>
+          <t>Christian School Association of Greater Harrisburg Inc.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>1500 Walnut Street, Suite 1300, Philadelphia, PA  19102</t>
+          <t>2000 Blue Mountain Parkway, Harrisburg, PA  17112</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>(215) 670-8411</t>
+          <t>(717) 982-2839</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>mstaples@csfphiladelphia.org</t>
+          <t>daniel.king@csagh.org</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>www.csfphiladelphia.org</t>
+          <t>www.csagh.org</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -4530,28 +4546,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Christian School Association of Greater Harrisburg, Inc.</t>
+          <t>Christian School Association of York</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2000 Blue Mountain Parkway, Harrisburg, PA  17112</t>
+          <t>907 Greenbriar Rd., York, PA  17404</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>(717) 982-2839</t>
+          <t>(717) 767-6842</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>daniel.king@csagh.org</t>
+          <t>aallen@csyonline.com</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>www.csagh.org</t>
+          <t>www.csyonline.com</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -4568,28 +4584,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Christian School Association of York</t>
+          <t>Commonwealth Charitable Management Inc.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>907 Greenbriar Rd., York, PA  17404</t>
+          <t>270 Lake Avenue, Montrose, PA  18801</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>(717) 767-6842</t>
+          <t>(570) 278-3800</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>aallen@csyonline.com</t>
+          <t>cclayton@commonwealthcharitable.org</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>www.csyonline.com</t>
+          <t>www.commonwealthcharitable.org</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -4606,28 +4622,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Commonwealth Charitable Management, Inc.</t>
+          <t>Community Country Day School</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>270 Lake Avenue, Montrose, PA  18801</t>
+          <t>5800 Old Zuck Road, Erie, PA  16506</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>(570) 278-3800</t>
+          <t>(814) 833-7933</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>cclayton@commonwealthcharitable.org</t>
+          <t>angelacollins@ccdserie.com</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>www.commonwealthcharitable.org</t>
+          <t>www.ccdserie.com</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -4644,28 +4660,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Community Country Day School</t>
+          <t>Community Foundation of Fayette County</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>5800 Old Zuck Road, Erie, PA  16506</t>
+          <t>250 West Main Street, Uniontown, PA  15401</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>(814) 833-7933</t>
+          <t>(724) 437-8600</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>angelacollins@ccdserie.com</t>
+          <t>cvalentine@cffayettepa.org</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>www.ccdserie.com</t>
+          <t>www.cffayettepa.org</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -4682,28 +4698,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Community Foundation of Fayette County</t>
+          <t>Community Foundation of Greene County</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>250 West Main Street, Uniontown, PA  15401</t>
+          <t>108 East High Street, P.O. Box 768, Waynesburg, PA  15370</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>(724) 437-8600</t>
+          <t>(724) 627-2010</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>cvalentine@cffayettepa.org</t>
+          <t>dave.cfgcpa@gmail.com</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>www.cffayettepa.org</t>
+          <t>www.cfgcpa.org</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -4720,28 +4736,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Community Foundation of Greene County</t>
+          <t>Community Foundation of Western PA and Eastern OH</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>108 East High Street, P.O. Box 768, Waynesburg, PA  15370</t>
+          <t>7 West State Street, Suite 301, Sharon, PA  16146</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>(724) 627-2010</t>
+          <t>(724) 981-5882</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>dave.cfgcpa@gmail.com</t>
+          <t>julia@comm-foundation.org</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>www.cfgcpa.org</t>
+          <t>www.comm-foundation.org</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -4758,28 +4774,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Community Foundation of Western PA and Eastern OH</t>
+          <t>Community Partnership School</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>7 West State Street, Suite 301, Sharon, PA  16146</t>
+          <t>3033 W. Glenwood Avenue, Philadelphia, PA  19121</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>(724) 981-5882</t>
+          <t>(215) 235-0461</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>julia@comm-foundation.org</t>
+          <t>m.closter@cpsphilly.org</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>www.comm-foundation.org</t>
+          <t>www.communitypartnershipschool.org</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -4796,28 +4812,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Community Partnership School</t>
+          <t>Comprehensive Learning Center Inc.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>3033 W. Glenwood Avenue, Philadelphia, PA  19121</t>
+          <t>444 Jacksonville Rd., Warminster, PA  18974</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>(215) 235-0461</t>
+          <t>(215) 956-3861</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>m.closter@cpsphilly.org</t>
+          <t>kmartin@clcschoolprograms.org</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>www.communitypartnershipschool.org</t>
+          <t>www.clcschoolprograms.org</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -4834,28 +4850,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Comprehensive Learning Center, Inc.</t>
+          <t>Cornerstone Christian Academy</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>444 Jacksonville Rd., Warminster, PA  18974</t>
+          <t>1939 S. 58th Street, P.O. Box 5520, Philadelphia, PA  19143</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>(215) 956-3861</t>
+          <t>(215) 724-6858</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>kmartin@clcschoolprograms.org</t>
+          <t>dblackwell@cornerstonephiladelphia.com</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>www.clcschoolprograms.org</t>
+          <t>www.wearecornerstone.com</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -4872,28 +4888,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Cornerstone Christian Academy</t>
+          <t>Crispus Attucks Association Inc.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>1939 S. 58th Street, P.O. Box 5520, Philadelphia, PA  19143</t>
+          <t>605 S. Duke Street, York, PA  17401</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>(215) 724-6858</t>
+          <t>(717) 848-3612</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>dblackwell@cornerstonephiladelphia.com</t>
+          <t>dwilliams@crispusattucks.org</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>www.wearecornerstone.com</t>
+          <t>www.crispusattucks.org</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -4910,28 +4926,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Crispus Attucks Association, Inc.</t>
+          <t>Cristo Rey Philadelphia High School</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>605 S. Duke Street, York, PA  17401</t>
+          <t>1717 W. Allegheny Avenue, Philadelphia, PA  19132</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>(717) 848-3612</t>
+          <t>(215) 219-3943</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>dwilliams@crispusattucks.org</t>
+          <t>ljensen@crphs.org</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>www.crispusattucks.org</t>
+          <t>www.cristoreyphiladelphia.org</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -4948,28 +4964,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Cristo Rey Philadelphia High School</t>
+          <t>Crossroads Foundation</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>1717 W. Allegheny Avenue, Philadelphia, PA  19132</t>
+          <t>6901 Lynn Way, Pittsburgh, PA  15208</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>(215) 219-3943</t>
+          <t>(412) 228-4611</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>ljensen@crphs.org</t>
+          <t>kkalson@crfdn.org</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>www.cristoreyphiladelphia.org</t>
+          <t>www.crossroadsfoundation.org</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -4986,28 +5002,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Crossroads Foundation</t>
+          <t>Dayspring Christian Academy</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>6901 Lynn Way, Pittsburgh, PA  15208</t>
+          <t>120 College Avenue, Suite 106, Mountville, PA  17554</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>(412) 228-4611</t>
+          <t>(717) 285-2000</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>kkalson@crfdn.org</t>
+          <t>jriddell@dayspringchristian.com</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>www.crossroadsfoundation.org</t>
+          <t>www.dayspringchristian.com</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -5024,28 +5040,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Dayspring Christian Academy</t>
+          <t>Delaware Valley Friends School</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>120 College Avenue, Suite 106, Mountville, PA  17554</t>
+          <t>19 E. Central Ave., Paoli, PA  19301</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>(717) 285-2000</t>
+          <t>(610) 640-4150</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>jriddell@dayspringchristian.com</t>
+          <t>stephanie.speakman@dvfriends.org</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>www.dayspringchristian.com</t>
+          <t>www.dvfriends.org</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -5062,28 +5078,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Delaware Valley Friends School</t>
+          <t>dePaul School in Northeastern Pennsylvania</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>19 E. Central Ave., Paoli, PA  19301</t>
+          <t>415 Biden Street, Scranton, PA  18505</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>(610) 640-4150</t>
+          <t>(570) 534-4736</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>stephanie.speakman@dvfriends.org</t>
+          <t>cgilroy@friendshiphousepa.org</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>www.dvfriends.org</t>
+          <t>www.depaulschoolnepa.org</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -5100,28 +5116,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>dePaul School in Northeastern Pennsylvania</t>
+          <t>Devon Preparatory School</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>415 Biden Street, Scranton, PA  18505</t>
+          <t>363 N. Valley Forge Road, Devon, PA  19333</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>(570) 534-4736</t>
+          <t>(610) 688-7337</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>cgilroy@friendshiphousepa.org</t>
+          <t>sroxberry@devonprep.com</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>www.depaulschoolnepa.org</t>
+          <t>www.devonprep.com</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -5138,28 +5154,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Devon Preparatory School</t>
+          <t>Diocese of Scranton Scholarship Foundation</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>363 N. Valley Forge Road, Devon, PA  19333</t>
+          <t>300 Wyoming Avenue, Scranton, PA  18503</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>(610) 688-7337</t>
+          <t>(570) 207-2251</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>sroxberry@devonprep.com</t>
+          <t>Kdonohue@dioceseofscranton.org</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>www.devonprep.com</t>
+          <t>www.dioceseofscranton.org</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -5176,28 +5192,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Diocese of Scranton Scholarship Foundation</t>
+          <t>Discovery MI Preschool d/b/a Discovery Montessori</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>300 Wyoming Avenue, Scranton, PA  18503</t>
+          <t>1733 N. Main Ave, Scranton, PA  18508</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>(570) 207-2251</t>
+          <t>(570) 702-7909</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kdonohue@dioceseofscranton.org</t>
+          <t>mydiscoverypreschool@gmail.com</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>www.dioceseofscranton.org</t>
+          <t>www.discoverypa.org</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -5214,28 +5230,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Discovery MI Preschool d/b/a Discovery Montessori</t>
+          <t>Drexel Neumann Academy</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>1733 N. Main Ave, Scranton, PA  18508</t>
+          <t>1901 Potter Street, Chester, PA  19013</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>(570) 702-7909</t>
+          <t>(610) 872-7358</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>mydiscoverypreschool@gmail.com</t>
+          <t>f.gillen@drexelneumannacademy.net</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>www.discoverypa.org</t>
+          <t>www.drexelneumannacademy.net</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -5252,28 +5268,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Drexel Neumann Academy</t>
+          <t>Eastern Pennsylvania Scholarship Foundation - Diocese of Allentown</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1901 Potter Street, Chester, PA  19013</t>
+          <t>P.O. Box F, 1515 Martin Luther King Jr. Drive, Allentown, PA  18102</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>(610) 872-7358</t>
+          <t>(484) 704-2311</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>f.gillen@drexelneumannacademy.net</t>
+          <t>aimpellizzeri@blocs.org</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>www.drexelneumannacademy.net</t>
+          <t>www.allentowndiocese.org</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -5290,28 +5306,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Eastern Pennsylvania Scholarship Foundation - Diocese of Allentown</t>
+          <t>Erie Day School Inc.</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>P.O. Box F, 1515 Martin Luther King Jr. Drive, Allentown, PA  18102</t>
+          <t>1372 West Sixth Street, Erie, PA  16505</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>(484) 704-2311</t>
+          <t>(814) 452-4273</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>aimpellizzeri@blocs.org</t>
+          <t>sgrosch@eriedayschool.com</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>www.allentowndiocese.org</t>
+          <t>www.eriedayschool.org</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -5328,28 +5344,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Erie Day School, Inc.</t>
+          <t>Everence Foundation Inc. d/b/a Mennonite Foundation</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>1372 West Sixth Street, Erie, PA  16505</t>
+          <t>1110 N. Main St., P.O. Box 483, Goshen, IN  46527</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>(814) 452-4273</t>
+          <t>(717) 653-6662</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>sgrosch@eriedayschool.com</t>
+          <t>Elyse.Kauffman@everence.com</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>www.eriedayschool.org</t>
+          <t>www.everence.com</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -5366,28 +5382,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Everence Foundation, Inc. d/b/a Mennonite Foundation</t>
+          <t>Extra Mile Education Foundation Inc.</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
-          <t>1110 N. Main St., P.O. Box 483, Goshen, IN  46527</t>
+          <t>603 Stanwix St., Suite 348, Pittsburgh, PA  15222</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>(717) 653-6662</t>
+          <t>(412) 716-8637</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Elyse.Kauffman@everence.com</t>
+          <t>avescio@extramilefdn.org</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>www.everence.com</t>
+          <t>www.extramilefdn.org</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -5404,28 +5420,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Extra Mile Education Foundation, Inc.</t>
+          <t>Faith Builders Educational Programs Inc.</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>603 Stanwix St., Suite 348, Pittsburgh, PA  15222</t>
+          <t>28527 Guys Mills Rd., Guys Mills, PA  16327</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>(412) 716-8637</t>
+          <t>(814) 789-4518</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>avescio@extramilefdn.org</t>
+          <t>secretary@fbscholarship.org</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>www.extramilefdn.org</t>
+          <t>www.fbscholarship.org</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -5442,28 +5458,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Faith Builders Educational Programs, Inc.</t>
+          <t>Faith Christian School Association of Monroe County Inc.</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>28527 Guys Mills Rd., Guys Mills, PA  16327</t>
+          <t>122 Dante Street, Roseto, PA  18013</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>(814) 789-4518</t>
+          <t>(610) 588-8815</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>secretary@fbscholarship.org</t>
+          <t>hazelton@fcslions.org</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>www.fbscholarship.org</t>
+          <t>www.fcslions.org</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -5480,28 +5496,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Faith Christian School Association of Monroe County, Inc.</t>
+          <t>Falk Laboratory School of the University of Pittsburgh</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>122 Dante Street, Roseto, PA  18013</t>
+          <t>4060 Allequippa Street, Pittsburgh, PA  15261</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>(610) 588-8815</t>
+          <t>(412) 624-8020</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>hazelton@fcslions.org</t>
+          <t>jill.sarada@pitt.edu</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>www.fcslions.org</t>
+          <t>www.falkschool.pitt.edu/</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -5518,28 +5534,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Falk Laboratory School of the University of Pittsburgh</t>
+          <t>Family Choice Scholarship Program of the PA Family Institute</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
-          <t>4060 Allequippa Street, Pittsburgh, PA  15261</t>
+          <t>23 North Front Street, Harrisburg, PA  17101</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>(412) 624-8020</t>
+          <t>(717) 743-1146</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>jill.sarada@pitt.edu</t>
+          <t>familychoice@pafamily.org</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>www.falkschool.pitt.edu/</t>
+          <t>www.myfamilychoice.org</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -5556,28 +5572,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Family Choice Scholarship Program of the PA Family Institute</t>
+          <t>First Regular Baptist Church of Northumberland</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
-          <t>23 North Front Street, Harrisburg, PA  17101</t>
+          <t>Northumberland Christian School, 351 Fifth Street, Northumberland, PA  17857</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>(717) 743-1146</t>
+          <t>(570) 473-9786</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>familychoice@pafamily.org</t>
+          <t>jdrees@norrychristian.net</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>www.myfamilychoice.org</t>
+          <t>www.norrychristian.net</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -5594,28 +5610,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>First Regular Baptist Church of Northumberland</t>
+          <t>First Tee Greater Philadelphia</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Northumberland Christian School, 351 Fifth Street, Northumberland, PA  17857</t>
+          <t>800 Walnut Lane, Philadelphia, PA  19128</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>(570) 473-9786</t>
+          <t>(215) 680-5750</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>jdrees@norrychristian.net</t>
+          <t>jmcaleese@firstteephila.org</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>www.norrychristian.net</t>
+          <t>www.firstteephiladelphia.org</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -5632,28 +5648,28 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>First Tee Greater Philadelphia</t>
+          <t>Foundation for Catholic Education</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
-          <t>800 Walnut Lane, Philadelphia, PA  19128</t>
+          <t>1373 Enterprise Drive, West Chester, PA  19380</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>(215) 680-5750</t>
+          <t>(610) 793-8065</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>jmcaleese@firstteephila.org</t>
+          <t>jparsons@ctdi.com</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>www.firstteephiladelphia.org</t>
+          <t>www.foundationforcatholiceducation.org</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -5670,28 +5686,28 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Foundation for Catholic Education</t>
+          <t>Foundation for Jewish Day Schools of Greater Philadelphia</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1373 Enterprise Drive, West Chester, PA  19380</t>
+          <t>2001 Market St. - 23rd Floor, Philadelphia, PA  19103</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>(610) 793-8065</t>
+          <t>(215) 832-0525</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>jparsons@ctdi.com</t>
+          <t>ematz@jewishphilly.org</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>www.foundationforcatholiceducation.org</t>
+          <t>www.jewishphilly.org</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -5708,28 +5724,28 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Foundation for Jewish Day Schools of Greater Philadelphia</t>
+          <t>Frankford Friends School</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2001 Market St. - 23rd Floor, Philadelphia, PA  19103</t>
+          <t>1500 Orthodox Street, Philadelphia, PA  19124</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>(215) 832-0525</t>
+          <t>(267) 513-8013</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>ematz@jewishphilly.org</t>
+          <t>jwheeler@frankfordfriends.org</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>www.jewishphilly.org</t>
+          <t>www.frankfordfriends.org</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -5746,28 +5762,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Frankford Friends School</t>
+          <t>French International School of Philadelphia</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>1500 Orthodox Street, Philadelphia, PA  19124</t>
+          <t>150 North Highland Avenue, Bala Cynwyd, PA  19004</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>(267) 513-8013</t>
+          <t>(610) 667-1284</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>jwheeler@frankfordfriends.org</t>
+          <t>Leballeur@frenchschoolphila.org</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>www.frankfordfriends.org</t>
+          <t>www.frenchschoolphila.org</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -5784,28 +5800,28 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>French International School of Philadelphia</t>
+          <t>Friends' Central School</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>150 North Highland Avenue, Bala Cynwyd, PA  19004</t>
+          <t>1101 City Avenue, Wynnewood, PA  19096</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>(610) 667-1284</t>
+          <t>(610) 645-5420</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Leballeur@frenchschoolphila.org</t>
+          <t>mdinofia@friendscentral.org</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>www.frenchschoolphila.org</t>
+          <t>www.friendscentral.org</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -5822,28 +5838,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Friends' Central School</t>
+          <t>Friends School Haverford</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>1101 City Avenue, Wynnewood, PA  19096</t>
+          <t>851 Buck Lane, Haverford, PA  19041</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>(610) 645-5420</t>
+          <t>(610) 642-2334</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>mdinofia@friendscentral.org</t>
+          <t>amyers@friendshaverford.org</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>www.friendscentral.org</t>
+          <t>www.friendshaverford.org</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -5860,28 +5876,28 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Friends School Haverford</t>
+          <t>Friends Select School</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>851 Buck Lane, Haverford, PA  19041</t>
+          <t>1651 Benjamin Franklin Parkway, Philadelphia, PA  19103</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>(610) 642-2334</t>
+          <t>(215) 561-5900</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>amyers@friendshaverford.org</t>
+          <t>aneglawi@friends-select.org</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>www.friendshaverford.org</t>
+          <t>www.friends-select.org</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -5898,28 +5914,28 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Friends Select School</t>
+          <t>Fund for Girard College</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
-          <t>1651 Benjamin Franklin Parkway, Philadelphia, PA  19103</t>
+          <t>2101 S. College Avenue, Philadelphia, PA  19121</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>(215) 561-5900</t>
+          <t>(215) 787-4436</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>aneglawi@friends-select.org</t>
+          <t>resposito@girardcollege.edu</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>www.friends-select.org</t>
+          <t>www.girardcollege.edu/support/fund/</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -5936,28 +5952,28 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Fund for Girard College</t>
+          <t>Fund for the Advancement of Minorities through Education Inc. (FAME)</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2101 S. College Avenue, Philadelphia, PA  19121</t>
+          <t>P.O. Box 100073, Pittsburgh, PA  15233</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>(215) 787-4436</t>
+          <t>(412) 363-5553</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>resposito@girardcollege.edu</t>
+          <t>hmoreland@famefund.org</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>www.girardcollege.edu/support/fund/</t>
+          <t>www.famefund.org</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -5974,28 +5990,28 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Fund for the Advancement of Minorities through Education, Inc. (FAME)</t>
+          <t>George Junior Republic</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>P.O. Box 100073, Pittsburgh, PA  15233</t>
+          <t>233 George Junior Road, Grove City, PA  16127</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>(412) 363-5553</t>
+          <t>(724) 458-9330</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>hmoreland@famefund.org</t>
+          <t>tduong@gjr.org</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>www.famefund.org</t>
+          <t>www.GJR.org</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -6012,28 +6028,28 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>George Junior Republic</t>
+          <t>George School</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>233 George Junior Road, Grove City, PA  16127</t>
+          <t>1690 Newtown Langhorne Road, Newtown, PA  18940</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>(724) 458-9330</t>
+          <t>(215) 579-6573</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>tduong@gjr.org</t>
+          <t>ahessert@georgeschool.org</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>www.GJR.org</t>
+          <t>www.georgeschool.org</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -6050,28 +6066,28 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>George School</t>
+          <t>Germantown Academy (Public School of Germantown)</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
-          <t>1690 Newtown Langhorne Road, Newtown, PA  18940</t>
+          <t>340 Morris Road, Fort Washington, PA  19034</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>(215) 579-6573</t>
+          <t>(267) 405-7140</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>ahessert@georgeschool.org</t>
+          <t>karen.wertz@germantownacademy.org</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>www.georgeschool.org</t>
+          <t>www.germantownacademy.net</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -6088,28 +6104,28 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Germantown Academy (Public School of Germantown)</t>
+          <t>Gesu School Inc.</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
-          <t>340 Morris Road, Fort Washington, PA  19034</t>
+          <t>1700 West Thompson Street, Philadelphia, PA  19121</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>(267) 405-7140</t>
+          <t>(267) 546-7484</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>karen.wertz@germantownacademy.org</t>
+          <t>rob.weinstein@gesuschool.org</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>www.germantownacademy.net</t>
+          <t>www.gesuschool.org</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -6126,28 +6142,28 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Gesu School, Inc.</t>
+          <t>Gladwyne Montessori School</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
-          <t>1700 West Thompson Street, Philadelphia, PA  19121</t>
+          <t>920 Youngsford Road, Gladwyne, PA  19035</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>(267) 546-7484</t>
+          <t>(610) 649-1761</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>rob.weinstein@gesuschool.org</t>
+          <t>mdyson@gladwyne.org</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>www.gesuschool.org</t>
+          <t>www.gladwyne.org</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -6164,28 +6180,28 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Gladwyne Montessori School</t>
+          <t>Goals and Assists Foundation</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
-          <t>920 Youngsford Road, Gladwyne, PA  19035</t>
+          <t>3601 S. Broad Street, Philadelphia, PA  19148</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>(610) 649-1761</t>
+          <t>(215) 952-5271</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>mdyson@gladwyne.org</t>
+          <t>sharan@sniderhockey.org</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>www.gladwyne.org</t>
+          <t>www.sniderhockey.org</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -6202,28 +6218,28 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Goals and Assists Foundation</t>
+          <t>Greene Street Friends School</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
-          <t>3601 S. Broad Street, Philadelphia, PA  19148</t>
+          <t>20 West Armat St, Philadelphia, PA  19144</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>(215) 952-5271</t>
+          <t>(215) 438-7000</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>sharan@sniderhockey.org</t>
+          <t>mwaldor@greenestreetfriends.org</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>www.sniderhockey.org</t>
+          <t>www.greenestreetfriends.org</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -6240,28 +6256,28 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Greene Street Friends School</t>
+          <t>Greene Towne School</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
-          <t>20 West Armat St, Philadelphia, PA  19144</t>
+          <t>55 N. 22nd Street, Philadelphia, PA  19103</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>(215) 438-7000</t>
+          <t>(215) 563-6368</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>mwaldor@greenestreetfriends.org</t>
+          <t>areath@gtms.org</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>www.greenestreetfriends.org</t>
+          <t>www.gtms.org</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -6278,28 +6294,28 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Greene Towne School</t>
+          <t>Gwynedd Mercy Academy High School</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
-          <t>55 N. 22nd Street, Philadelphia, PA  19103</t>
+          <t>1345 Sumneytown Pike, Lower Gwynedd, PA  19002</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>(215) 563-6368</t>
+          <t>(267) 885-3717</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>areath@gtms.org</t>
+          <t>cfrascatore@gmahs.org</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>www.gtms.org</t>
+          <t>www.gmahs.org</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -6316,28 +6332,28 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Gwynedd Mercy Academy High School</t>
+          <t>Harrisburg Academy</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
-          <t>1345 Sumneytown Pike, Lower Gwynedd, PA  19002</t>
+          <t>10 Erford Road, Wormleysburg, PA  17043</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>(267) 885-3717</t>
+          <t>(717) 763-7811</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>cfrascatore@gmahs.org</t>
+          <t>preston.s@harrisburgacademy.org</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>www.gmahs.org</t>
+          <t>www.harrisburgacademy.org</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -6354,28 +6370,28 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Harrisburg Academy</t>
+          <t>Heritage Community Initiatives</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
-          <t>10 Erford Road, Wormleysburg, PA  17043</t>
+          <t>820 Braddock Avenue, Braddock, PA  15104</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>(717) 763-7811</t>
+          <t>(412) 351-0535</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>preston.s@harrisburgacademy.org</t>
+          <t>lkelley@heritageserves.org</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>www.harrisburgacademy.org</t>
+          <t>www.heritageserves.org</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -6392,28 +6408,28 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Heritage Community Initiatives</t>
+          <t>High Point Classical Academy</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
-          <t>820 Braddock Avenue, Braddock, PA  15104</t>
+          <t>1919 Mountain Road, Larksville, PA  18651</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>(412) 351-0535</t>
+          <t>(570) 592-4203</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>lkelley@heritageserves.org</t>
+          <t>bakolodgie@highpointclassicalacademy.com</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>www.heritageserves.org</t>
+          <t>highpointclassicalacademy.com</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -6430,28 +6446,28 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>High Point Classical Academy</t>
+          <t>Hill School</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
-          <t>1919 Mountain Road, Larksville, PA  18651</t>
+          <t>860 Beech Street, Pottstown, PA  19484</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>(570) 592-4203</t>
+          <t>(610) 705-1199</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>bakolodgie@highpointclassicalacademy.com</t>
+          <t>kkoller@thehill.org</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>highpointclassicalacademy.com</t>
+          <t>www.thehill.org</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -6468,28 +6484,28 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Hill School</t>
+          <t>HMS School for Children with Cerebral Palsy</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
-          <t>860 Beech Street, Pottstown, PA  19484</t>
+          <t>4400 Baltimore Avenue, Philadelphia, PA  19104</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>(610) 705-1199</t>
+          <t>(215) 222-2566</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>kkoller@thehill.org</t>
+          <t>Cpimentel@HMSSchool.org</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>www.thehill.org</t>
+          <t>www.hmsschool.org</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -6506,28 +6522,28 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>HMS School for Children with Cerebral Palsy</t>
+          <t>Holy Family Foundation</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
-          <t>4400 Baltimore Avenue, Philadelphia, PA  19104</t>
+          <t>8235 Ohio River Blvd., Pittsburgh, PA  15202</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>(215) 222-2566</t>
+          <t>(412) 239-9011</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Cpimentel@HMSSchool.org</t>
+          <t>sexauer.michael@hfi-pgh.org</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>www.hmsschool.org</t>
+          <t>www.hfi-pgh.org</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -6544,28 +6560,28 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Holy Family Foundation</t>
+          <t>Hope Partnership for Education</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
-          <t>8235 Ohio River Blvd., Pittsburgh, PA  15202</t>
+          <t>2601 N. 11th St., Philadelphia, PA  19133</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>(412) 239-9011</t>
+          <t>(215) 232-5410</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>sexauer.michael@hfi-pgh.org</t>
+          <t>vsheppard@hope-partnership.org</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>www.hfi-pgh.org</t>
+          <t>www.hope-partnership.org</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -6582,28 +6598,28 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Hope Partnership for Education</t>
+          <t>House of Hope York PA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2601 N. 11th St., Philadelphia, PA  19133</t>
+          <t>23 N. Pleasant Avenue, Jacobus, PA  17407</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>(215) 232-5410</t>
+          <t>(717) 235-3198</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>vsheppard@hope-partnership.org</t>
+          <t>lori.ziegler@houseofhopeyork.org</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>www.hope-partnership.org</t>
+          <t>www.houseof hopeyork.org</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -6620,30 +6636,26 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>House of Hope York, PA</t>
+          <t>IFA Foundation</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
-          <t>23 N. Pleasant Avenue, Jacobus, PA  17407</t>
+          <t>7157 Camp Hill Rd., Fort Washington, PA  19034</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>(717) 235-3198</t>
+          <t>(484) 919-0282</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>lori.ziegler@houseofhopeyork.org</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>www.houseof hopeyork.org</t>
-        </is>
-      </c>
+          <t>john@ifa.llc</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr">
         <is>
           <t>https://dced.pa.gov/wp-content/themes/business2015/csv/eitc_so_list.csv</t>
@@ -6658,26 +6670,30 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>IFA Foundation</t>
+          <t>Imani Christian Academy</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
-          <t>7157 Camp Hill Rd., Fort Washington, PA  19034</t>
+          <t>2150 East Hills Drive, Pittsburgh, PA  15221</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>(484) 919-0282</t>
+          <t>(412) 731-7982</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>john@ifa.llc</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr"/>
+          <t>pnzambi@imaniadmin.org</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>www.imanipgh.org</t>
+        </is>
+      </c>
       <c r="H199" t="inlineStr">
         <is>
           <t>https://dced.pa.gov/wp-content/themes/business2015/csv/eitc_so_list.csv</t>
@@ -6692,28 +6708,28 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Imani Christian Academy</t>
+          <t>Independence Mission Schools</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2150 East Hills Drive, Pittsburgh, PA  15221</t>
+          <t>1012 W. Thompson Street, Philadelphia, PA  19122</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>(412) 731-7982</t>
+          <t>(215) 771-7038</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>pnzambi@imaniadmin.org</t>
+          <t>bfoley@imsphila.org</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>www.imanipgh.org</t>
+          <t>https://imsphila.org/</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -6730,28 +6746,28 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Independence Mission Schools</t>
+          <t>Indian Creek Valley Christian Family and Children's Center</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
-          <t>1012 W. Thompson Street, Philadelphia, PA  19122</t>
+          <t>2166 Indian Head Rd., Champion, PA  15622</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>(215) 771-7038</t>
+          <t>(724) 455-2122</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>bfoley@imsphila.org</t>
+          <t>merle_skinner@champion.org</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://imsphila.org/</t>
+          <t>www.champion.org</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -6768,28 +6784,28 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Indian Creek Valley Christian Family and Children's Center</t>
+          <t>Jewish Community Alliance of Northeastern Pennsylvania</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2166 Indian Head Rd., Champion, PA  15622</t>
+          <t>613 S.J. Strauss Lane, Kingston, PA  18704</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>(724) 455-2122</t>
+          <t>(570) 574-1136</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>merle_skinner@champion.org</t>
+          <t>jgillespie@nepajca.org.</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>www.champion.org</t>
+          <t>www.jewishwilkes-barre.org</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -6806,28 +6822,28 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Jewish Community Alliance of Northeastern Pennsylvania</t>
+          <t>Jewish Federation of the Lehigh Valley</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
-          <t>613 S.J. Strauss Lane, Kingston, PA  18704</t>
+          <t>702 N. 22nd Street, Allentown, PA  18104</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>(570) 574-1136</t>
+          <t>(610) 821-5500</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>jgillespie@nepajca.org.</t>
+          <t>aaron@jflv.org</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>www.jewishwilkes-barre.org</t>
+          <t>www.jewishlehighvalley.org</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -6844,28 +6860,28 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Jewish Federation of the Lehigh Valley</t>
+          <t>Joey F. Casey Memorial Foundation</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
-          <t>702 N. 22nd Street, Allentown, PA  18104</t>
+          <t>8121 Cresco Avenue, Philadelphia, PA  19136</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>(610) 821-5500</t>
+          <t>(215) 512-2685</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>aaron@jflv.org</t>
+          <t>tcrosset@outlook.com</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>www.jewishlehighvalley.org</t>
+          <t>www.joeycasey.com</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -6882,28 +6898,28 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Joey F. Casey Memorial Foundation</t>
+          <t>Junior Achievement of Western PA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
-          <t>8121 Cresco Avenue, Philadelphia, PA  19136</t>
+          <t>90 Emerson Lane, Suite 1403, Bridgeville, PA  15017</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>(215) 512-2685</t>
+          <t>(814) 691-7619</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>tcrosset@outlook.com</t>
+          <t>jknepper@jawesternpa.org</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>www.joeycasey.com</t>
+          <t>www.jawesternpa.org</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -6920,28 +6936,28 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Junior Achievement of Western PA</t>
+          <t>Keystone Christian Education Association</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
-          <t>90 Emerson Lane, Suite 1403, Bridgeville, PA  15017</t>
+          <t>6101 Bell Road, Harrisburg, PA  17111</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>(814) 691-7619</t>
+          <t>(717) 564-1164</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>jknepper@jawesternpa.org</t>
+          <t>tclater@kcea.com</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>www.jawesternpa.org</t>
+          <t>KCEA.com</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -6958,28 +6974,28 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Keystone Christian Education Association</t>
+          <t>Kimberton Waldorf School</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
-          <t>6101 Bell Road, Harrisburg, PA  17111</t>
+          <t>410 West Seven Stars Road, Phoenixville, PA  19460</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>(717) 564-1164</t>
+          <t>(610) 933-3635</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>tclater@kcea.com</t>
+          <t>development@kimberton.org</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>KCEA.com</t>
+          <t>www.kimberton.org</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -6996,28 +7012,28 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Kimberton Waldorf School</t>
+          <t>Kiskiminetas Springs School</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
-          <t>410 West Seven Stars Road, Phoenixville, PA  19460</t>
+          <t>1888 Brett Lane, Saltsburg, PA  15681</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>(610) 933-3635</t>
+          <t>(724) 639-8047</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>development@kimberton.org</t>
+          <t>vickie.fluharty@kiski.org</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>www.kimberton.org</t>
+          <t>www.kiski.org</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -7034,28 +7050,28 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Kiskiminetas Springs School</t>
+          <t>La Salle Academy</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
-          <t>1888 Brett Lane, Saltsburg, PA  15681</t>
+          <t>1434 North 2nd Street, Philadelphia, PA  19122</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>(724) 639-8047</t>
+          <t>(215) 739-5804</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>vickie.fluharty@kiski.org</t>
+          <t>mgthomson@lasalleacademy.net</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>www.kiski.org</t>
+          <t>www.lasalleacademy.net</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -7072,28 +7088,28 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>La Salle Academy</t>
+          <t>Lancaster Country Day School</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
-          <t>1434 North 2nd Street, Philadelphia, PA  19122</t>
+          <t>725 Hamilton Road, Lancaster, PA  17603</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>(215) 739-5804</t>
+          <t>(717) 397-7240</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>mgthomson@lasalleacademy.net</t>
+          <t>lamars@lancastercountryday.org</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>www.lasalleacademy.net</t>
+          <t>www.lancastercountryday.org</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -7110,28 +7126,28 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Lancaster Country Day School</t>
+          <t>Lancaster County Career &amp; Technology Foundation</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
-          <t>725 Hamilton Road, Lancaster, PA  17603</t>
+          <t>432 Old Market Street, Mt. Joy, PA  17552</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>(717) 397-7240</t>
+          <t>(717) 653-3009</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>lamars@lancastercountryday.org</t>
+          <t>jbaker@lancasterctc.edu</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>www.lancastercountryday.org</t>
+          <t>www.lcctf.org</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -7148,28 +7164,28 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Lancaster County Career &amp; Technology Foundation</t>
+          <t>Lancaster County Christian School</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
-          <t>432 Old Market Street, Mt. Joy, PA  17552</t>
+          <t>2390 New Holland Pike, Lancaster, PA  17601</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>(717) 653-3009</t>
+          <t>(717) 556-0711</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>jbaker@lancasterctc.edu</t>
+          <t>nlong@lccs.cc</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>www.lcctf.org</t>
+          <t>www.lccs.cc</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -7186,28 +7202,28 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Lancaster County Christian School</t>
+          <t>Liguori Academy Inc.</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2390 New Holland Pike, Lancaster, PA  17601</t>
+          <t>2343 East Tucker Street, Philadelphia, PA  19125</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>(717) 556-0711</t>
+          <t>(267) 571-1952</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>nlong@lccs.cc</t>
+          <t>mmarrone@liguoriacademy.org</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>www.lccs.cc</t>
+          <t>www.liguoriacademy.org</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -7224,28 +7240,28 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Liguori Academy, Inc.</t>
+          <t>Linden Hall School for Girls</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2343 East Tucker Street, Philadelphia, PA  19125</t>
+          <t>212 E. Main Street, Lititz, PA  17543</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>(267) 571-1952</t>
+          <t>(717) 626-8512</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>mmarrone@liguoriacademy.org</t>
+          <t>business@lindenhall.org</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>www.liguoriacademy.org</t>
+          <t>www.lindenhall.org</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -7262,28 +7278,28 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Linden Hall School for Girls</t>
+          <t>LOGAN Hope</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
-          <t>212 E. Main Street, Lititz, PA  17543</t>
+          <t>4934 N. 13th St., Philadelphia, PA  19141</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>(717) 626-8512</t>
+          <t>(215) 455-7442</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>business@lindenhall.org</t>
+          <t>jim@loganhope.org</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>www.lindenhall.org</t>
+          <t>www.loganhope.org</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -7300,28 +7316,28 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>LOGAN Hope</t>
+          <t>Logos Academy (Harrisburg)</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
-          <t>4934 N. 13th St., Philadelphia, PA  19141</t>
+          <t>251 Verbeke Street, Harrisburg, PA  17102</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>(215) 455-7442</t>
+          <t>(717) 727-5154</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>jim@loganhope.org</t>
+          <t>lauren.bonnema@logoshbg.org</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>www.loganhope.org</t>
+          <t>www.logosHBG.org</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -7338,28 +7354,28 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Logos Academy (Harrisburg)</t>
+          <t>Logos Academy Scholarship Organization</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
-          <t>251 Verbeke Street, Harrisburg, PA  17102</t>
+          <t>250 West King Street, York, PA  17401</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>(717) 727-5154</t>
+          <t>(717) 848-9835</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>lauren.bonnema@logoshbg.org</t>
+          <t>lisa.knier@logosyork.org</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>www.logosHBG.org</t>
+          <t>www.logosyork.org</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -7376,28 +7392,28 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Logos Academy Scholarship Organization</t>
+          <t>Londonderry School</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
-          <t>250 West King Street, York, PA  17401</t>
+          <t>1800 Bamberger Road, Harrisburg, PA  17110</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>(717) 848-9835</t>
+          <t>(717) 540-0543</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>lisa.knier@logosyork.org</t>
+          <t>jennifer.pomerantz@thelondonderryschool.org</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>www.logosyork.org</t>
+          <t>www.thelondonderryschool.org</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -7414,28 +7430,28 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Londonderry School</t>
+          <t>Malvern Preparatory School</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
-          <t>1800 Bamberger Road, Harrisburg, PA  17110</t>
+          <t>418 S. Warren Avenue, Malvern, PA  19355</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>(717) 540-0543</t>
+          <t>(484) 595-1122</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>jennifer.pomerantz@thelondonderryschool.org</t>
+          <t>nwertsch@malvernprep.org</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>www.thelondonderryschool.org</t>
+          <t>www.malvernprep.org</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -7452,28 +7468,28 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Malvern Preparatory School</t>
+          <t>McGlynn Center</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
-          <t>418 S. Warren Avenue, Malvern, PA  19355</t>
+          <t>72 Midland Court, P.O. Box 842, Wilkes-Barre, PA  18702</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>(484) 595-1122</t>
+          <t>(570) 824-8891</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>nwertsch@malvernprep.org</t>
+          <t>pnork@mcglynncenter.org</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>www.malvernprep.org</t>
+          <t>www.mcglynncenter.org</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -7490,28 +7506,28 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>McGlynn Center</t>
+          <t>Meadowbrook Christian School Scholarship Organization K-12</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
-          <t>72 Midland Court, P.O. Box 842, Wilkes-Barre, PA  18702</t>
+          <t>Wesleyan Church Corporation, 363 Stamm Road, Milton, PA  17847</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>(570) 824-8891</t>
+          <t>(570) 742-2638</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>pnork@mcglynncenter.org</t>
+          <t>sheri.hoffman@mcslions.org</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>www.mcglynncenter.org</t>
+          <t>www.mcslions.org</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -7528,28 +7544,28 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Meadowbrook Christian School Scholarship Organization K-12</t>
+          <t>Media-Providence Friends School Inc.</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Wesleyan Church Corporation, 363 Stamm Road, Milton, PA  17847</t>
+          <t>125 W. Third Street, Media, PA  19063</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>(570) 742-2638</t>
+          <t>(610) 565-1960</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>sheri.hoffman@mcslions.org</t>
+          <t>cmcgoff@mpfs.org</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>www.mcslions.org</t>
+          <t>www.mpfs.org</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -7566,28 +7582,28 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Media-Providence Friends School, Inc.</t>
+          <t>Mercersburg Academy</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
-          <t>125 W. Third Street, Media, PA  19063</t>
+          <t>100 Academy Drive, Mercersburg, PA  17236</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>(610) 565-1960</t>
+          <t>(717) 328-6359</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>cmcgoff@mpfs.org</t>
+          <t>batsonm@mercersburg.edu</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>www.mpfs.org</t>
+          <t>www.mercersburg.edu</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -7604,28 +7620,28 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Mercersburg Academy</t>
+          <t>Mercy Vocational High School</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
         <is>
-          <t>100 Academy Drive, Mercersburg, PA  17236</t>
+          <t>d/b/a Mercy Career &amp; Technical High School, 2900 W. Hunting Park Avenue, Philadelphia, PA  19129</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>(717) 328-6359</t>
+          <t>(215) 226-1225</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>batsonm@mercersburg.edu</t>
+          <t>ngreen@mercycte.org</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>www.mercersburg.edu</t>
+          <t>www.mercyvocational.org</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -7642,28 +7658,28 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Mercy Vocational High School</t>
+          <t>Mercyhurst Preparatory School</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
-          <t>d/b/a Mercy Career &amp; Technical High School, 2900 W. Hunting Park Avenue, Philadelphia, PA  19129</t>
+          <t>538 East Grandview Blvd., Erie, PA  16504</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>(215) 226-1225</t>
+          <t>(814) 824-2408</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>ngreen@mercycte.org</t>
+          <t>jgray@mpslakers.com</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>www.mercyvocational.org</t>
+          <t>www.mpslakers.com</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -7680,28 +7696,28 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Mercyhurst Preparatory School</t>
+          <t>Merion Mercy Academy</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
-          <t>538 East Grandview Blvd., Erie, PA  16504</t>
+          <t>511 Montgomery Ave., Merion Station, PA  19066</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>(814) 824-2408</t>
+          <t>(610) 664-6655</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>jgray@mpslakers.com</t>
+          <t>kcawley@merion-mercy.com</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>www.mpslakers.com</t>
+          <t>www.merion-mercy.com</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -7718,28 +7734,28 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Merion Mercy Academy</t>
+          <t>MMI Preparatory School</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
-          <t>511 Montgomery Ave., Merion Station, PA  19066</t>
+          <t>154 Centre Street, Freeland, PA  18224</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>(610) 664-6655</t>
+          <t>(570) 636-1108</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>kcawley@merion-mercy.com</t>
+          <t>kmcnulty@mmiprep.org</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>www.merion-mercy.com</t>
+          <t>www.mmiprep.org</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -7756,28 +7772,28 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>MMI Preparatory School</t>
+          <t>Montessori Academy of Lancaster</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
-          <t>154 Centre Street, Freeland, PA  18224</t>
+          <t>2750 Weaver Road, Lancaster, PA  17601</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>(570) 636-1108</t>
+          <t>(717) 560-0815</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>kmcnulty@mmiprep.org</t>
+          <t>carol@montlanc.com</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>www.mmiprep.org</t>
+          <t>www.montlanc.com</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -7794,28 +7810,28 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Montessori Academy of Lancaster</t>
+          <t>Montgomery County Scholarships Inc.</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2750 Weaver Road, Lancaster, PA  17601</t>
+          <t>101 Greenwood Avenue, Suite 380, Jenkintown, PA  19046</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>(717) 560-0815</t>
+          <t>(215) 253-8511</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>carol@montlanc.com</t>
+          <t>jed.silversmith@pataxcredits.org</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>www.montlanc.com</t>
+          <t>www.pataxcredits.org/</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -7832,28 +7848,28 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Montgomery County Scholarships, Inc.</t>
+          <t>Moravian Academy</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
-          <t>101 Greenwood Avenue, Suite 380, Jenkintown, PA  19046</t>
+          <t>7 East Market Street, Bethlehem, PA  18018</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>(215) 253-8511</t>
+          <t>(610) 332-5291</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>jed.silversmith@pataxcredits.org</t>
+          <t>bzaiser@mamail.net</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>www.pataxcredits.org/</t>
+          <t>www.moravianacademy.org</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -7870,28 +7886,28 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Moravian Academy</t>
+          <t>Nativity School of Harrisburg</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
-          <t>7 East Market Street, Bethlehem, PA  18018</t>
+          <t>2101 N. 5th Street, Harrisburg, PA  17110</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>(610) 332-5291</t>
+          <t>(717) 236-5602</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>bzaiser@mamail.net</t>
+          <t>er@nativityschoolofharrisburg.org</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>www.moravianacademy.org</t>
+          <t>www.nativityharrisburg.org</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -7908,28 +7924,28 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Nativity School of Harrisburg</t>
+          <t>NativityMiguel School of Scranton</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2101 N. 5th Street, Harrisburg, PA  17110</t>
+          <t>2300 Adams Ave., Scranton, PA  18509</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>(717) 236-5602</t>
+          <t>(570) 955-5176</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>er@nativityschoolofharrisburg.org</t>
+          <t>rprislupski@nmscranton.org</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>www.nativityharrisburg.org</t>
+          <t>www.nativitymiguelscranton.org</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -7946,28 +7962,28 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>NativityMiguel School of Scranton</t>
+          <t>Neumann Scholarship Foundation</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2300 Adams Ave., Scranton, PA  18509</t>
+          <t>4800 Union Deposit Road, Harrisburg, PA  17111</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>(570) 955-5176</t>
+          <t>(717) 657-4804</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>rprislupski@nmscranton.org</t>
+          <t>dbreen@hbgdiocese.org</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>www.nativitymiguelscranton.org</t>
+          <t>www.hbgdiocese.org</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -7984,28 +8000,28 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Neumann Scholarship Foundation</t>
+          <t>Newtown Friends School</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
-          <t>4800 Union Deposit Road, Harrisburg, PA  17111</t>
+          <t>1940 Newtown Langhorne Road, Newtown, PA  18940</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>(717) 657-4804</t>
+          <t>(215) 968-2225</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>dbreen@hbgdiocese.org</t>
+          <t>cfrank@newtownfriends.org</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>www.hbgdiocese.org</t>
+          <t>www.newtownfriends.org</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -8022,28 +8038,28 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Newtown Friends School</t>
+          <t>Our Lady of the Sacred Heart High School</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
-          <t>1940 Newtown Langhorne Road, Newtown, PA  18940</t>
+          <t>1504 Woodcrest Avenue, Coraopolis, PA  15108</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>(215) 968-2225</t>
+          <t>(412) 269-7726</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>cfrank@newtownfriends.org</t>
+          <t>ckarashin@olsh.org</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>www.newtownfriends.org</t>
+          <t>www.olsh.org</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -8060,30 +8076,26 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Our Lady of the Sacred Heart High School</t>
+          <t>Our Promise Inc.</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
-          <t>1504 Woodcrest Avenue, Coraopolis, PA  15108</t>
+          <t>1205 E. Columbia Ave., Philadelphia, PA  19125</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>(412) 269-7726</t>
+          <t>(267) 825-3188</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>ckarashin@olsh.org</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>www.olsh.org</t>
-        </is>
-      </c>
+          <t>sherman.washi@gmail.com</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr">
         <is>
           <t>https://dced.pa.gov/wp-content/themes/business2015/csv/eitc_so_list.csv</t>
@@ -8098,26 +8110,30 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Our Promise Inc.</t>
+          <t>Pen Ryn School</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
-          <t>1205 E. Columbia Ave., Philadelphia, PA  19125</t>
+          <t>235 South Olds Boulevard, Fairless Hills, PA  19030</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>(267) 825-3188</t>
+          <t>(215) 547-1800</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>sherman.washi@gmail.com</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr"/>
+          <t>billodcpa@aol.com</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>www.penryn.org</t>
+        </is>
+      </c>
       <c r="H237" t="inlineStr">
         <is>
           <t>https://dced.pa.gov/wp-content/themes/business2015/csv/eitc_so_list.csv</t>
@@ -8132,28 +8148,28 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Pen Ryn School</t>
+          <t>Penngift Foundation Inc.</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr">
         <is>
-          <t>235 South Olds Boulevard, Fairless Hills, PA  19030</t>
+          <t>P.O. Box 121, Elverson, PA  19520</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>(215) 547-1800</t>
+          <t>(610) 286-1936</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>billodcpa@aol.com</t>
+          <t>jcox@penngift.org</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>www.penryn.org</t>
+          <t>www.penngift.org</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -8170,28 +8186,28 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Penngift Foundation, Inc.</t>
+          <t>Penn-Mont Academy</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
         <is>
-          <t>P.O. Box 121, Elverson, PA  19520</t>
+          <t>131 Holliday Hills Drive, Hollidaysburg, PA  16648</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>(610) 286-1936</t>
+          <t>(814) 696-8801</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>jcox@penngift.org</t>
+          <t>kathleen.dombrosky@pennmontacademy.com</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>www.penngift.org</t>
+          <t>www.pennmontacademy.com</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -8208,28 +8224,28 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Penn-Mont Academy</t>
+          <t>Perkiomen School</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
-          <t>131 Holliday Hills Drive, Hollidaysburg, PA  16648</t>
+          <t>200 Seminary Street, Pennsburg, PA  18073</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>(814) 696-8801</t>
+          <t>(267) 717-5548</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>kathleen.dombrosky@pennmontacademy.com</t>
+          <t>sfarrand@perkiomen.org</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>www.pennmontacademy.com</t>
+          <t>www.perkiomen.org</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -8246,28 +8262,28 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Perkiomen School</t>
+          <t>Phase 4 Learning Center Inc.</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
-          <t>200 Seminary Street, Pennsburg, PA  18073</t>
+          <t>5850 Centre Avenue, Pittsburgh, PA  15206</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>(267) 717-5548</t>
+          <t>(215) 650-9004</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>sfarrand@perkiomen.org</t>
+          <t>eraphael@phase4lc.org</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>www.perkiomen.org</t>
+          <t>www.phase4learningcenter.org</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -8284,28 +8300,28 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Phase 4 Learning Center, Inc.</t>
+          <t>Philadelphia School of Democracy Inc.</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
-          <t>5850 Centre Avenue, Pittsburgh, PA  15206</t>
+          <t>4950 Springfield Ave., Philadelphia, PA  19143</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>(215) 650-9004</t>
+          <t>(215) 218-9586</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>eraphael@phase4lc.org</t>
+          <t>mark@phillyfreeschool.org</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>www.phase4learningcenter.org</t>
+          <t>www.phillyfreeschool.org</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -8322,28 +8338,28 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Philadelphia School of Democracy, Inc.</t>
+          <t>Pittsburgh Jewish Educational Improvement Foundation</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
-          <t>4950 Springfield Ave., Philadelphia, PA  19143</t>
+          <t>2000 Technology Drive, Pittsburgh, PA  15219</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>(215) 218-9586</t>
+          <t>(412) 992-5250</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>mark@phillyfreeschool.org</t>
+          <t>sjablow@jfedpgh.org</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>www.phillyfreeschool.org</t>
+          <t>www.jewishpgh.org</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -8360,28 +8376,28 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Pittsburgh Jewish Educational Improvement Foundation</t>
+          <t>PJHS Scholarship Organization  (St. Joe's Prep &amp; Scranton Prep)</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2000 Technology Drive, Pittsburgh, PA  15219</t>
+          <t>1000 Wyoming Avenue, Scranton, PA  18509</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>(412) 992-5250</t>
+          <t>(570) 941-7737</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>sjablow@jfedpgh.org</t>
+          <t>mweed@scrantonprep.com</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>www.jewishpgh.org</t>
+          <t>www.scrantonprep.com</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -8398,28 +8414,28 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>PJHS Scholarship Organization  (St. Joe's Prep &amp; Scranton Prep)</t>
+          <t>Pocono Mountains United Way</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
         <is>
-          <t>1000 Wyoming Avenue, Scranton, PA  18509</t>
+          <t>301 McConnell Street, Stroudsburg, PA  18360</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>(570) 941-7737</t>
+          <t>(570) 517-3955</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>mweed@scrantonprep.com</t>
+          <t>michael@poconounitedway.org</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>www.scrantonprep.com</t>
+          <t>www.poconounitedway.org</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -8436,28 +8452,28 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Pocono Mountains United Way</t>
+          <t>Poise Foundation</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr">
         <is>
-          <t>301 McConnell Street, Stroudsburg, PA  18360</t>
+          <t>Two Gateway Center, Suite 1700, 603 Stanwix Street, Pittsburgh, PA  15222</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>(570) 517-3955</t>
+          <t>(412) 281-4967</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>michael@poconounitedway.org</t>
+          <t>Kjackson@poisefdn.org</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>www.poconounitedway.org</t>
+          <t>www.poisefoundation.org</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -8474,28 +8490,28 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Poise Foundation</t>
+          <t>Quaker School at Horsham</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Two Gateway Center, Suite 1700, 603 Stanwix Street, Pittsburgh, PA  15222</t>
+          <t>250 Meetinghouse Rd., Horsham, PA  19044</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>(412) 281-4967</t>
+          <t>(215) 674-2875</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Kjackson@poisefdn.org</t>
+          <t>gim@quakerschool.org</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>www.poisefoundation.org</t>
+          <t>www.quakerschool.org</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -8512,28 +8528,28 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Quaker School at Horsham</t>
+          <t>Sacred Heart Academy Bryn Mawr</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
         <is>
-          <t>250 Meetinghouse Rd., Horsham, PA  19044</t>
+          <t>480 S. Bryn Mawr Avenue, Bryn Mawr, PA  19010</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>(215) 674-2875</t>
+          <t>(610) 527-3915</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>gim@quakerschool.org</t>
+          <t>howard.walker@shabrynmawr.org</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>www.quakerschool.org</t>
+          <t>www.shabrynmawr.org</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -8550,28 +8566,28 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Sacred Heart Academy Bryn Mawr</t>
+          <t>Saint James School</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
         <is>
-          <t>480 S. Bryn Mawr Avenue, Bryn Mawr, PA  19010</t>
+          <t>3217 W. Clearfield Street, Philadelphia, PA  19132</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>(610) 527-3915</t>
+          <t>(484) 224-3886</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>howard.walker@shabrynmawr.org</t>
+          <t>taxcredit@stjamesphila.org</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>www.shabrynmawr.org</t>
+          <t>www.stjamesphila.org</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -8588,28 +8604,28 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Saint James School</t>
+          <t>Salvaggio Academy</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
-          <t>3217 W. Clearfield Street, Philadelphia, PA  19132</t>
+          <t>1390 Ridgeview Drive, Allentown, PA  18104</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>(484) 224-3886</t>
+          <t>(610) 530-5241</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>taxcredit@stjamesphila.org</t>
+          <t>salvaggioacademy.tax@cai.io</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>www.stjamesphila.org</t>
+          <t>www.salvaggioacademy.org</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -8626,28 +8642,28 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Salvaggio Academy</t>
+          <t>Scholarship Partners Foundation</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
         <is>
-          <t>1390 Ridgeview Drive, Allentown, PA  18104</t>
+          <t>723 East Pittsburgh St., Greensburg, PA  15601</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>(610) 530-5241</t>
+          <t>(724) 552-2589</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>salvaggioacademy.tax@cai.io</t>
+          <t>wbarnes@dioceseofgreensburg.org</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>www.salvaggioacademy.org</t>
+          <t>www.dioceseofgreensburg.org</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -8664,28 +8680,28 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Scholarship Partners Foundation</t>
+          <t>Scholastic Opportunity Scholarship Fund (SOS)</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
-          <t>723 East Pittsburgh St., Greensburg, PA  15601</t>
+          <t>Diocese of Pittsburgh, 2900 Noblestown Rd., Pittsburgh, PA  15205</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>(724) 552-2589</t>
+          <t>(412) 456-3085</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>wbarnes@dioceseofgreensburg.org</t>
+          <t>mfreker@diopitt.org</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>www.dioceseofgreensburg.org</t>
+          <t>www.diopitt.org</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -8702,28 +8718,28 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Scholastic Opportunity Scholarship Fund (SOS)</t>
+          <t>Sewickley Academy</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Diocese of Pittsburgh, 2900 Noblestown Rd., Pittsburgh, PA  15205</t>
+          <t>315 Academy Avenue, Sewickley, PA  15143</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>(412) 456-3085</t>
+          <t>(412) 741-2230</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>mfreker@diopitt.org</t>
+          <t>bvuono@sewickley.org</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>www.diopitt.org</t>
+          <t>www.sewickley.org</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -8740,28 +8756,28 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Sewickley Academy</t>
+          <t>Shady Side Academy</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
-          <t>315 Academy Avenue, Sewickley, PA  15143</t>
+          <t>423 Fox Chapel Road, Pittsburgh, PA  15238</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>(412) 741-2230</t>
+          <t>(412) 968-3032</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>bvuono@sewickley.org</t>
+          <t>jscott@shadysideacademy.org</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>www.sewickley.org</t>
+          <t>www.shadysideacademy.org</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -8778,28 +8794,28 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Shady Side Academy</t>
+          <t>Silverback Educational Foundation for the Arts Dance &amp; Athletics</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
-          <t>423 Fox Chapel Road, Pittsburgh, PA  15238</t>
+          <t>3811 West Chester Pike, Bldg. 2, Ste. 200, Newtown Square, PA  19073</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>(412) 968-3032</t>
+          <t>(717) 856-9195</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>jscott@shadysideacademy.org</t>
+          <t>rstover@grahampartners.net</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>www.shadysideacademy.org</t>
+          <t>www.silverback-sefada.org</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -8816,28 +8832,28 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Silverback Educational Foundation for the Arts, Dance &amp; Athletics</t>
+          <t>Solebury School</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr">
         <is>
-          <t>3811 West Chester Pike, Bldg. 2, Ste. 200, Newtown Square, PA  19073</t>
+          <t>6832 Phillips Mill Road, New Hope, PA  18938</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>(717) 856-9195</t>
+          <t>(215) 862-5261</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>rstover@grahampartners.net</t>
+          <t>mmarshall@solebury.org</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>www.silverback-sefada.org</t>
+          <t>www.solebury.org</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -8854,30 +8870,26 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Solebury School</t>
+          <t>Spanish Scholarship Fund</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr">
         <is>
-          <t>6832 Phillips Mill Road, New Hope, PA  18938</t>
+          <t>1436 Lansdowne Ave, Darby, PA  19023</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>(215) 862-5261</t>
+          <t>(610) 558-4593</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>mmarshall@solebury.org</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>www.solebury.org</t>
-        </is>
-      </c>
+          <t>rowers3@verizon.net</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr">
         <is>
           <t>https://dced.pa.gov/wp-content/themes/business2015/csv/eitc_so_list.csv</t>
@@ -8892,26 +8904,30 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Spanish Scholarship Fund</t>
+          <t>Springside Chestnut Hill Academy</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1436 Lansdowne Ave, Darby, PA  19023</t>
+          <t>500 West Willow Grove Avenue, Philadelphia, PA  19118</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>(610) 558-4593</t>
+          <t>(215) 754-1622</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>rowers3@verizon.net</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr"/>
+          <t>mboozer@sch.org</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>www.sch.org</t>
+        </is>
+      </c>
       <c r="H258" t="inlineStr">
         <is>
           <t>https://dced.pa.gov/wp-content/themes/business2015/csv/eitc_so_list.csv</t>
@@ -8926,28 +8942,28 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Springside Chestnut Hill Academy</t>
+          <t>St. Edmund's Academy</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr">
         <is>
-          <t>500 West Willow Grove Avenue, Philadelphia, PA  19118</t>
+          <t>5705 Darlington Road, Pittsburgh, PA  15217</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>(215) 754-1622</t>
+          <t>(412) 521-1907</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>mboozer@sch.org</t>
+          <t>dianamcallister@stedmunds.net</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>www.sch.org</t>
+          <t>www.stedmunds.net</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -8964,28 +8980,28 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>St. Edmund's Academy</t>
+          <t>St. Stephen's Episcopal School</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
         <is>
-          <t>5705 Darlington Road, Pittsburgh, PA  15217</t>
+          <t>215 N. Front Street, Harrisburg, PA  17101</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>(412) 521-1907</t>
+          <t>(717) 238-8590</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>dianamcallister@stedmunds.net</t>
+          <t>dshaffer@sseschool.org</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>www.stedmunds.net</t>
+          <t>www.sseschool.org</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -9002,28 +9018,28 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>St. Stephen's Episcopal School</t>
+          <t>State College Friends School</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
-          <t>215 N. Front Street, Harrisburg, PA  17101</t>
+          <t>1900 University Drive, State College, PA  16801</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>(717) 238-8590</t>
+          <t>(814) 237-8386</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>dshaffer@sseschool.org</t>
+          <t>jlove@scfriends.org</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>www.sseschool.org</t>
+          <t>www.scfriends.org</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -9040,28 +9056,28 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>State College Friends School</t>
+          <t>Susquehanna Waldorf School</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
-          <t>1900 University Drive, State College, PA  16801</t>
+          <t>15 West Walnut St., Marietta, PA  17547</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>(814) 237-8386</t>
+          <t>(717) 649-1344</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>jlove@scfriends.org</t>
+          <t>deborah.duke@susquehanna.org</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>www.scfriends.org</t>
+          <t>www.susquehannawaldorf.org</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -9078,28 +9094,28 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Susquehanna Waldorf School</t>
+          <t>Talk Institute and School a/k/a Talk Inc.</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
         <is>
-          <t>15 West Walnut St., Marietta, PA  17547</t>
+          <t>6 Campus Blvd., Newtown Square, PA  19073</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>(717) 649-1344</t>
+          <t>(610) 356-5566</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>deborah.duke@susquehanna.org</t>
+          <t>kristen.tabun@talkinc.org</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>www.susquehannawaldorf.org</t>
+          <t>www.talkinc.org</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -9116,28 +9132,28 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Talk Institute and School a/k/a Talk, Inc.</t>
+          <t>The Baldwin School</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr">
         <is>
-          <t>6 Campus Blvd., Newtown Square, PA  19073</t>
+          <t>701 Montgomery Ave., Bryn Mawr, PA  19010</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>(610) 356-5566</t>
+          <t>(610) 525-2700</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>kristen.tabun@talkinc.org</t>
+          <t>brian.lorigan@baldwinschool.org</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>www.talkinc.org</t>
+          <t>www.baldwinschool.org</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -9154,28 +9170,28 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>The Baldwin School</t>
+          <t>The Campus Laboratory School of Carlow University</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr">
         <is>
-          <t>701 Montgomery Ave., Bryn Mawr, PA  19010</t>
+          <t>3333 Fifth Avenue, Pittsburgh, PA  15213</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>(610) 525-2700</t>
+          <t>(412) 578-2072</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>brian.lorigan@baldwinschool.org</t>
+          <t>hashroyer@carlow.edu</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>www.baldwinschool.org</t>
+          <t>www.camousschool.edu</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -9192,28 +9208,28 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>The Campus Laboratory School of Carlow University</t>
+          <t>The Church Farm School</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
-          <t>3333 Fifth Avenue, Pittsburgh, PA  15213</t>
+          <t>1001 East Lincoln Highway, Exton, PA  19341</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>(412) 578-2072</t>
+          <t>(610) 363-5383</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>hashroyer@carlow.edu</t>
+          <t>advancement@gocfs.net</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>www.camousschool.edu</t>
+          <t>www.gocfs.net</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -9230,28 +9246,28 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>The Church Farm School</t>
+          <t>The Concept School</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr">
         <is>
-          <t>1001 East Lincoln Highway, Exton, PA  19341</t>
+          <t>1120 E. Street Rd., Westtown, PA  19395</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>(610) 363-5383</t>
+          <t>(610) 399-1135</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>advancement@gocfs.net</t>
+          <t>slevine@theconceptschool.org</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>www.gocfs.net</t>
+          <t>www.theconceptschool.org</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -9268,28 +9284,28 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>The Concept School</t>
+          <t>The Ellis School</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr">
         <is>
-          <t>1120 E. Street Rd., Westtown, PA  19395</t>
+          <t>6425 Fifth Avenue, Pittsburgh, PA  15206</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>(610) 399-1135</t>
+          <t>(412) 661-5992</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>slevine@theconceptschool.org</t>
+          <t>devereuxc@theellisschool.org</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>www.theconceptschool.org</t>
+          <t>www.theellisschool.org</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -9306,28 +9322,28 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>The Ellis School</t>
+          <t>The Episcopal Academy</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr">
         <is>
-          <t>6425 Fifth Avenue, Pittsburgh, PA  15206</t>
+          <t>1785 Bishop White Drive, Newtown Square, PA  19073</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>(412) 661-5992</t>
+          <t>(484) 424-1424</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>devereuxc@theellisschool.org</t>
+          <t>tfanning@episcopalacademy.org</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>www.theellisschool.org</t>
+          <t>www.episcopalacademy.org</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -9344,28 +9360,28 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>The Episcopal Academy</t>
+          <t>The Glen Montessori School</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
-          <t>1785 Bishop White Drive, Newtown Square, PA  19073</t>
+          <t>950 Perry Highway, Pittsburgh, PA  15237</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>(484) 424-1424</t>
+          <t>(412) 318-4885</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>tfanning@episcopalacademy.org</t>
+          <t>jherrmann@glenmontessori.org</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>www.episcopalacademy.org</t>
+          <t>www.glenmontessori.org</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -9382,28 +9398,28 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>The Glen Montessori School</t>
+          <t>The Grayson School</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
-          <t>950 Perry Highway, Pittsburgh, PA  15237</t>
+          <t>211 Matsonford Rd., Radnor, PA  19008</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>(412) 318-4885</t>
+          <t>(484) 428-3241</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>jherrmann@glenmontessori.org</t>
+          <t>jnance@thegraysonschool.org</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>www.glenmontessori.org</t>
+          <t>www.thegraysonschool.org</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -9420,28 +9436,28 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>The Grayson School</t>
+          <t>The Haverford School</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
-          <t>211 Matsonford Rd., Radnor, PA  19008</t>
+          <t>450 Lancaster Avenue, Haverford, PA  19041</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>(484) 428-3241</t>
+          <t>(484) 417-2794</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>jnance@thegraysonschool.org</t>
+          <t>mnierenberg@haverford.org</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>www.thegraysonschool.org</t>
+          <t>www.haverford.org</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -9458,28 +9474,28 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>The Haverford School</t>
+          <t>The Hill Top Preparatory School Inc.</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
-          <t>450 Lancaster Avenue, Haverford, PA  19041</t>
+          <t>737 S. Ithan Avenue, Bryn Mawr, PA  19010</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>(484) 417-2794</t>
+          <t>(610) 527-3230</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>mnierenberg@haverford.org</t>
+          <t>jtremoglie@hilltopprep.org</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>www.haverford.org</t>
+          <t>www.hilltopprep.org</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -9496,28 +9512,28 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>The Hill Top Preparatory School, Inc.</t>
+          <t>The Hillside School</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
-          <t>737 S. Ithan Avenue, Bryn Mawr, PA  19010</t>
+          <t>2697 Brookside Road, Macungie, PA  18062</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>(610) 527-3230</t>
+          <t>(610) 967-3701</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>jtremoglie@hilltopprep.org</t>
+          <t>dkuntzman@hillsideschool.org</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>www.hilltopprep.org</t>
+          <t>www.hillsideschool.org</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -9534,28 +9550,28 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>The Hillside School</t>
+          <t>The Janus School</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2697 Brookside Road, Macungie, PA  18062</t>
+          <t>205 Lefever Road, Mount Joy, PA  17552</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>(610) 967-3701</t>
+          <t>(717) 653-0025</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>dkuntzman@hillsideschool.org</t>
+          <t>sshaffer@thejanusschool.org</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>www.hillsideschool.org</t>
+          <t>www.thejanusschool.org</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -9572,28 +9588,28 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>The Janus School</t>
+          <t>The Joshua Group</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
-          <t>205 Lefever Road, Mount Joy, PA  17552</t>
+          <t>1442 Market St., Harrisburg, PA  17103</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>(717) 653-0025</t>
+          <t>(717) 236-4464</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>sshaffer@thejanusschool.org</t>
+          <t>j.politis@joshuagrouphbg.org</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>www.thejanusschool.org</t>
+          <t>www.joshuagroup.org</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -9610,28 +9626,28 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>The Joshua Group</t>
+          <t>The Learning Lamp Inc.</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
-          <t>1442 Market St., Harrisburg, PA  17103</t>
+          <t>2025 Bedford St., Johnstown, PA  15904</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>(717) 236-4464</t>
+          <t>(814) 262-0732</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>j.politis@joshuagrouphbg.org</t>
+          <t>lspangler@thelearninglamp.org</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>www.joshuagroup.org</t>
+          <t>www.thelearninglamp.org</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -9648,28 +9664,28 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>The Learning Lamp, Inc.</t>
+          <t>The Neighborhood Academy</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2025 Bedford St., Johnstown, PA  15904</t>
+          <t>709 North Aiken Avenue, Pittsburgh, PA  15206</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>(814) 262-0732</t>
+          <t>(412) 365-5045</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>lspangler@thelearninglamp.org</t>
+          <t>jamie.donne@theneighborhoodacademy.org</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>www.thelearninglamp.org</t>
+          <t>www.theneighborhoodacademy.org</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -9686,28 +9702,28 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>The Neighborhood Academy</t>
+          <t>The Phelps School</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
-          <t>709 North Aiken Avenue, Pittsburgh, PA  15206</t>
+          <t>583 Sugartown Road, Malvern, PA  19355</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>(412) 365-5045</t>
+          <t>(610) 644-1754</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>jamie.donne@theneighborhoodacademy.org</t>
+          <t>sfahey@thephelpsschool.org</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>www.theneighborhoodacademy.org</t>
+          <t>www.thephelpsschool.org</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -9724,28 +9740,28 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>The Phelps School</t>
+          <t>The Samuel School</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
-          <t>583 Sugartown Road, Malvern, PA  19355</t>
+          <t>510 Joyce Road, Camp Hill, PA  17011</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>(610) 644-1754</t>
+          <t>(717) 557-1119</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>sfahey@thephelpsschool.org</t>
+          <t>rpeck@samuelschool.com</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>www.thephelpsschool.org</t>
+          <t>www.samuelschool.com</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -9762,28 +9778,28 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>The Samuel School</t>
+          <t>The School in Rose Valley</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
-          <t>510 Joyce Road, Camp Hill, PA  17011</t>
+          <t>20 School Lane, Rose Valley, PA  19063</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>(717) 557-1119</t>
+          <t>(610) 566-1088</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>rpeck@samuelschool.com</t>
+          <t>nava@theschoolinrosevalley.org</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>www.samuelschool.com</t>
+          <t>www.theschoolinrosevalley.org</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -9800,28 +9816,28 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>The School in Rose Valley</t>
+          <t>The Shipley School</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
-          <t>20 School Lane, Rose Valley, PA  19063</t>
+          <t>814 Yarrow Street, Bryn Mawr, PA  19010</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>(610) 566-1088</t>
+          <t>(610) 525-4300</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>nava@theschoolinrosevalley.org</t>
+          <t>pdaly@shipleyschool.org</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>www.theschoolinrosevalley.org</t>
+          <t>www.shipleyschool.org</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -9838,28 +9854,28 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>The Shipley School</t>
+          <t>The Swain School Inc.</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
-          <t>814 Yarrow Street, Bryn Mawr, PA  19010</t>
+          <t>1100 S. 24th Street, Allentown, PA  18103</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>(610) 525-4300</t>
+          <t>(610) 332-5291</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>pdaly@shipleyschool.org</t>
+          <t>bzaiser@mamail.net</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>www.shipleyschool.org</t>
+          <t>www.moravianacademy.org</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -9876,28 +9892,28 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>The Swain School, Inc.</t>
+          <t>The Vista School</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
-          <t>1100 S. 24th Street, Allentown, PA  18103</t>
+          <t>1021 Springboard Drive, Hershey, PA  17033</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>(610) 332-5291</t>
+          <t>(717) 583-5102</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>bzaiser@mamail.net</t>
+          <t>communications@vistaautismservices.org</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>www.moravianacademy.org</t>
+          <t>www.thevistaschool.org</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -9914,28 +9930,28 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>The Vista School</t>
+          <t>Tom Johnson Boys Academy d/b/a Mon Valley Boys Academy</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
-          <t>1021 Springboard Drive, Hershey, PA  17033</t>
+          <t>653 S. Agnes Lane, West Mifflin, PA  15122</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>(717) 583-5102</t>
+          <t>(412) 599-1458</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>communications@vistaautismservices.org</t>
+          <t>sheila.rawlings@mytjba.org</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>www.thevistaschool.org</t>
+          <t>mytjba.org</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -9952,28 +9968,28 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Tom Johnson Boys Academy d/b/a Mon Valley Boys Academy</t>
+          <t>Trinity Lutheran Church &amp; School</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
-          <t>653 S. Agnes Lane, West Mifflin, PA  15122</t>
+          <t>53 West Avenue, Wellsboro, PA  16901</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>(412) 599-1458</t>
+          <t>(570) 724-7723</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>sheila.rawlings@mytjba.org</t>
+          <t>bkohler@trinitylutheranwellsboro.org</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>mytjba.org</t>
+          <t>www.trinitylutheranwellsboro.org</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -9990,28 +10006,28 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Trinity Lutheran Church &amp; School</t>
+          <t>United Disabilities Services</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
-          <t>53 West Avenue, Wellsboro, PA  16901</t>
+          <t>2270 Erin Court, Lancaster, PA  17601</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>(570) 724-7723</t>
+          <t>(717) 715-8770</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>bkohler@trinitylutheranwellsboro.org</t>
+          <t>elizabethb@udservices.org</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>www.trinitylutheranwellsboro.org</t>
+          <t>www.udservices.org/school</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -10028,28 +10044,28 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>United Disabilities Services</t>
+          <t>United Way of Lackawanna and Wayne Counties</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2270 Erin Court, Lancaster, PA  17601</t>
+          <t>615 Jefferson Avenue, Scranton, PA  18510</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>(717) 715-8770</t>
+          <t>(570) 343-1267</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>elizabethb@udservices.org</t>
+          <t>abassani@uwlc.net</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>www.udservices.org/school</t>
+          <t>www.uwlc.net</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -10066,28 +10082,28 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>United Way of Lackawanna and Wayne Counties</t>
+          <t>Upland Country Day School</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
-          <t>615 Jefferson Avenue, Scranton, PA  18510</t>
+          <t>420 West Street Road, Kennett Square, PA  19348</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>(570) 343-1267</t>
+          <t>(610) 444-8114</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>abassani@uwlc.net</t>
+          <t>eswarter@uplandcds.org</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>www.uwlc.net</t>
+          <t>www.uplandcds.org</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -10104,28 +10120,28 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Upland Country Day School</t>
+          <t>Valley School of Ligonier</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
-          <t>420 West Street Road, Kennett Square, PA  19348</t>
+          <t>P.O. Box 616, Ligonier, PA  15658</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>(610) 444-8114</t>
+          <t>(724) 238-5028</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>eswarter@uplandcds.org</t>
+          <t>development@valleyschoolofligonier.org</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>www.uplandcds.org</t>
+          <t>www.valleyschoolofligonier.org</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -10142,28 +10158,28 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Valley School of Ligonier</t>
+          <t>Villa Joseph Marie High School</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
-          <t>P.O. Box 616, Ligonier, PA  15658</t>
+          <t>1180 Holland Road, Holland, PA  18966</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>(724) 238-5028</t>
+          <t>(215) 357-8810</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>development@valleyschoolofligonier.org</t>
+          <t>lharkrader@vjmhs.org</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>www.valleyschoolofligonier.org</t>
+          <t>www.vjmhs.org</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -10180,28 +10196,28 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Villa Joseph Marie High School</t>
+          <t>Villa Maria Academy (Malvern)</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
-          <t>1180 Holland Road, Holland, PA  18966</t>
+          <t>370 Central Avenue, Malvern, PA  19355</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>(215) 357-8810</t>
+          <t>(610) 644-2551</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>lharkrader@vjmhs.org</t>
+          <t>mlamb@vmahs.org</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>www.vjmhs.org</t>
+          <t>www.vmahs.org</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -10218,28 +10234,28 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Villa Maria Academy (Malvern)</t>
+          <t>Villa Maria Academy Lower School</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
-          <t>370 Central Avenue, Malvern, PA  19355</t>
+          <t>280 IHM Drive, Malvern, PA  19355</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>(610) 644-2551</t>
+          <t>(610) 644-4864</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>mlamb@vmahs.org</t>
+          <t>pscanlon@villamaria.org</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>www.vmahs.org</t>
+          <t>www.villamaria.org</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -10256,28 +10272,28 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Villa Maria Academy Lower School</t>
+          <t>Villa Maria Cathedral Preparatory Catholic School System</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
-          <t>280 IHM Drive, Malvern, PA  19355</t>
+          <t>250 West 10th Street, Erie, PA  16501</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>(610) 644-4864</t>
+          <t>(814) 453-7737</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>pscanlon@villamaria.org</t>
+          <t>Joanne.Rogers@cathedralprep.com</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>www.villamaria.org</t>
+          <t>www.cathedralprep.com</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -10294,28 +10310,28 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Villa Maria Cathedral Preparatory Catholic School System</t>
+          <t>Waldorf School of Pittsburgh</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
-          <t>250 West 10th Street, Erie, PA  16501</t>
+          <t>201 S. Winebiddle Street, Pittsburgh, PA  15224</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>(814) 453-7737</t>
+          <t>(412) 441-5792</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Joanne.Rogers@cathedralprep.com</t>
+          <t>dtaylor@waldorfpittsburgh.org</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>www.cathedralprep.com</t>
+          <t>www.waldorfpittsburgh.org</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -10332,28 +10348,28 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Waldorf School of Pittsburgh</t>
+          <t>Washington County Community Foundation</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
         <is>
-          <t>201 S. Winebiddle Street, Pittsburgh, PA  15224</t>
+          <t>1253 Route 519, P.O. Box 308, Eighty Four, PA  15330</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>(412) 441-5792</t>
+          <t>(724) 222-6330</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>dtaylor@waldorfpittsburgh.org</t>
+          <t>scholar@wccf.net</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>www.waldorfpittsburgh.org</t>
+          <t>www.wccf.net</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -10370,28 +10386,28 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Washington County Community Foundation</t>
+          <t>Water Street Ministries</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
-          <t>1253 Route 519, P.O. Box 308, Eighty Four, PA  15330</t>
+          <t>P.O. Box 7267, Lancaster, PA  17604</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>(724) 222-6330</t>
+          <t>(717) 358-2084</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>scholar@wccf.net</t>
+          <t>mwilcox@wsm.org</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>www.wccf.net</t>
+          <t>www.wsm.org</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -10408,28 +10424,28 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Water Street Ministries</t>
+          <t>Watson Institute</t>
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
-          <t>P.O. Box 7267, Lancaster, PA  17604</t>
+          <t>301 Camp Meeting Road, Sewickley, PA  15143</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>(717) 358-2084</t>
+          <t>(412) 749-2885</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>mwilcox@wsm.org</t>
+          <t>karam@thewatsoninstitute.org</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>www.wsm.org</t>
+          <t>www.thewatsoninstitute.org</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -10446,28 +10462,28 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Watson Institute</t>
+          <t>West Chester Friends School</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
-          <t>301 Camp Meeting Road, Sewickley, PA  15143</t>
+          <t>415 N. High Street, West Chester, PA  19380</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>(412) 749-2885</t>
+          <t>(610) 696-2615</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>karam@thewatsoninstitute.org</t>
+          <t>smccardell@wcfriends.org</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>www.thewatsoninstitute.org</t>
+          <t>www.wcfriends.org</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -10484,28 +10500,28 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>West Chester Friends School</t>
+          <t>Western Pennsylvania Montessori School</t>
         </is>
       </c>
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
-          <t>415 N. High Street, West Chester, PA  19380</t>
+          <t>2379 Wyland Ave., Allison Park, PA  15101</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>(610) 696-2615</t>
+          <t>(412) 487-2700</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>smccardell@wcfriends.org</t>
+          <t>director@wpms.edu</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>www.wcfriends.org</t>
+          <t>www.wpms.edu</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -10522,28 +10538,28 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Western Pennsylvania Montessori School</t>
+          <t>Westtown School</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2379 Wyland Ave., Allison Park, PA  15101</t>
+          <t>975 Westtown Road, West Chester, PA  19382</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>(412) 487-2700</t>
+          <t>(610) 399-7922</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>director@wpms.edu</t>
+          <t>courtnay.tyus@westtown.edu</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>www.wpms.edu</t>
+          <t>www.westtown.edu</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -10560,28 +10576,28 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Westtown School</t>
+          <t>William Penn Charter School</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
-          <t>975 Westtown Road, West Chester, PA  19382</t>
+          <t>3000 West School House Lane, Philadelphia, PA  19144</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>(610) 399-7922</t>
+          <t>(215) 844-3460</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>courtnay.tyus@westtown.edu</t>
+          <t>crahill@penncharter.com</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>www.westtown.edu</t>
+          <t>www.penncharter.com</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -10598,28 +10614,28 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>William Penn Charter School</t>
+          <t>Winchester Thurston School</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
         <is>
-          <t>3000 West School House Lane, Philadelphia, PA  19144</t>
+          <t>555 Morewood Avenue, Pittsburgh, PA  15213</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>(215) 844-3460</t>
+          <t>(412) 578-3738</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>crahill@penncharter.com</t>
+          <t>gaym@winchesterthurston.org</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>www.penncharter.com</t>
+          <t>www.winchesterthurston.org</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -10636,28 +10652,28 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Winchester Thurston School</t>
+          <t>Wyoming Seminary</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
-          <t>555 Morewood Avenue, Pittsburgh, PA  15213</t>
+          <t>201 North Sprague Avenue, Kingston, PA  18704</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>(412) 578-3738</t>
+          <t>(570) 270-2143</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>gaym@winchesterthurston.org</t>
+          <t>cconnolly@wyomingseminary.org</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>www.winchesterthurston.org</t>
+          <t>www.wyomingseminary.org</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -10674,28 +10690,28 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Wyoming Seminary</t>
+          <t>Wyoming Valley Children's Association</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
-          <t>201 North Sprague Avenue, Kingston, PA  18704</t>
+          <t>1133 Wyoming Avenue, Forty Fort, PA  18704</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>(570) 270-2143</t>
+          <t>(570) 714-1246</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>cconnolly@wyomingseminary.org</t>
+          <t>nzanon@wvcakids.org</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>www.wyomingseminary.org</t>
+          <t>www.wvcakids.org</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -10712,28 +10728,28 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Wyoming Valley Children's Association</t>
+          <t>Wyoming Valley Montessori Association Inc.</t>
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
-          <t>1133 Wyoming Avenue, Forty Fort, PA  18704</t>
+          <t>d/b/a Wyoming Valley Montessori School, 851 West Market Street, Kingston, PA  18704</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>(570) 714-1246</t>
+          <t>(570) 288-3708</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>nzanon@wvcakids.org</t>
+          <t>cdecker@wvms.org</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>www.wvcakids.org</t>
+          <t>www.wvms.org</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -10750,28 +10766,28 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Wyoming Valley Montessori Association, Inc.</t>
+          <t>Yeshiva Academy of Harrisburg Foundation</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
-          <t>d/b/a Wyoming Valley Montessori School, 851 West Market Street, Kingston, PA  18704</t>
+          <t>d/b/a Silver Academy Foundation, 4218 Prosperous Drive, Harrisburg, PA  17112</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>(570) 288-3708</t>
+          <t>(717) 574-9121</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>cdecker@wvms.org</t>
+          <t>martinlowy@comcast.net</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>www.wvms.org</t>
+          <t>www.silveracademypa.org</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -10788,28 +10804,28 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Yeshiva Academy of Harrisburg Foundation</t>
+          <t>York College of Pennsylvania</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
-          <t>d/b/a Silver Academy Foundation, 4218 Prosperous Drive, Harrisburg, PA  17112</t>
+          <t>441 Country Club Road, York, PA  17403</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>(717) 574-9121</t>
+          <t>(717) 815-6711</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>martinlowy@comcast.net</t>
+          <t>dkey1@ycds.org</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>www.silveracademypa.org</t>
+          <t>www.ycds.org</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -10826,28 +10842,28 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>York College of Pennsylvania</t>
+          <t>YSC Academy</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
-          <t>441 Country Club Road, York, PA  17403</t>
+          <t>2501 Seaport Drive, Union Power Plant, River Front Suite No. 100, Chester, PA  19013</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>(717) 815-6711</t>
+          <t>(610) 722-0500</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>dkey1@ycds.org</t>
+          <t>gokupniarek@strikerpartners.com</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>www.ycds.org</t>
+          <t>www.yscacademy.com</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -10859,38 +10875,22 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>RI</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>YSC Academy</t>
+          <t>Achievement for Children with Challenges Empowered by School Scholarships (ACCESS)</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>2501 Seaport Drive, Union Power Plant, River Front Suite No. 100, Chester, PA  19013</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>(610) 722-0500</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>gokupniarek@strikerpartners.com</t>
-        </is>
-      </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>www.yscacademy.com</t>
-        </is>
-      </c>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" t="inlineStr"/>
+      <c r="F310" t="inlineStr"/>
+      <c r="G310" t="inlineStr"/>
       <c r="H310" t="inlineStr">
         <is>
-          <t>https://dced.pa.gov/wp-content/themes/business2015/csv/eitc_so_list.csv</t>
+          <t>https://tax.ri.gov/sites/g/files/xkgbur541/files/2025-07/Tax%20Credits%20for%20Contributions%20to%20Scholarship%20Organizations%20June%2030%20SGO%20List%20for%202025.pdf</t>
         </is>
       </c>
     </row>
@@ -10902,7 +10902,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Achievement for Children with Challenges Empowered by School Scholarships (ACCESS)</t>
+          <t>Children's Tuition Fund of Rhode Island</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Children's Tuition Fund of Rhode Island</t>
+          <t>F.A.C.E. of Rhode Island</t>
         </is>
       </c>
       <c r="C312" t="inlineStr"/>
@@ -10946,7 +10946,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>F.A.C.E. of Rhode Island</t>
+          <t>Scholarships to Economically Poor Students (STEPS)</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
@@ -10968,7 +10968,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Scholarships to Economically Poor Students (STEPS)</t>
+          <t>Star Scholars Opportunity Program</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
@@ -10990,7 +10990,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Star Scholars Opportunity Program</t>
+          <t>Teach Initiative</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
@@ -11012,7 +11012,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Teach Initiative</t>
+          <t>The Foundation for Rhode Island Day Schools</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
@@ -11029,12 +11029,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>RI</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>The Foundation for Rhode Island Day Schools</t>
+          <t>South Dakota Partners in Education</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
@@ -11044,19 +11044,19 @@
       <c r="G317" t="inlineStr"/>
       <c r="H317" t="inlineStr">
         <is>
-          <t>https://tax.ri.gov/sites/g/files/xkgbur541/files/2025-07/Tax%20Credits%20for%20Contributions%20to%20Scholarship%20Organizations%20June%2030%20SGO%20List%20for%202025.pdf</t>
+          <t>https://dlr.sd.gov/insurance/tax_credit_program/documents/sgo_participation_list.pdf</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>South Dakota Partners in Education</t>
+          <t>Anabaptist Scholarship Foundation of Virginia</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
@@ -11066,7 +11066,7 @@
       <c r="G318" t="inlineStr"/>
       <c r="H318" t="inlineStr">
         <is>
-          <t>https://dlr.sd.gov/insurance/tax_credit_program/documents/sgo_participation_list.pdf</t>
+          <t>https://www.doe.virginia.gov/home/showpublisheddocument/76022/639071974827670000</t>
         </is>
       </c>
     </row>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Anabaptist Scholarship Foundation of Virginia</t>
+          <t>Anna Julia Cooper Scholarship Foundation</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
@@ -11100,7 +11100,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Anna Julia Cooper Scholarship Foundation</t>
+          <t>Association of Christian Schools International (ACSI Children's Tuition Fund)</t>
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
@@ -11122,7 +11122,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Association of Christian Schools International (ACSI Children's Tuition Fund)</t>
+          <t>Atlantic Shores Tuition Foundation</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Atlantic Shores Tuition Foundation</t>
+          <t>Autism Envisioned Foundation</t>
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
@@ -11166,7 +11166,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Autism Envisioned Foundation</t>
+          <t>Boys Home of Virginia</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Boys Home of Virginia</t>
+          <t>Carlisle School</t>
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Carlisle School</t>
+          <t>Rise Academy</t>
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Rise Academy</t>
+          <t>Diocese of Arlington Scholarship Foundation Inc.</t>
         </is>
       </c>
       <c r="C326" t="inlineStr"/>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Diocese of Arlington Scholarship Foundation, Inc.</t>
+          <t>Dunlap Garrick Christian Community Foundation</t>
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Dunlap Garrick Christian Community Foundation</t>
+          <t>Elijah House Academy</t>
         </is>
       </c>
       <c r="C328" t="inlineStr"/>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Elijah House Academy</t>
+          <t>Fishburne-Hudgins Educational Foundation</t>
         </is>
       </c>
       <c r="C329" t="inlineStr"/>
@@ -11320,7 +11320,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Fishburne-Hudgins Educational Foundation</t>
+          <t>Fork Union Military Academy Foundation</t>
         </is>
       </c>
       <c r="C330" t="inlineStr"/>
@@ -11342,7 +11342,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Fork Union Military Academy Foundation</t>
+          <t>Foundation for Educational &amp; Developmental Opportunity</t>
         </is>
       </c>
       <c r="C331" t="inlineStr"/>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Foundation for Educational &amp; Developmental Opportunity</t>
+          <t>Great Aspirations Scholarship Program (GRASP)</t>
         </is>
       </c>
       <c r="C332" t="inlineStr"/>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Great Aspirations Scholarship Program (GRASP)</t>
+          <t>Hague School Foundation</t>
         </is>
       </c>
       <c r="C333" t="inlineStr"/>
@@ -11408,7 +11408,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Hague School Foundation</t>
+          <t>Hargrave Foundation</t>
         </is>
       </c>
       <c r="C334" t="inlineStr"/>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Hargrave Foundation</t>
+          <t>Imago Dei Scholarship Foundation</t>
         </is>
       </c>
       <c r="C335" t="inlineStr"/>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Imago Dei Scholarship Foundation</t>
+          <t>Jackson-Feild Homes</t>
         </is>
       </c>
       <c r="C336" t="inlineStr"/>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Jackson-Feild Homes</t>
+          <t>Liberty Christian Academy Inc.</t>
         </is>
       </c>
       <c r="C337" t="inlineStr"/>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Liberty Christian Academy, Inc.</t>
+          <t>Lunenburg-Nottoway Educational Foundation</t>
         </is>
       </c>
       <c r="C338" t="inlineStr"/>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Lunenburg-Nottoway Educational Foundation</t>
+          <t>McMahon-Parater Foundation for Education</t>
         </is>
       </c>
       <c r="C339" t="inlineStr"/>
@@ -11540,7 +11540,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>McMahon-Parater Foundation for Education</t>
+          <t>New Covenant Schools</t>
         </is>
       </c>
       <c r="C340" t="inlineStr"/>
@@ -11562,7 +11562,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>New Covenant Schools</t>
+          <t>North Cross School</t>
         </is>
       </c>
       <c r="C341" t="inlineStr"/>
@@ -11584,7 +11584,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>North Cross School</t>
+          <t>Potomac Conference Education Fund</t>
         </is>
       </c>
       <c r="C342" t="inlineStr"/>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Potomac Conference Education Fund</t>
+          <t>RENEWANATION</t>
         </is>
       </c>
       <c r="C343" t="inlineStr"/>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>RENEWANATION</t>
+          <t>Richmond Jewish Foundation</t>
         </is>
       </c>
       <c r="C344" t="inlineStr"/>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Richmond Jewish Foundation</t>
+          <t>St. Andrew's School</t>
         </is>
       </c>
       <c r="C345" t="inlineStr"/>
@@ -11672,7 +11672,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>St. Andrew's School</t>
+          <t>Commonwealth Opportunity Scholars</t>
         </is>
       </c>
       <c r="C346" t="inlineStr"/>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Commonwealth Opportunity Scholars</t>
+          <t>The Community Foundation of Harrisonburg and Rockingham County</t>
         </is>
       </c>
       <c r="C347" t="inlineStr"/>
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>The Community Foundation of Harrisonburg and Rockingham County</t>
+          <t>The Community Foundation of the Rappahannock River Region</t>
         </is>
       </c>
       <c r="C348" t="inlineStr"/>
@@ -11738,7 +11738,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>The Community Foundation of the Rappahannock River Region</t>
+          <t>The Hunter School Foundation</t>
         </is>
       </c>
       <c r="C349" t="inlineStr"/>
@@ -11760,7 +11760,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>The Hunter School Foundation</t>
+          <t>The Nansemond-Suffolk Academy Educational Foundation</t>
         </is>
       </c>
       <c r="C350" t="inlineStr"/>
@@ -11782,7 +11782,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>The Nansemond-Suffolk Academy Educational Foundation</t>
+          <t>Tidewater Jewish Foundation Inc.</t>
         </is>
       </c>
       <c r="C351" t="inlineStr"/>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Tidewater Jewish Foundation, Inc.</t>
+          <t>Torah Education Scholarship Foundation</t>
         </is>
       </c>
       <c r="C352" t="inlineStr"/>
@@ -11826,7 +11826,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Torah Education Scholarship Foundation</t>
+          <t>Up Rva</t>
         </is>
       </c>
       <c r="C353" t="inlineStr"/>
@@ -11848,7 +11848,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Up Rva</t>
+          <t>Virginia Foundation for LD Students</t>
         </is>
       </c>
       <c r="C354" t="inlineStr"/>
@@ -11870,7 +11870,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Virginia Foundation for LD Students</t>
+          <t>Hampton Roads International Montessori School</t>
         </is>
       </c>
       <c r="C355" t="inlineStr"/>
@@ -11884,28 +11884,6 @@
         </is>
       </c>
     </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>Hampton Roads International Montessori School</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr"/>
-      <c r="D356" t="inlineStr"/>
-      <c r="E356" t="inlineStr"/>
-      <c r="F356" t="inlineStr"/>
-      <c r="G356" t="inlineStr"/>
-      <c r="H356" t="inlineStr">
-        <is>
-          <t>https://www.doe.virginia.gov/home/showpublisheddocument/76022/639071974827670000</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
